--- a/RECEITAS TAXA ADM.xlsx
+++ b/RECEITAS TAXA ADM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HomePC\.gemini\antigravity-ide\scratch\analise-dre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4919145F-8896-4D5B-90C9-65BA62BC875D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B32862-419D-4651-9D9C-89F2596BC922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="30">
   <si>
     <t>Unna</t>
   </si>
@@ -121,6 +121,9 @@
   <si>
     <t>Receitas ADM</t>
   </si>
+  <si>
+    <t xml:space="preserve"> R$                        -  </t>
+  </si>
 </sst>
 </file>
 
@@ -130,11 +133,11 @@
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_(&quot;R$ &quot;* #,##0.00_);_(&quot;R$ &quot;* \(#,##0.00\);_(&quot;R$ &quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;R$ &quot;* #,##0.00_);_(&quot;R$ &quot;* \(#,##0.00\);_(&quot;R$ &quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="mm/yyyy"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -210,14 +213,14 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -227,9 +230,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -439,7 +442,7 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -670,7 +673,7 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="181" formatCode="mm/yyyy"/>
+      <numFmt numFmtId="168" formatCode="mm/yyyy"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -690,7 +693,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BancoReceitasTable" displayName="BancoReceitasTable" ref="A1:E691">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BancoReceitasTable" displayName="BancoReceitasTable" ref="A1:E696">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Projeto"/>
     <tableColumn id="13" xr3:uid="{99B5B262-4E36-4F00-91BC-C71FC6DB0293}" name="Tipologia" dataDxfId="1"/>
@@ -851,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:E691"/>
+  <dimension ref="A1:E696"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="26.85546875" customWidth="1"/>
@@ -4829,7 +4832,7 @@
         <v>28</v>
       </c>
       <c r="C243" s="3">
-        <v>67799.292406384033</v>
+        <v>65261.14</v>
       </c>
       <c r="D243" s="3">
         <v>65261.141000000003</v>
@@ -4846,7 +4849,7 @@
         <v>28</v>
       </c>
       <c r="C244" s="3">
-        <v>80298.519792962383</v>
+        <v>76993.48</v>
       </c>
       <c r="D244" s="3">
         <v>76993.481</v>
@@ -4863,7 +4866,7 @@
         <v>28</v>
       </c>
       <c r="C245" s="3">
-        <v>93091.621963850092</v>
+        <v>89459.09</v>
       </c>
       <c r="D245" s="3">
         <v>89459.092000000004</v>
@@ -4880,7 +4883,7 @@
         <v>28</v>
       </c>
       <c r="C246" s="3">
-        <v>56394.557159293872</v>
+        <v>147746.59</v>
       </c>
       <c r="D246" s="3">
         <v>147746.59</v>
@@ -4897,7 +4900,7 @@
         <v>28</v>
       </c>
       <c r="C247" s="3">
-        <v>65105.281540402473</v>
+        <v>129512.84</v>
       </c>
       <c r="D247" s="3">
         <v>129512.84</v>
@@ -4914,7 +4917,7 @@
         <v>28</v>
       </c>
       <c r="C248" s="3">
-        <v>61385.898678576181</v>
+        <v>148727.01999999999</v>
       </c>
       <c r="D248" s="3">
         <v>148727.01999999999</v>
@@ -4931,7 +4934,7 @@
         <v>28</v>
       </c>
       <c r="C249" s="3">
-        <v>94088.405443177166</v>
+        <v>161939.65</v>
       </c>
       <c r="D249" s="3">
         <v>161939.65</v>
@@ -4948,7 +4951,7 @@
         <v>28</v>
       </c>
       <c r="C250" s="3">
-        <v>118228.84063921495</v>
+        <v>227086.8</v>
       </c>
       <c r="D250" s="3">
         <v>223185.60973583115</v>
@@ -4965,7 +4968,7 @@
         <v>28</v>
       </c>
       <c r="C251" s="3">
-        <v>82308.760051792415</v>
+        <v>260326.74</v>
       </c>
       <c r="D251" s="3">
         <v>257916.9790871164</v>
@@ -4982,7 +4985,7 @@
         <v>28</v>
       </c>
       <c r="C252" s="3">
-        <v>75702.773115966498</v>
+        <v>300590.25</v>
       </c>
       <c r="D252" s="3">
         <v>296628.61066605983</v>
@@ -4999,7 +5002,7 @@
         <v>28</v>
       </c>
       <c r="C253" s="3">
-        <v>64843.519347541172</v>
+        <v>318921.73</v>
       </c>
       <c r="D253" s="3">
         <v>312081.02263981133</v>
@@ -5016,7 +5019,7 @@
         <v>28</v>
       </c>
       <c r="C254" s="3">
-        <v>164392.43687510595</v>
+        <v>351008.9</v>
       </c>
       <c r="D254" s="3">
         <v>343287.25888166309</v>
@@ -5033,7 +5036,7 @@
         <v>28</v>
       </c>
       <c r="C255" s="3">
-        <v>188245.29237142461</v>
+        <v>375939.69</v>
       </c>
       <c r="D255" s="3">
         <v>366781.74312216497</v>
@@ -5050,7 +5053,7 @@
         <v>28</v>
       </c>
       <c r="C256" s="3">
-        <v>99753.649377040172</v>
+        <v>383019.2</v>
       </c>
       <c r="D256" s="3">
         <v>372798.22664559499</v>
@@ -5067,7 +5070,7 @@
         <v>28</v>
       </c>
       <c r="C257" s="3">
-        <v>228221.43636734033</v>
+        <v>424085.36</v>
       </c>
       <c r="D257" s="3">
         <v>411937.07012415456</v>
@@ -5084,7 +5087,7 @@
         <v>28</v>
       </c>
       <c r="C258" s="3">
-        <v>98745.431155653103</v>
+        <v>328868.13</v>
       </c>
       <c r="D258" s="3">
         <v>319127.77719144791</v>
@@ -5101,7 +5104,7 @@
         <v>28</v>
       </c>
       <c r="C259" s="3">
-        <v>166057.65778935311</v>
+        <v>340252.41</v>
       </c>
       <c r="D259" s="3">
         <v>329319.16157688777</v>
@@ -5118,7 +5121,7 @@
         <v>28</v>
       </c>
       <c r="C260" s="3">
-        <v>105095.67611345652</v>
+        <v>256434.06</v>
       </c>
       <c r="D260" s="3">
         <v>247621.21180339801</v>
@@ -5135,7 +5138,7 @@
         <v>28</v>
       </c>
       <c r="C261" s="3">
-        <v>160786.76445105742</v>
+        <v>260310.09</v>
       </c>
       <c r="D261" s="3">
         <v>250855.2542084007</v>
@@ -5152,7 +5155,7 @@
         <v>28</v>
       </c>
       <c r="C262" s="3">
-        <v>217328.80914298337</v>
+        <v>278158.43</v>
       </c>
       <c r="D262" s="3">
         <v>267410.12154762237</v>
@@ -5169,7 +5172,7 @@
         <v>28</v>
       </c>
       <c r="C263" s="3">
-        <v>223960.72735638081</v>
+        <v>198853.41</v>
       </c>
       <c r="D263" s="3">
         <v>190388.12671829486</v>
@@ -5185,8 +5188,8 @@
       <c r="B264" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C264" s="3">
-        <v>284014.40989396046</v>
+      <c r="C264" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D264" s="3">
         <v>169808.69468307818</v>
@@ -5202,8 +5205,8 @@
       <c r="B265" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C265" s="3">
-        <v>399625.21870709886</v>
+      <c r="C265" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D265" s="3">
         <v>224047.11135465943</v>
@@ -5219,8 +5222,8 @@
       <c r="B266" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C266" s="3">
-        <v>313899.27084089181</v>
+      <c r="C266" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D266" s="3">
         <v>256507.95557092282</v>
@@ -5236,8 +5239,8 @@
       <c r="B267" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C267" s="3">
-        <v>296632.72085421719</v>
+      <c r="C267" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D267" s="3">
         <v>241350.51618362853</v>
@@ -5253,8 +5256,8 @@
       <c r="B268" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C268" s="3">
-        <v>316340.24823390151</v>
+      <c r="C268" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D268" s="3">
         <v>249851.59082992279</v>
@@ -5270,8 +5273,8 @@
       <c r="B269" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C269" s="3">
-        <v>342708.66505052266</v>
+      <c r="C269" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D269" s="3">
         <v>259759.90071645114</v>
@@ -5287,8 +5290,8 @@
       <c r="B270" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C270" s="3">
-        <v>430467.92073291191</v>
+      <c r="C270" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D270" s="3">
         <v>264381.13121420774</v>
@@ -5305,7 +5308,7 @@
         <v>28</v>
       </c>
       <c r="C271" s="3">
-        <v>431906.58119180059</v>
+        <v>221068.84</v>
       </c>
       <c r="D271" s="3">
         <v>213673.75465270071</v>
@@ -5322,7 +5325,7 @@
         <v>28</v>
       </c>
       <c r="C272" s="3">
-        <v>325581.37376718386</v>
+        <v>318039.02</v>
       </c>
       <c r="D272" s="3">
         <v>176375.67321924114</v>
@@ -5339,7 +5342,7 @@
         <v>28</v>
       </c>
       <c r="C273" s="3">
-        <v>311550.96667898021</v>
+        <v>627728.86</v>
       </c>
       <c r="D273" s="3">
         <v>169421.79362995201</v>
@@ -5356,7 +5359,7 @@
         <v>28</v>
       </c>
       <c r="C274" s="3">
-        <v>289978.74195600208</v>
+        <v>394888.77</v>
       </c>
       <c r="D274" s="3">
         <v>75228.333738672736</v>
@@ -5373,7 +5376,7 @@
         <v>28</v>
       </c>
       <c r="C275" s="3">
-        <v>359314.64205159876</v>
+        <v>531945.79</v>
       </c>
       <c r="D275" s="3">
         <v>22125.980511374339</v>
@@ -5390,7 +5393,7 @@
         <v>28</v>
       </c>
       <c r="C276" s="3">
-        <v>346928.17774100654</v>
+        <v>598553.74</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="4">
@@ -5405,7 +5408,7 @@
         <v>28</v>
       </c>
       <c r="C277" s="3">
-        <v>341946.45257366507</v>
+        <v>432253.01</v>
       </c>
       <c r="D277" s="3"/>
       <c r="E277" s="4">
@@ -5420,7 +5423,7 @@
         <v>28</v>
       </c>
       <c r="C278" s="3">
-        <v>131747.90285380371</v>
+        <v>231392.12</v>
       </c>
       <c r="D278" s="3"/>
       <c r="E278" s="4">
@@ -5434,8 +5437,8 @@
       <c r="B279" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C279" s="3">
-        <v>65703.073185928675</v>
+      <c r="C279" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="D279" s="3"/>
       <c r="E279" s="4">
@@ -5450,7 +5453,7 @@
         <v>28</v>
       </c>
       <c r="C280" s="3">
-        <v>35661.87108603563</v>
+        <v>20028.330000000002</v>
       </c>
       <c r="D280" s="3"/>
       <c r="E280" s="4">
@@ -5465,7 +5468,7 @@
         <v>28</v>
       </c>
       <c r="C281" s="3">
-        <v>24979.690634333194</v>
+        <v>168138.81</v>
       </c>
       <c r="D281" s="3"/>
       <c r="E281" s="4">
@@ -5474,87 +5477,77 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C282" s="3">
-        <v>25212.524959232152</v>
-      </c>
-      <c r="D282" s="3">
-        <v>24691.682193703251</v>
-      </c>
+        <v>98070.38</v>
+      </c>
+      <c r="D282" s="3"/>
       <c r="E282" s="4">
-        <v>45839</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C283" s="3">
-        <v>67204.745290938736</v>
-      </c>
-      <c r="D283" s="3">
-        <v>65816.423199018289</v>
-      </c>
+        <v>84094.83</v>
+      </c>
+      <c r="D283" s="3"/>
       <c r="E283" s="4">
-        <v>45870</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C284" s="3">
-        <v>81518.247506175598</v>
-      </c>
-      <c r="D284" s="3">
-        <v>79834.235708831198</v>
-      </c>
+        <v>57748.03</v>
+      </c>
+      <c r="D284" s="3"/>
       <c r="E284" s="4">
-        <v>45901</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C285" s="3">
-        <v>54457.985144909791</v>
-      </c>
-      <c r="D285" s="3">
-        <v>53332.986850059562</v>
-      </c>
+        <v>46336.35</v>
+      </c>
+      <c r="D285" s="3"/>
       <c r="E285" s="4">
-        <v>45931</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C286" s="3">
-        <v>45839.064371133427</v>
-      </c>
-      <c r="D286" s="3">
-        <v>44892.119395832604</v>
-      </c>
+        <v>94742.51</v>
+      </c>
+      <c r="D286" s="3"/>
       <c r="E286" s="4">
-        <v>45962</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
@@ -5565,13 +5558,13 @@
         <v>28</v>
       </c>
       <c r="C287" s="3">
-        <v>30767.521918081562</v>
+        <v>25212.524959232152</v>
       </c>
       <c r="D287" s="3">
-        <v>30131.920658283623</v>
+        <v>24691.682193703251</v>
       </c>
       <c r="E287" s="4">
-        <v>45992</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -5582,13 +5575,13 @@
         <v>28</v>
       </c>
       <c r="C288" s="3">
-        <v>59033.491767121071</v>
+        <v>67204.745290938736</v>
       </c>
       <c r="D288" s="3">
-        <v>57813.977669220003</v>
+        <v>65816.423199018289</v>
       </c>
       <c r="E288" s="4">
-        <v>46023</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -5599,13 +5592,13 @@
         <v>28</v>
       </c>
       <c r="C289" s="3">
-        <v>43563.452441023081</v>
+        <v>81518.247506175598</v>
       </c>
       <c r="D289" s="3">
-        <v>42162.848076049311</v>
+        <v>79834.235708831198</v>
       </c>
       <c r="E289" s="4">
-        <v>46054</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -5616,13 +5609,13 @@
         <v>28</v>
       </c>
       <c r="C290" s="3">
-        <v>41696.11818349018</v>
+        <v>54457.985144909791</v>
       </c>
       <c r="D290" s="3">
-        <v>50616.952564215171</v>
+        <v>53332.986850059562</v>
       </c>
       <c r="E290" s="4">
-        <v>46082</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
@@ -5633,13 +5626,13 @@
         <v>28</v>
       </c>
       <c r="C291" s="3">
-        <v>24016.950594697322</v>
+        <v>45839.064371133427</v>
       </c>
       <c r="D291" s="3">
-        <v>24016.950594697322</v>
+        <v>44892.119395832604</v>
       </c>
       <c r="E291" s="4">
-        <v>46113</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
@@ -5650,13 +5643,13 @@
         <v>28</v>
       </c>
       <c r="C292" s="3">
-        <v>22279.218700217491</v>
+        <v>30767.521918081562</v>
       </c>
       <c r="D292" s="3">
-        <v>22502.004899053598</v>
+        <v>30131.920658283623</v>
       </c>
       <c r="E292" s="4">
-        <v>46143</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
@@ -5667,13 +5660,13 @@
         <v>28</v>
       </c>
       <c r="C293" s="3">
-        <v>37793.894683640276</v>
+        <v>59033.491767121071</v>
       </c>
       <c r="D293" s="3">
-        <v>22310.157754646581</v>
+        <v>57813.977669220003</v>
       </c>
       <c r="E293" s="4">
-        <v>46174</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
@@ -5683,12 +5676,14 @@
       <c r="B294" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C294" s="3"/>
+      <c r="C294" s="3">
+        <v>43563.452441023081</v>
+      </c>
       <c r="D294" s="3">
-        <v>49691.786272111094</v>
+        <v>42162.848076049311</v>
       </c>
       <c r="E294" s="4">
-        <v>46204</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
@@ -5698,12 +5693,14 @@
       <c r="B295" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C295" s="3"/>
+      <c r="C295" s="3">
+        <v>41696.11818349018</v>
+      </c>
       <c r="D295" s="3">
-        <v>53845.225014443873</v>
+        <v>50616.952564215171</v>
       </c>
       <c r="E295" s="4">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
@@ -5713,12 +5710,14 @@
       <c r="B296" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C296" s="3"/>
+      <c r="C296" s="3">
+        <v>24016.950594697322</v>
+      </c>
       <c r="D296" s="3">
-        <v>106119.79913019613</v>
+        <v>24016.950594697322</v>
       </c>
       <c r="E296" s="4">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -5728,12 +5727,14 @@
       <c r="B297" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C297" s="3"/>
+      <c r="C297" s="3">
+        <v>22279.218700217491</v>
+      </c>
       <c r="D297" s="3">
-        <v>75995.762885377932</v>
+        <v>22502.004899053598</v>
       </c>
       <c r="E297" s="4">
-        <v>46296</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -5743,12 +5744,14 @@
       <c r="B298" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C298" s="3"/>
+      <c r="C298" s="3">
+        <v>37793.894683640276</v>
+      </c>
       <c r="D298" s="3">
-        <v>153017.06009183478</v>
+        <v>22310.157754646581</v>
       </c>
       <c r="E298" s="4">
-        <v>46327</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
@@ -5760,10 +5763,10 @@
       </c>
       <c r="C299" s="3"/>
       <c r="D299" s="3">
-        <v>95957.779999007005</v>
+        <v>49691.786272111094</v>
       </c>
       <c r="E299" s="4">
-        <v>46357</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -5775,10 +5778,10 @@
       </c>
       <c r="C300" s="3"/>
       <c r="D300" s="3">
-        <v>93885.455564390097</v>
+        <v>53845.225014443873</v>
       </c>
       <c r="E300" s="4">
-        <v>46388</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
@@ -5790,10 +5793,10 @@
       </c>
       <c r="C301" s="3"/>
       <c r="D301" s="3">
-        <v>782.06549708552996</v>
+        <v>106119.79913019613</v>
       </c>
       <c r="E301" s="4">
-        <v>46419</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -5805,10 +5808,10 @@
       </c>
       <c r="C302" s="3"/>
       <c r="D302" s="3">
-        <v>899.37532164835932</v>
+        <v>75995.762885377932</v>
       </c>
       <c r="E302" s="4">
-        <v>46447</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -5820,93 +5823,85 @@
       </c>
       <c r="C303" s="3"/>
       <c r="D303" s="3">
-        <v>742.96222223125346</v>
+        <v>153017.06009183478</v>
       </c>
       <c r="E303" s="4">
-        <v>46478</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C304" s="3">
-        <v>130557.75855251723</v>
-      </c>
+      <c r="C304" s="3"/>
       <c r="D304" s="3">
-        <v>121706.83669056174</v>
+        <v>95957.779999007005</v>
       </c>
       <c r="E304" s="4">
-        <v>46082</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C305" s="3">
-        <v>145517.47756593174</v>
-      </c>
+      <c r="C305" s="3"/>
       <c r="D305" s="3">
-        <v>160282.66404025999</v>
+        <v>93885.455564390097</v>
       </c>
       <c r="E305" s="4">
-        <v>46113</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C306" s="3">
-        <v>213848.5456893518</v>
-      </c>
+      <c r="C306" s="3"/>
       <c r="D306" s="3">
-        <v>139534.81269658412</v>
+        <v>782.06549708552996</v>
       </c>
       <c r="E306" s="4">
-        <v>46143</v>
+        <v>46419</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C307" s="3">
-        <v>154879.189241727</v>
-      </c>
+      <c r="C307" s="3"/>
       <c r="D307" s="3">
-        <v>190644.10172966716</v>
+        <v>899.37532164835932</v>
       </c>
       <c r="E307" s="4">
-        <v>46174</v>
+        <v>46447</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C308" s="3"/>
       <c r="D308" s="3">
-        <v>218665.07066914329</v>
+        <v>742.96222223125346</v>
       </c>
       <c r="E308" s="4">
-        <v>46204</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
@@ -5916,12 +5911,14 @@
       <c r="B309" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C309" s="3"/>
+      <c r="C309" s="3">
+        <v>130557.75855251723</v>
+      </c>
       <c r="D309" s="3">
-        <v>194438.83823416091</v>
+        <v>121706.83669056174</v>
       </c>
       <c r="E309" s="4">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
@@ -5931,12 +5928,14 @@
       <c r="B310" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C310" s="3"/>
+      <c r="C310" s="3">
+        <v>145517.47756593174</v>
+      </c>
       <c r="D310" s="3">
-        <v>212706.03684854065</v>
+        <v>160282.66404025999</v>
       </c>
       <c r="E310" s="4">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
@@ -5946,12 +5945,14 @@
       <c r="B311" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C311" s="3"/>
+      <c r="C311" s="3">
+        <v>213848.5456893518</v>
+      </c>
       <c r="D311" s="3">
-        <v>201638.08963449506</v>
+        <v>139534.81269658412</v>
       </c>
       <c r="E311" s="4">
-        <v>46296</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
@@ -5961,12 +5962,14 @@
       <c r="B312" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C312" s="3"/>
+      <c r="C312" s="3">
+        <v>154879.189241727</v>
+      </c>
       <c r="D312" s="3">
-        <v>253511.41308461598</v>
+        <v>190644.10172966716</v>
       </c>
       <c r="E312" s="4">
-        <v>46327</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
@@ -5978,10 +5981,10 @@
       </c>
       <c r="C313" s="3"/>
       <c r="D313" s="3">
-        <v>182703.12133667633</v>
+        <v>218665.07066914329</v>
       </c>
       <c r="E313" s="4">
-        <v>46357</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
@@ -5993,10 +5996,10 @@
       </c>
       <c r="C314" s="3"/>
       <c r="D314" s="3">
-        <v>275220.72990772035</v>
+        <v>194438.83823416091</v>
       </c>
       <c r="E314" s="4">
-        <v>46388</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
@@ -6008,10 +6011,10 @@
       </c>
       <c r="C315" s="3"/>
       <c r="D315" s="3">
-        <v>260199.02052536307</v>
+        <v>212706.03684854065</v>
       </c>
       <c r="E315" s="4">
-        <v>46419</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
@@ -6023,10 +6026,10 @@
       </c>
       <c r="C316" s="3"/>
       <c r="D316" s="3">
-        <v>372541.47237241012</v>
+        <v>201638.08963449506</v>
       </c>
       <c r="E316" s="4">
-        <v>46447</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
@@ -6038,10 +6041,10 @@
       </c>
       <c r="C317" s="3"/>
       <c r="D317" s="3">
-        <v>346409.3611102929</v>
+        <v>253511.41308461598</v>
       </c>
       <c r="E317" s="4">
-        <v>46478</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
@@ -6053,10 +6056,10 @@
       </c>
       <c r="C318" s="3"/>
       <c r="D318" s="3">
-        <v>384376.49057458638</v>
+        <v>182703.12133667633</v>
       </c>
       <c r="E318" s="4">
-        <v>46508</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
@@ -6068,10 +6071,10 @@
       </c>
       <c r="C319" s="3"/>
       <c r="D319" s="3">
-        <v>428319.46353792783</v>
+        <v>275220.72990772035</v>
       </c>
       <c r="E319" s="4">
-        <v>46539</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
@@ -6083,10 +6086,10 @@
       </c>
       <c r="C320" s="3"/>
       <c r="D320" s="3">
-        <v>421140.90494358575</v>
+        <v>260199.02052536307</v>
       </c>
       <c r="E320" s="4">
-        <v>46569</v>
+        <v>46419</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
@@ -6098,10 +6101,10 @@
       </c>
       <c r="C321" s="3"/>
       <c r="D321" s="3">
-        <v>469060.96078479185</v>
+        <v>372541.47237241012</v>
       </c>
       <c r="E321" s="4">
-        <v>46600</v>
+        <v>46447</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
@@ -6113,10 +6116,10 @@
       </c>
       <c r="C322" s="3"/>
       <c r="D322" s="3">
-        <v>367686.05404775304</v>
+        <v>346409.3611102929</v>
       </c>
       <c r="E322" s="4">
-        <v>46631</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
@@ -6128,10 +6131,10 @@
       </c>
       <c r="C323" s="3"/>
       <c r="D323" s="3">
-        <v>372141.82142757607</v>
+        <v>384376.49057458638</v>
       </c>
       <c r="E323" s="4">
-        <v>46661</v>
+        <v>46508</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
@@ -6143,10 +6146,10 @@
       </c>
       <c r="C324" s="3"/>
       <c r="D324" s="3">
-        <v>446043.96832483035</v>
+        <v>428319.46353792783</v>
       </c>
       <c r="E324" s="4">
-        <v>46692</v>
+        <v>46539</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
@@ -6158,10 +6161,10 @@
       </c>
       <c r="C325" s="3"/>
       <c r="D325" s="3">
-        <v>311111.79896031803</v>
+        <v>421140.90494358575</v>
       </c>
       <c r="E325" s="4">
-        <v>46722</v>
+        <v>46569</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
@@ -6173,10 +6176,10 @@
       </c>
       <c r="C326" s="3"/>
       <c r="D326" s="3">
-        <v>305627.73834288761</v>
+        <v>469060.96078479185</v>
       </c>
       <c r="E326" s="4">
-        <v>46753</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
@@ -6188,10 +6191,10 @@
       </c>
       <c r="C327" s="3"/>
       <c r="D327" s="3">
-        <v>231778.54284055185</v>
+        <v>367686.05404775304</v>
       </c>
       <c r="E327" s="4">
-        <v>46784</v>
+        <v>46631</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
@@ -6203,10 +6206,10 @@
       </c>
       <c r="C328" s="3"/>
       <c r="D328" s="3">
-        <v>244098.91822220921</v>
+        <v>372141.82142757607</v>
       </c>
       <c r="E328" s="4">
-        <v>46813</v>
+        <v>46661</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
@@ -6218,10 +6221,10 @@
       </c>
       <c r="C329" s="3"/>
       <c r="D329" s="3">
-        <v>202824.1589779802</v>
+        <v>446043.96832483035</v>
       </c>
       <c r="E329" s="4">
-        <v>46844</v>
+        <v>46692</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
@@ -6233,10 +6236,10 @@
       </c>
       <c r="C330" s="3"/>
       <c r="D330" s="3">
-        <v>216301.30828066528</v>
+        <v>311111.79896031803</v>
       </c>
       <c r="E330" s="4">
-        <v>46874</v>
+        <v>46722</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
@@ -6248,10 +6251,10 @@
       </c>
       <c r="C331" s="3"/>
       <c r="D331" s="3">
-        <v>165141.24738905087</v>
+        <v>305627.73834288761</v>
       </c>
       <c r="E331" s="4">
-        <v>46905</v>
+        <v>46753</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
@@ -6263,10 +6266,10 @@
       </c>
       <c r="C332" s="3"/>
       <c r="D332" s="3">
-        <v>153274.04575221747</v>
+        <v>231778.54284055185</v>
       </c>
       <c r="E332" s="4">
-        <v>46935</v>
+        <v>46784</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
@@ -6278,10 +6281,10 @@
       </c>
       <c r="C333" s="3"/>
       <c r="D333" s="3">
-        <v>174766.6779602975</v>
+        <v>244098.91822220921</v>
       </c>
       <c r="E333" s="4">
-        <v>46966</v>
+        <v>46813</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
@@ -6293,10 +6296,10 @@
       </c>
       <c r="C334" s="3"/>
       <c r="D334" s="3">
-        <v>139604.78949518781</v>
+        <v>202824.1589779802</v>
       </c>
       <c r="E334" s="4">
-        <v>46997</v>
+        <v>46844</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
@@ -6308,10 +6311,10 @@
       </c>
       <c r="C335" s="3"/>
       <c r="D335" s="3">
-        <v>140029.9431847127</v>
+        <v>216301.30828066528</v>
       </c>
       <c r="E335" s="4">
-        <v>47027</v>
+        <v>46874</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
@@ -6323,10 +6326,10 @@
       </c>
       <c r="C336" s="3"/>
       <c r="D336" s="3">
-        <v>84069.190393174416</v>
+        <v>165141.24738905087</v>
       </c>
       <c r="E336" s="4">
-        <v>47058</v>
+        <v>46905</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -6338,10 +6341,10 @@
       </c>
       <c r="C337" s="3"/>
       <c r="D337" s="3">
-        <v>34694.62291577772</v>
+        <v>153274.04575221747</v>
       </c>
       <c r="E337" s="4">
-        <v>47088</v>
+        <v>46935</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
@@ -6353,10 +6356,10 @@
       </c>
       <c r="C338" s="3"/>
       <c r="D338" s="3">
-        <v>51875.220394012395</v>
+        <v>174766.6779602975</v>
       </c>
       <c r="E338" s="4">
-        <v>47119</v>
+        <v>46966</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -6368,10 +6371,10 @@
       </c>
       <c r="C339" s="3"/>
       <c r="D339" s="3">
-        <v>23523.629521159535</v>
+        <v>139604.78949518781</v>
       </c>
       <c r="E339" s="4">
-        <v>47150</v>
+        <v>46997</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
@@ -6383,10 +6386,10 @@
       </c>
       <c r="C340" s="3"/>
       <c r="D340" s="3">
-        <v>21098.31894327913</v>
+        <v>140029.9431847127</v>
       </c>
       <c r="E340" s="4">
-        <v>47178</v>
+        <v>47027</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
@@ -6398,10 +6401,10 @@
       </c>
       <c r="C341" s="3"/>
       <c r="D341" s="3">
-        <v>30676.451904165464</v>
+        <v>84069.190393174416</v>
       </c>
       <c r="E341" s="4">
-        <v>47209</v>
+        <v>47058</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -6413,10 +6416,10 @@
       </c>
       <c r="C342" s="3"/>
       <c r="D342" s="3">
-        <v>45680.875426169805</v>
+        <v>34694.62291577772</v>
       </c>
       <c r="E342" s="4">
-        <v>47239</v>
+        <v>47088</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
@@ -6428,10 +6431,10 @@
       </c>
       <c r="C343" s="3"/>
       <c r="D343" s="3">
-        <v>10957.105833724585</v>
+        <v>51875.220394012395</v>
       </c>
       <c r="E343" s="4">
-        <v>47270</v>
+        <v>47119</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
@@ -6443,10 +6446,10 @@
       </c>
       <c r="C344" s="3"/>
       <c r="D344" s="3">
-        <v>3021.6313353260739</v>
+        <v>23523.629521159535</v>
       </c>
       <c r="E344" s="4">
-        <v>47300</v>
+        <v>47150</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
@@ -6458,10 +6461,10 @@
       </c>
       <c r="C345" s="3"/>
       <c r="D345" s="3">
-        <v>377.74179724702827</v>
+        <v>21098.31894327913</v>
       </c>
       <c r="E345" s="4">
-        <v>47331</v>
+        <v>47178</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
@@ -6473,10 +6476,10 @@
       </c>
       <c r="C346" s="3"/>
       <c r="D346" s="3">
-        <v>7177.0941476935404</v>
+        <v>30676.451904165464</v>
       </c>
       <c r="E346" s="4">
-        <v>47362</v>
+        <v>47209</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
@@ -6488,10 +6491,10 @@
       </c>
       <c r="C347" s="3"/>
       <c r="D347" s="3">
-        <v>8310.3195394346258</v>
+        <v>45680.875426169805</v>
       </c>
       <c r="E347" s="4">
-        <v>47392</v>
+        <v>47239</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
@@ -6503,85 +6506,85 @@
       </c>
       <c r="C348" s="3"/>
       <c r="D348" s="3">
-        <v>6799.352350446512</v>
+        <v>10957.105833724585</v>
       </c>
       <c r="E348" s="4">
-        <v>47423</v>
+        <v>47270</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C349" s="3">
-        <v>30130.775000000001</v>
-      </c>
-      <c r="D349" s="3"/>
+      <c r="C349" s="3"/>
+      <c r="D349" s="3">
+        <v>3021.6313353260739</v>
+      </c>
       <c r="E349" s="4">
-        <v>45170</v>
+        <v>47300</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C350" s="3">
-        <v>38558.961000000003</v>
-      </c>
-      <c r="D350" s="3"/>
+      <c r="C350" s="3"/>
+      <c r="D350" s="3">
+        <v>377.74179724702827</v>
+      </c>
       <c r="E350" s="4">
-        <v>45200</v>
+        <v>47331</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C351" s="3">
-        <v>77485.978000000003</v>
-      </c>
-      <c r="D351" s="3"/>
+      <c r="C351" s="3"/>
+      <c r="D351" s="3">
+        <v>7177.0941476935404</v>
+      </c>
       <c r="E351" s="4">
-        <v>45231</v>
+        <v>47362</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C352" s="3">
-        <v>24178.572</v>
-      </c>
-      <c r="D352" s="3"/>
+      <c r="C352" s="3"/>
+      <c r="D352" s="3">
+        <v>8310.3195394346258</v>
+      </c>
       <c r="E352" s="4">
-        <v>45261</v>
+        <v>47392</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C353" s="3">
-        <v>62108.562000000013</v>
-      </c>
-      <c r="D353" s="3"/>
+      <c r="C353" s="3"/>
+      <c r="D353" s="3">
+        <v>6799.352350446512</v>
+      </c>
       <c r="E353" s="4">
-        <v>45292</v>
+        <v>47423</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
@@ -6592,11 +6595,11 @@
         <v>28</v>
       </c>
       <c r="C354" s="3">
-        <v>37123.801999999996</v>
+        <v>30130.775000000001</v>
       </c>
       <c r="D354" s="3"/>
       <c r="E354" s="4">
-        <v>45323</v>
+        <v>45170</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -6607,11 +6610,11 @@
         <v>28</v>
       </c>
       <c r="C355" s="3">
-        <v>20666.242000000002</v>
+        <v>38558.961000000003</v>
       </c>
       <c r="D355" s="3"/>
       <c r="E355" s="4">
-        <v>45352</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
@@ -6622,11 +6625,11 @@
         <v>28</v>
       </c>
       <c r="C356" s="3">
-        <v>70332.395000000004</v>
+        <v>77485.978000000003</v>
       </c>
       <c r="D356" s="3"/>
       <c r="E356" s="4">
-        <v>45383</v>
+        <v>45231</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
@@ -6637,11 +6640,11 @@
         <v>28</v>
       </c>
       <c r="C357" s="3">
-        <v>46771.264999999999</v>
+        <v>24178.572</v>
       </c>
       <c r="D357" s="3"/>
       <c r="E357" s="4">
-        <v>45413</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
@@ -6652,11 +6655,11 @@
         <v>28</v>
       </c>
       <c r="C358" s="3">
-        <v>43923.928000000014</v>
+        <v>62108.562000000013</v>
       </c>
       <c r="D358" s="3"/>
       <c r="E358" s="4">
-        <v>45444</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -6667,11 +6670,11 @@
         <v>28</v>
       </c>
       <c r="C359" s="3">
-        <v>46834.330999999998</v>
+        <v>37123.801999999996</v>
       </c>
       <c r="D359" s="3"/>
       <c r="E359" s="4">
-        <v>45474</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
@@ -6682,11 +6685,11 @@
         <v>28</v>
       </c>
       <c r="C360" s="3">
-        <v>78670.63900000001</v>
+        <v>20666.242000000002</v>
       </c>
       <c r="D360" s="3"/>
       <c r="E360" s="4">
-        <v>45505</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
@@ -6697,11 +6700,11 @@
         <v>28</v>
       </c>
       <c r="C361" s="3">
-        <v>103769.64199999999</v>
+        <v>70332.395000000004</v>
       </c>
       <c r="D361" s="3"/>
       <c r="E361" s="4">
-        <v>45536</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
@@ -6712,11 +6715,11 @@
         <v>28</v>
       </c>
       <c r="C362" s="3">
-        <v>87782.781000000017</v>
+        <v>46771.264999999999</v>
       </c>
       <c r="D362" s="3"/>
       <c r="E362" s="4">
-        <v>45566</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -6727,11 +6730,11 @@
         <v>28</v>
       </c>
       <c r="C363" s="3">
-        <v>76568.732999999993</v>
+        <v>43923.928000000014</v>
       </c>
       <c r="D363" s="3"/>
       <c r="E363" s="4">
-        <v>45597</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
@@ -6742,11 +6745,11 @@
         <v>28</v>
       </c>
       <c r="C364" s="3">
-        <v>107837.569</v>
+        <v>46834.330999999998</v>
       </c>
       <c r="D364" s="3"/>
       <c r="E364" s="4">
-        <v>45627</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
@@ -6757,11 +6760,11 @@
         <v>28</v>
       </c>
       <c r="C365" s="3">
-        <v>88596.103000000003</v>
+        <v>78670.63900000001</v>
       </c>
       <c r="D365" s="3"/>
       <c r="E365" s="4">
-        <v>45658</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -6772,11 +6775,11 @@
         <v>28</v>
       </c>
       <c r="C366" s="3">
-        <v>150026.516</v>
+        <v>103769.64199999999</v>
       </c>
       <c r="D366" s="3"/>
       <c r="E366" s="4">
-        <v>45689</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
@@ -6787,11 +6790,11 @@
         <v>28</v>
       </c>
       <c r="C367" s="3">
-        <v>179151.39599999995</v>
+        <v>87782.781000000017</v>
       </c>
       <c r="D367" s="3"/>
       <c r="E367" s="4">
-        <v>45717</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
@@ -6802,11 +6805,11 @@
         <v>28</v>
       </c>
       <c r="C368" s="3">
-        <v>152045.40000000002</v>
+        <v>76568.732999999993</v>
       </c>
       <c r="D368" s="3"/>
       <c r="E368" s="4">
-        <v>45748</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -6817,11 +6820,11 @@
         <v>28</v>
       </c>
       <c r="C369" s="3">
-        <v>167363.64200000002</v>
+        <v>107837.569</v>
       </c>
       <c r="D369" s="3"/>
       <c r="E369" s="4">
-        <v>45778</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -6832,11 +6835,11 @@
         <v>28</v>
       </c>
       <c r="C370" s="3">
-        <v>177970.74705999997</v>
+        <v>88596.103000000003</v>
       </c>
       <c r="D370" s="3"/>
       <c r="E370" s="4">
-        <v>45809</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
@@ -6847,11 +6850,11 @@
         <v>28</v>
       </c>
       <c r="C371" s="3">
-        <v>210039.28201000002</v>
+        <v>150026.516</v>
       </c>
       <c r="D371" s="3"/>
       <c r="E371" s="4">
-        <v>45839</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
@@ -6862,11 +6865,11 @@
         <v>28</v>
       </c>
       <c r="C372" s="3">
-        <v>106528.88401999998</v>
+        <v>179151.39599999995</v>
       </c>
       <c r="D372" s="3"/>
       <c r="E372" s="4">
-        <v>45870</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
@@ -6877,11 +6880,11 @@
         <v>28</v>
       </c>
       <c r="C373" s="3">
-        <v>140690.58727999998</v>
+        <v>152045.40000000002</v>
       </c>
       <c r="D373" s="3"/>
       <c r="E373" s="4">
-        <v>45901</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -6892,11 +6895,11 @@
         <v>28</v>
       </c>
       <c r="C374" s="3">
-        <v>191261.03599</v>
+        <v>167363.64200000002</v>
       </c>
       <c r="D374" s="3"/>
       <c r="E374" s="4">
-        <v>45931</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -6907,11 +6910,11 @@
         <v>28</v>
       </c>
       <c r="C375" s="3">
-        <v>70253.478990000003</v>
+        <v>177970.74705999997</v>
       </c>
       <c r="D375" s="3"/>
       <c r="E375" s="4">
-        <v>45962</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -6922,11 +6925,11 @@
         <v>28</v>
       </c>
       <c r="C376" s="3">
-        <v>166515.68897000002</v>
+        <v>210039.28201000002</v>
       </c>
       <c r="D376" s="3"/>
       <c r="E376" s="4">
-        <v>45992</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
@@ -6937,11 +6940,11 @@
         <v>28</v>
       </c>
       <c r="C377" s="3">
-        <v>86831.99768</v>
+        <v>106528.88401999998</v>
       </c>
       <c r="D377" s="3"/>
       <c r="E377" s="4">
-        <v>46023</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -6952,11 +6955,11 @@
         <v>28</v>
       </c>
       <c r="C378" s="3">
-        <v>73873.089990000008</v>
+        <v>140690.58727999998</v>
       </c>
       <c r="D378" s="3"/>
       <c r="E378" s="4">
-        <v>46054</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
@@ -6967,11 +6970,11 @@
         <v>28</v>
       </c>
       <c r="C379" s="3">
-        <v>203586.33702000004</v>
+        <v>191261.03599</v>
       </c>
       <c r="D379" s="3"/>
       <c r="E379" s="4">
-        <v>46082</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
@@ -6982,11 +6985,11 @@
         <v>28</v>
       </c>
       <c r="C380" s="3">
-        <v>0</v>
+        <v>70253.478990000003</v>
       </c>
       <c r="D380" s="3"/>
       <c r="E380" s="4">
-        <v>46113</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -6997,11 +7000,11 @@
         <v>28</v>
       </c>
       <c r="C381" s="3">
-        <v>0</v>
+        <v>166515.68897000002</v>
       </c>
       <c r="D381" s="3"/>
       <c r="E381" s="4">
-        <v>46143</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
@@ -7012,92 +7015,86 @@
         <v>28</v>
       </c>
       <c r="C382" s="3">
-        <v>0</v>
+        <v>86831.99768</v>
       </c>
       <c r="D382" s="3"/>
       <c r="E382" s="4">
-        <v>46174</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C383" s="3">
-        <v>24793.759999999998</v>
-      </c>
-      <c r="D383" s="3">
-        <v>11292.80706258391</v>
-      </c>
+        <v>73873.089990000008</v>
+      </c>
+      <c r="D383" s="3"/>
       <c r="E383" s="4">
-        <v>46113</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C384" s="3">
-        <v>15771.623288620114</v>
-      </c>
-      <c r="D384" s="3">
-        <v>22384.323892746368</v>
-      </c>
+        <v>203586.33702000004</v>
+      </c>
+      <c r="D384" s="3"/>
       <c r="E384" s="4">
-        <v>46143</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C385" s="3">
-        <v>26475.609246023771</v>
-      </c>
-      <c r="D385" s="3">
-        <v>28623.602210727429</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D385" s="3"/>
       <c r="E385" s="4">
-        <v>46174</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C386" s="3"/>
-      <c r="D386" s="3">
-        <v>16610.991857632467</v>
-      </c>
+      <c r="C386" s="3">
+        <v>0</v>
+      </c>
+      <c r="D386" s="3"/>
       <c r="E386" s="4">
-        <v>46204</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C387" s="3"/>
-      <c r="D387" s="3">
-        <v>13736.098356247983</v>
-      </c>
+      <c r="C387" s="3">
+        <v>0</v>
+      </c>
+      <c r="D387" s="3"/>
       <c r="E387" s="4">
-        <v>46235</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
@@ -7107,12 +7104,14 @@
       <c r="B388" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C388" s="3"/>
+      <c r="C388" s="3">
+        <v>24793.759999999998</v>
+      </c>
       <c r="D388" s="3">
-        <v>13197.588803662673</v>
+        <v>11292.80706258391</v>
       </c>
       <c r="E388" s="4">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
@@ -7122,12 +7121,14 @@
       <c r="B389" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C389" s="3"/>
+      <c r="C389" s="3">
+        <v>15771.623288620114</v>
+      </c>
       <c r="D389" s="3">
-        <v>13087.673292852491</v>
+        <v>22384.323892746368</v>
       </c>
       <c r="E389" s="4">
-        <v>46296</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
@@ -7137,12 +7138,14 @@
       <c r="B390" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C390" s="3"/>
+      <c r="C390" s="3">
+        <v>26475.609246023771</v>
+      </c>
       <c r="D390" s="3">
-        <v>18324.067690712716</v>
+        <v>28623.602210727429</v>
       </c>
       <c r="E390" s="4">
-        <v>46327</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
@@ -7154,10 +7157,10 @@
       </c>
       <c r="C391" s="3"/>
       <c r="D391" s="3">
-        <v>3307.1852635072619</v>
+        <v>16610.991857632467</v>
       </c>
       <c r="E391" s="4">
-        <v>46357</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
@@ -7169,10 +7172,10 @@
       </c>
       <c r="C392" s="3"/>
       <c r="D392" s="3">
-        <v>4414.0102417935732</v>
+        <v>13736.098356247983</v>
       </c>
       <c r="E392" s="4">
-        <v>46388</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
@@ -7184,10 +7187,10 @@
       </c>
       <c r="C393" s="3"/>
       <c r="D393" s="3">
-        <v>4032.001365212182</v>
+        <v>13197.588803662673</v>
       </c>
       <c r="E393" s="4">
-        <v>46419</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
@@ -7199,10 +7202,10 @@
       </c>
       <c r="C394" s="3"/>
       <c r="D394" s="3">
-        <v>183.62217655841809</v>
+        <v>13087.673292852491</v>
       </c>
       <c r="E394" s="4">
-        <v>46447</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
@@ -7214,10 +7217,10 @@
       </c>
       <c r="C395" s="3"/>
       <c r="D395" s="3">
-        <v>101.5322704343982</v>
+        <v>18324.067690712716</v>
       </c>
       <c r="E395" s="4">
-        <v>46478</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
@@ -7229,10 +7232,10 @@
       </c>
       <c r="C396" s="3"/>
       <c r="D396" s="3">
-        <v>117.56368155561897</v>
+        <v>3307.1852635072619</v>
       </c>
       <c r="E396" s="4">
-        <v>46508</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
@@ -7244,95 +7247,85 @@
       </c>
       <c r="C397" s="3"/>
       <c r="D397" s="3">
-        <v>101.5322704343982</v>
+        <v>4414.0102417935732</v>
       </c>
       <c r="E397" s="4">
-        <v>46539</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C398" s="3">
-        <v>26851.820000000007</v>
-      </c>
+      <c r="C398" s="3"/>
       <c r="D398" s="3">
-        <v>73492.855181265666</v>
+        <v>4032.001365212182</v>
       </c>
       <c r="E398" s="4">
-        <v>45292</v>
+        <v>46419</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C399" s="3">
-        <v>166811.38069934564</v>
-      </c>
+      <c r="C399" s="3"/>
       <c r="D399" s="3">
-        <v>195487.31110603162</v>
+        <v>183.62217655841809</v>
       </c>
       <c r="E399" s="4">
-        <v>45323</v>
+        <v>46447</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C400" s="3">
-        <v>154809.84939034589</v>
-      </c>
+      <c r="C400" s="3"/>
       <c r="D400" s="3">
-        <v>224756.69659730501</v>
+        <v>101.5322704343982</v>
       </c>
       <c r="E400" s="4">
-        <v>45352</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C401" s="3">
-        <v>255368.67</v>
-      </c>
+      <c r="C401" s="3"/>
       <c r="D401" s="3">
-        <v>223097.26223554183</v>
+        <v>117.56368155561897</v>
       </c>
       <c r="E401" s="4">
-        <v>45383</v>
+        <v>46508</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C402" s="3">
-        <v>162881.49229537524</v>
-      </c>
+      <c r="C402" s="3"/>
       <c r="D402" s="3">
-        <v>146805.03255676565</v>
+        <v>101.5322704343982</v>
       </c>
       <c r="E402" s="4">
-        <v>45413</v>
+        <v>46539</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
@@ -7343,13 +7336,13 @@
         <v>28</v>
       </c>
       <c r="C403" s="3">
-        <v>101930.18455784231</v>
+        <v>26851.820000000007</v>
       </c>
       <c r="D403" s="3">
-        <v>114612.68743379244</v>
+        <v>73492.855181265666</v>
       </c>
       <c r="E403" s="4">
-        <v>45444</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
@@ -7360,13 +7353,13 @@
         <v>28</v>
       </c>
       <c r="C404" s="3">
-        <v>171765.37459269757</v>
+        <v>166811.38069934564</v>
       </c>
       <c r="D404" s="3">
-        <v>165479.94181190446</v>
+        <v>195487.31110603162</v>
       </c>
       <c r="E404" s="4">
-        <v>45474</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
@@ -7377,13 +7370,13 @@
         <v>28</v>
       </c>
       <c r="C405" s="3">
-        <v>200119.48519500322</v>
+        <v>154809.84939034589</v>
       </c>
       <c r="D405" s="3">
-        <v>153235.56239591271</v>
+        <v>224756.69659730501</v>
       </c>
       <c r="E405" s="4">
-        <v>45505</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
@@ -7394,13 +7387,13 @@
         <v>28</v>
       </c>
       <c r="C406" s="3">
-        <v>122618.12646991033</v>
+        <v>255368.67</v>
       </c>
       <c r="D406" s="3">
-        <v>170763.88289773563</v>
+        <v>223097.26223554183</v>
       </c>
       <c r="E406" s="4">
-        <v>45536</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
@@ -7411,13 +7404,13 @@
         <v>28</v>
       </c>
       <c r="C407" s="3">
-        <v>109173.12817728696</v>
+        <v>162881.49229537524</v>
       </c>
       <c r="D407" s="3">
-        <v>94498.684539740629</v>
+        <v>146805.03255676565</v>
       </c>
       <c r="E407" s="4">
-        <v>45566</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
@@ -7428,13 +7421,13 @@
         <v>28</v>
       </c>
       <c r="C408" s="3">
-        <v>64939.473290446986</v>
+        <v>101930.18455784231</v>
       </c>
       <c r="D408" s="3">
-        <v>97181.352062473889</v>
+        <v>114612.68743379244</v>
       </c>
       <c r="E408" s="4">
-        <v>45597</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
@@ -7445,13 +7438,13 @@
         <v>28</v>
       </c>
       <c r="C409" s="3">
-        <v>98395.325175217033</v>
+        <v>171765.37459269757</v>
       </c>
       <c r="D409" s="3">
-        <v>81701.45647079288</v>
+        <v>165479.94181190446</v>
       </c>
       <c r="E409" s="4">
-        <v>45627</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
@@ -7462,13 +7455,13 @@
         <v>28</v>
       </c>
       <c r="C410" s="3">
-        <v>103451.0419977219</v>
+        <v>200119.48519500322</v>
       </c>
       <c r="D410" s="3">
-        <v>61307.972932066135</v>
+        <v>153235.56239591271</v>
       </c>
       <c r="E410" s="4">
-        <v>45658</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
@@ -7479,13 +7472,13 @@
         <v>28</v>
       </c>
       <c r="C411" s="3">
-        <v>122918.29</v>
+        <v>122618.12646991033</v>
       </c>
       <c r="D411" s="3">
-        <v>126727.81265862651</v>
+        <v>170763.88289773563</v>
       </c>
       <c r="E411" s="4">
-        <v>45689</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
@@ -7496,13 +7489,13 @@
         <v>28</v>
       </c>
       <c r="C412" s="3">
-        <v>136650.91</v>
+        <v>109173.12817728696</v>
       </c>
       <c r="D412" s="3">
-        <v>137834.41282565994</v>
+        <v>94498.684539740629</v>
       </c>
       <c r="E412" s="4">
-        <v>45717</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
@@ -7513,13 +7506,13 @@
         <v>28</v>
       </c>
       <c r="C413" s="3">
-        <v>136165.79502335232</v>
+        <v>64939.473290446986</v>
       </c>
       <c r="D413" s="3">
-        <v>153193.8377705579</v>
+        <v>97181.352062473889</v>
       </c>
       <c r="E413" s="4">
-        <v>45748</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
@@ -7530,13 +7523,13 @@
         <v>28</v>
       </c>
       <c r="C414" s="3">
-        <v>199823.24395059652</v>
+        <v>98395.325175217033</v>
       </c>
       <c r="D414" s="3">
-        <v>144793.3259503216</v>
+        <v>81701.45647079288</v>
       </c>
       <c r="E414" s="4">
-        <v>45778</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
@@ -7547,13 +7540,13 @@
         <v>28</v>
       </c>
       <c r="C415" s="3">
-        <v>167059.63684127861</v>
+        <v>103451.0419977219</v>
       </c>
       <c r="D415" s="3">
-        <v>169959.11456421643</v>
+        <v>61307.972932066135</v>
       </c>
       <c r="E415" s="4">
-        <v>45809</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
@@ -7564,13 +7557,13 @@
         <v>28</v>
       </c>
       <c r="C416" s="3">
-        <v>160446.04582894297</v>
+        <v>122918.29</v>
       </c>
       <c r="D416" s="3">
-        <v>196230.06442875389</v>
+        <v>126727.81265862651</v>
       </c>
       <c r="E416" s="4">
-        <v>45839</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
@@ -7581,13 +7574,13 @@
         <v>28</v>
       </c>
       <c r="C417" s="3">
-        <v>198879.01733365844</v>
+        <v>136650.91</v>
       </c>
       <c r="D417" s="3">
-        <v>170602.04455675464</v>
+        <v>137834.41282565994</v>
       </c>
       <c r="E417" s="4">
-        <v>45870</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
@@ -7598,13 +7591,13 @@
         <v>28</v>
       </c>
       <c r="C418" s="3">
-        <v>200379.34</v>
+        <v>136165.79502335232</v>
       </c>
       <c r="D418" s="3">
-        <v>142063.24842978764</v>
+        <v>153193.8377705579</v>
       </c>
       <c r="E418" s="4">
-        <v>45901</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
@@ -7615,13 +7608,13 @@
         <v>28</v>
       </c>
       <c r="C419" s="3">
-        <v>214970.12258073571</v>
+        <v>199823.24395059652</v>
       </c>
       <c r="D419" s="3">
-        <v>144804.30602459595</v>
+        <v>144793.3259503216</v>
       </c>
       <c r="E419" s="4">
-        <v>45931</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -7632,13 +7625,13 @@
         <v>28</v>
       </c>
       <c r="C420" s="3">
-        <v>96943.01</v>
+        <v>167059.63684127861</v>
       </c>
       <c r="D420" s="3">
-        <v>152071.1240663589</v>
+        <v>169959.11456421643</v>
       </c>
       <c r="E420" s="4">
-        <v>45962</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
@@ -7649,13 +7642,13 @@
         <v>28</v>
       </c>
       <c r="C421" s="3">
-        <v>123079.08</v>
+        <v>160446.04582894297</v>
       </c>
       <c r="D421" s="3">
-        <v>110966.5758362138</v>
+        <v>196230.06442875389</v>
       </c>
       <c r="E421" s="4">
-        <v>45992</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
@@ -7666,13 +7659,13 @@
         <v>28</v>
       </c>
       <c r="C422" s="3">
-        <v>179863.01220826618</v>
+        <v>198879.01733365844</v>
       </c>
       <c r="D422" s="3">
-        <v>164577.46838944222</v>
+        <v>170602.04455675464</v>
       </c>
       <c r="E422" s="4">
-        <v>46023</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
@@ -7683,13 +7676,13 @@
         <v>28</v>
       </c>
       <c r="C423" s="3">
-        <v>164075.29806907824</v>
+        <v>200379.34</v>
       </c>
       <c r="D423" s="3">
-        <v>194553.09972318442</v>
+        <v>142063.24842978764</v>
       </c>
       <c r="E423" s="4">
-        <v>46054</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
@@ -7700,13 +7693,13 @@
         <v>28</v>
       </c>
       <c r="C424" s="3">
-        <v>181931.9978069053</v>
+        <v>214970.12258073571</v>
       </c>
       <c r="D424" s="3">
-        <v>319950.70281713275</v>
+        <v>144804.30602459595</v>
       </c>
       <c r="E424" s="4">
-        <v>46082</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
@@ -7717,13 +7710,13 @@
         <v>28</v>
       </c>
       <c r="C425" s="3">
-        <v>163601.48263622401</v>
+        <v>96943.01</v>
       </c>
       <c r="D425" s="3">
-        <v>274870.90740838833</v>
+        <v>152071.1240663589</v>
       </c>
       <c r="E425" s="4">
-        <v>46113</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
@@ -7734,13 +7727,13 @@
         <v>28</v>
       </c>
       <c r="C426" s="3">
-        <v>121181.49074320766</v>
+        <v>123079.08</v>
       </c>
       <c r="D426" s="3">
-        <v>325257.22176030773</v>
+        <v>110966.5758362138</v>
       </c>
       <c r="E426" s="4">
-        <v>46143</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
@@ -7751,13 +7744,13 @@
         <v>28</v>
       </c>
       <c r="C427" s="3">
-        <v>156205.71780410968</v>
+        <v>179863.01220826618</v>
       </c>
       <c r="D427" s="3">
-        <v>310175.55260951165</v>
+        <v>164577.46838944222</v>
       </c>
       <c r="E427" s="4">
-        <v>46174</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
@@ -7767,12 +7760,14 @@
       <c r="B428" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C428" s="3"/>
+      <c r="C428" s="3">
+        <v>164075.29806907824</v>
+      </c>
       <c r="D428" s="3">
-        <v>277375.85079180083</v>
+        <v>194553.09972318442</v>
       </c>
       <c r="E428" s="4">
-        <v>46204</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
@@ -7782,12 +7777,14 @@
       <c r="B429" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C429" s="3"/>
+      <c r="C429" s="3">
+        <v>181931.9978069053</v>
+      </c>
       <c r="D429" s="3">
-        <v>347998.12806845881</v>
+        <v>319950.70281713275</v>
       </c>
       <c r="E429" s="4">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
@@ -7797,12 +7794,14 @@
       <c r="B430" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C430" s="3"/>
+      <c r="C430" s="3">
+        <v>163601.48263622401</v>
+      </c>
       <c r="D430" s="3">
-        <v>363714.15498141845</v>
+        <v>274870.90740838833</v>
       </c>
       <c r="E430" s="4">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
@@ -7812,12 +7811,14 @@
       <c r="B431" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C431" s="3"/>
+      <c r="C431" s="3">
+        <v>121181.49074320766</v>
+      </c>
       <c r="D431" s="3">
-        <v>496546.60061978025</v>
+        <v>325257.22176030773</v>
       </c>
       <c r="E431" s="4">
-        <v>46296</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
@@ -7827,12 +7828,14 @@
       <c r="B432" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C432" s="3"/>
+      <c r="C432" s="3">
+        <v>156205.71780410968</v>
+      </c>
       <c r="D432" s="3">
-        <v>438469.13169096923</v>
+        <v>310175.55260951165</v>
       </c>
       <c r="E432" s="4">
-        <v>46327</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
@@ -7844,10 +7847,10 @@
       </c>
       <c r="C433" s="3"/>
       <c r="D433" s="3">
-        <v>231511.25059344835</v>
+        <v>277375.85079180083</v>
       </c>
       <c r="E433" s="4">
-        <v>46357</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
@@ -7859,10 +7862,10 @@
       </c>
       <c r="C434" s="3"/>
       <c r="D434" s="3">
-        <v>257989.3357702471</v>
+        <v>347998.12806845881</v>
       </c>
       <c r="E434" s="4">
-        <v>46388</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
@@ -7874,10 +7877,10 @@
       </c>
       <c r="C435" s="3"/>
       <c r="D435" s="3">
-        <v>421635.44307790889</v>
+        <v>363714.15498141845</v>
       </c>
       <c r="E435" s="4">
-        <v>46419</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
@@ -7889,10 +7892,10 @@
       </c>
       <c r="C436" s="3"/>
       <c r="D436" s="3">
-        <v>647032.65941540583</v>
+        <v>496546.60061978025</v>
       </c>
       <c r="E436" s="4">
-        <v>46447</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
@@ -7904,10 +7907,10 @@
       </c>
       <c r="C437" s="3"/>
       <c r="D437" s="3">
-        <v>619635.20725139673</v>
+        <v>438469.13169096923</v>
       </c>
       <c r="E437" s="4">
-        <v>46478</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
@@ -7919,10 +7922,10 @@
       </c>
       <c r="C438" s="3"/>
       <c r="D438" s="3">
-        <v>473162.88208968361</v>
+        <v>231511.25059344835</v>
       </c>
       <c r="E438" s="4">
-        <v>46508</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
@@ -7934,10 +7937,10 @@
       </c>
       <c r="C439" s="3"/>
       <c r="D439" s="3">
-        <v>446898.22018258745</v>
+        <v>257989.3357702471</v>
       </c>
       <c r="E439" s="4">
-        <v>46539</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
@@ -7949,10 +7952,10 @@
       </c>
       <c r="C440" s="3"/>
       <c r="D440" s="3">
-        <v>340362.50406525249</v>
+        <v>421635.44307790889</v>
       </c>
       <c r="E440" s="4">
-        <v>46569</v>
+        <v>46419</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
@@ -7964,93 +7967,85 @@
       </c>
       <c r="C441" s="3"/>
       <c r="D441" s="3">
-        <v>200253.18518613285</v>
+        <v>647032.65941540583</v>
       </c>
       <c r="E441" s="4">
-        <v>46600</v>
+        <v>46447</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C442" s="3">
-        <v>92993.94544996148</v>
-      </c>
-      <c r="D442" s="3"/>
+      <c r="C442" s="3"/>
+      <c r="D442" s="3">
+        <v>619635.20725139673</v>
+      </c>
       <c r="E442" s="4">
-        <v>45992</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C443" s="3">
-        <v>119807.97601575598</v>
-      </c>
+      <c r="C443" s="3"/>
       <c r="D443" s="3">
-        <v>119756.7618951456</v>
+        <v>473162.88208968361</v>
       </c>
       <c r="E443" s="4">
-        <v>46023</v>
+        <v>46508</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C444" s="3">
-        <v>167984.15201723264</v>
-      </c>
+      <c r="C444" s="3"/>
       <c r="D444" s="3">
-        <v>166813.9079674992</v>
+        <v>446898.22018258745</v>
       </c>
       <c r="E444" s="4">
-        <v>46054</v>
+        <v>46539</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C445" s="3">
-        <v>215703.30706053553</v>
-      </c>
+      <c r="C445" s="3"/>
       <c r="D445" s="3">
-        <v>215611.0576303672</v>
+        <v>340362.50406525249</v>
       </c>
       <c r="E445" s="4">
-        <v>46082</v>
+        <v>46569</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C446" s="3">
-        <v>178228.674851786</v>
-      </c>
+      <c r="C446" s="3"/>
       <c r="D446" s="3">
-        <v>142629.01857913361</v>
+        <v>200253.18518613285</v>
       </c>
       <c r="E446" s="4">
-        <v>46113</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
@@ -8061,13 +8056,11 @@
         <v>28</v>
       </c>
       <c r="C447" s="3">
-        <v>99010.759076728253</v>
-      </c>
-      <c r="D447" s="3">
-        <v>119963.05646960158</v>
-      </c>
+        <v>92993.94544996148</v>
+      </c>
+      <c r="D447" s="3"/>
       <c r="E447" s="4">
-        <v>46143</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
@@ -8078,13 +8071,13 @@
         <v>28</v>
       </c>
       <c r="C448" s="3">
-        <v>125437.20844000007</v>
+        <v>119807.97601575598</v>
       </c>
       <c r="D448" s="3">
-        <v>212871.68948322959</v>
+        <v>119756.7618951456</v>
       </c>
       <c r="E448" s="4">
-        <v>46174</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
@@ -8094,12 +8087,14 @@
       <c r="B449" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C449" s="3"/>
+      <c r="C449" s="3">
+        <v>167984.15201723264</v>
+      </c>
       <c r="D449" s="3">
-        <v>302854.65848242573</v>
+        <v>166813.9079674992</v>
       </c>
       <c r="E449" s="4">
-        <v>46204</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
@@ -8109,12 +8104,14 @@
       <c r="B450" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C450" s="3"/>
+      <c r="C450" s="3">
+        <v>215703.30706053553</v>
+      </c>
       <c r="D450" s="3">
-        <v>280166.12220368109</v>
+        <v>215611.0576303672</v>
       </c>
       <c r="E450" s="4">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
@@ -8124,12 +8121,14 @@
       <c r="B451" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C451" s="3"/>
+      <c r="C451" s="3">
+        <v>178228.674851786</v>
+      </c>
       <c r="D451" s="3">
-        <v>177590.24392782358</v>
+        <v>142629.01857913361</v>
       </c>
       <c r="E451" s="4">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
@@ -8139,97 +8138,91 @@
       <c r="B452" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C452" s="3"/>
+      <c r="C452" s="3">
+        <v>99010.759076728253</v>
+      </c>
       <c r="D452" s="3">
-        <v>45074.872474069423</v>
+        <v>119963.05646960158</v>
       </c>
       <c r="E452" s="4">
-        <v>46296</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C453" s="3">
-        <v>19584.319258181378</v>
+        <v>125437.20844000007</v>
       </c>
       <c r="D453" s="3">
-        <v>19584.319258181375</v>
+        <v>212871.68948322959</v>
       </c>
       <c r="E453" s="4">
-        <v>45170</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C454" s="3">
-        <v>33157.46608977556</v>
-      </c>
+      <c r="C454" s="3"/>
       <c r="D454" s="3">
-        <v>33201.363937808812</v>
+        <v>302854.65848242573</v>
       </c>
       <c r="E454" s="4">
-        <v>45200</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C455" s="3">
-        <v>51487.02341419139</v>
-      </c>
+      <c r="C455" s="3"/>
       <c r="D455" s="3">
-        <v>51487.02341419139</v>
+        <v>280166.12220368109</v>
       </c>
       <c r="E455" s="4">
-        <v>45231</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C456" s="3">
-        <v>29982.972168923607</v>
-      </c>
+      <c r="C456" s="3"/>
       <c r="D456" s="3">
-        <v>29982.972168923607</v>
+        <v>177590.24392782358</v>
       </c>
       <c r="E456" s="4">
-        <v>45261</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C457" s="3">
-        <v>44957.664924564924</v>
-      </c>
+      <c r="C457" s="3"/>
       <c r="D457" s="3">
-        <v>44957.664924564924</v>
+        <v>45074.872474069423</v>
       </c>
       <c r="E457" s="4">
-        <v>45292</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
@@ -8240,13 +8233,13 @@
         <v>28</v>
       </c>
       <c r="C458" s="3">
-        <v>21535.88354184922</v>
+        <v>19584.319258181378</v>
       </c>
       <c r="D458" s="3">
-        <v>21535.88354184922</v>
+        <v>19584.319258181375</v>
       </c>
       <c r="E458" s="4">
-        <v>45323</v>
+        <v>45170</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
@@ -8257,13 +8250,13 @@
         <v>28</v>
       </c>
       <c r="C459" s="3">
-        <v>22093.922811214816</v>
+        <v>33157.46608977556</v>
       </c>
       <c r="D459" s="3">
-        <v>22093.922811214808</v>
+        <v>33201.363937808812</v>
       </c>
       <c r="E459" s="4">
-        <v>45352</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
@@ -8274,13 +8267,13 @@
         <v>28</v>
       </c>
       <c r="C460" s="3">
-        <v>46306.77660016506</v>
+        <v>51487.02341419139</v>
       </c>
       <c r="D460" s="3">
-        <v>46306.776600165053</v>
+        <v>51487.02341419139</v>
       </c>
       <c r="E460" s="4">
-        <v>45383</v>
+        <v>45231</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
@@ -8291,13 +8284,13 @@
         <v>28</v>
       </c>
       <c r="C461" s="3">
-        <v>47898.044578191897</v>
+        <v>29982.972168923607</v>
       </c>
       <c r="D461" s="3">
-        <v>47898.04457819189</v>
+        <v>29982.972168923607</v>
       </c>
       <c r="E461" s="4">
-        <v>45413</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
@@ -8308,13 +8301,13 @@
         <v>28</v>
       </c>
       <c r="C462" s="3">
-        <v>40326.864942313507</v>
+        <v>44957.664924564924</v>
       </c>
       <c r="D462" s="3">
-        <v>40326.864942313514</v>
+        <v>44957.664924564924</v>
       </c>
       <c r="E462" s="4">
-        <v>45444</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
@@ -8325,13 +8318,13 @@
         <v>28</v>
       </c>
       <c r="C463" s="3">
-        <v>57802.291959106376</v>
+        <v>21535.88354184922</v>
       </c>
       <c r="D463" s="3">
-        <v>57802.291959106369</v>
+        <v>21535.88354184922</v>
       </c>
       <c r="E463" s="4">
-        <v>45474</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
@@ -8342,13 +8335,13 @@
         <v>28</v>
       </c>
       <c r="C464" s="3">
-        <v>88534.714708509302</v>
+        <v>22093.922811214816</v>
       </c>
       <c r="D464" s="3">
-        <v>88534.714708509287</v>
+        <v>22093.922811214808</v>
       </c>
       <c r="E464" s="4">
-        <v>45505</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
@@ -8359,13 +8352,13 @@
         <v>28</v>
       </c>
       <c r="C465" s="3">
-        <v>47272.172344710641</v>
+        <v>46306.77660016506</v>
       </c>
       <c r="D465" s="3">
-        <v>47272.172344710641</v>
+        <v>46306.776600165053</v>
       </c>
       <c r="E465" s="4">
-        <v>45536</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
@@ -8376,13 +8369,13 @@
         <v>28</v>
       </c>
       <c r="C466" s="3">
-        <v>107496.49013155067</v>
+        <v>47898.044578191897</v>
       </c>
       <c r="D466" s="3">
-        <v>107496.49013155069</v>
+        <v>47898.04457819189</v>
       </c>
       <c r="E466" s="4">
-        <v>45566</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
@@ -8393,13 +8386,13 @@
         <v>28</v>
       </c>
       <c r="C467" s="3">
-        <v>72088.000288274052</v>
+        <v>40326.864942313507</v>
       </c>
       <c r="D467" s="3">
-        <v>72088.000288274023</v>
+        <v>40326.864942313514</v>
       </c>
       <c r="E467" s="4">
-        <v>45597</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
@@ -8410,13 +8403,13 @@
         <v>28</v>
       </c>
       <c r="C468" s="3">
-        <v>59843.837644577608</v>
+        <v>57802.291959106376</v>
       </c>
       <c r="D468" s="3">
-        <v>59843.837644577608</v>
+        <v>57802.291959106369</v>
       </c>
       <c r="E468" s="4">
-        <v>45627</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
@@ -8427,13 +8420,13 @@
         <v>28</v>
       </c>
       <c r="C469" s="3">
-        <v>92206.68100426592</v>
+        <v>88534.714708509302</v>
       </c>
       <c r="D469" s="3">
-        <v>92206.681004265905</v>
+        <v>88534.714708509287</v>
       </c>
       <c r="E469" s="4">
-        <v>45658</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
@@ -8444,13 +8437,13 @@
         <v>28</v>
       </c>
       <c r="C470" s="3">
-        <v>67829.975967821461</v>
+        <v>47272.172344710641</v>
       </c>
       <c r="D470" s="3">
-        <v>67829.975967821447</v>
+        <v>47272.172344710641</v>
       </c>
       <c r="E470" s="4">
-        <v>45689</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
@@ -8461,13 +8454,13 @@
         <v>28</v>
       </c>
       <c r="C471" s="3">
-        <v>104933.01920021485</v>
+        <v>107496.49013155067</v>
       </c>
       <c r="D471" s="3">
-        <v>104933.01920021485</v>
+        <v>107496.49013155069</v>
       </c>
       <c r="E471" s="4">
-        <v>45717</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
@@ -8478,13 +8471,13 @@
         <v>28</v>
       </c>
       <c r="C472" s="3">
-        <v>103936.34990262899</v>
+        <v>72088.000288274052</v>
       </c>
       <c r="D472" s="3">
-        <v>105005.06945063527</v>
+        <v>72088.000288274023</v>
       </c>
       <c r="E472" s="4">
-        <v>45748</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
@@ -8495,13 +8488,13 @@
         <v>28</v>
       </c>
       <c r="C473" s="3">
-        <v>100847.41125942138</v>
+        <v>59843.837644577608</v>
       </c>
       <c r="D473" s="3">
-        <v>99734.793863381827</v>
+        <v>59843.837644577608</v>
       </c>
       <c r="E473" s="4">
-        <v>45778</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
@@ -8512,13 +8505,13 @@
         <v>28</v>
       </c>
       <c r="C474" s="3">
-        <v>79529.460583435008</v>
+        <v>92206.68100426592</v>
       </c>
       <c r="D474" s="3">
-        <v>79529.460583435008</v>
+        <v>92206.681004265905</v>
       </c>
       <c r="E474" s="4">
-        <v>45809</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
@@ -8529,13 +8522,13 @@
         <v>28</v>
       </c>
       <c r="C475" s="3">
-        <v>77436.813221762583</v>
+        <v>67829.975967821461</v>
       </c>
       <c r="D475" s="3">
-        <v>77436.813221762583</v>
+        <v>67829.975967821447</v>
       </c>
       <c r="E475" s="4">
-        <v>45839</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
@@ -8546,13 +8539,13 @@
         <v>28</v>
       </c>
       <c r="C476" s="3">
-        <v>91938.98020487951</v>
+        <v>104933.01920021485</v>
       </c>
       <c r="D476" s="3">
-        <v>91938.98020487951</v>
+        <v>104933.01920021485</v>
       </c>
       <c r="E476" s="4">
-        <v>45870</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
@@ -8563,13 +8556,13 @@
         <v>28</v>
       </c>
       <c r="C477" s="3">
-        <v>79385.948344763252</v>
+        <v>103936.34990262899</v>
       </c>
       <c r="D477" s="3">
-        <v>79385.948344763252</v>
+        <v>105005.06945063527</v>
       </c>
       <c r="E477" s="4">
-        <v>45901</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
@@ -8580,13 +8573,13 @@
         <v>28</v>
       </c>
       <c r="C478" s="3">
-        <v>26482.069378111279</v>
+        <v>100847.41125942138</v>
       </c>
       <c r="D478" s="3">
-        <v>26482.069378111268</v>
+        <v>99734.793863381827</v>
       </c>
       <c r="E478" s="4">
-        <v>45931</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
@@ -8597,13 +8590,13 @@
         <v>28</v>
       </c>
       <c r="C479" s="3">
-        <v>12711.39525591745</v>
+        <v>79529.460583435008</v>
       </c>
       <c r="D479" s="3">
-        <v>12711.395255917352</v>
+        <v>79529.460583435008</v>
       </c>
       <c r="E479" s="4">
-        <v>45962</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
@@ -8614,88 +8607,98 @@
         <v>28</v>
       </c>
       <c r="C480" s="3">
-        <v>4018.5517036805713</v>
+        <v>77436.813221762583</v>
       </c>
       <c r="D480" s="3">
-        <v>4018.5517036805718</v>
+        <v>77436.813221762583</v>
       </c>
       <c r="E480" s="4">
-        <v>45992</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C481" s="3">
-        <v>69023</v>
-      </c>
-      <c r="D481" s="3"/>
+        <v>91938.98020487951</v>
+      </c>
+      <c r="D481" s="3">
+        <v>91938.98020487951</v>
+      </c>
       <c r="E481" s="4">
-        <v>44805</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C482" s="3">
-        <v>69023</v>
-      </c>
-      <c r="D482" s="3"/>
+        <v>79385.948344763252</v>
+      </c>
+      <c r="D482" s="3">
+        <v>79385.948344763252</v>
+      </c>
       <c r="E482" s="4">
-        <v>44835</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C483" s="3">
-        <v>69023</v>
-      </c>
-      <c r="D483" s="3"/>
+        <v>26482.069378111279</v>
+      </c>
+      <c r="D483" s="3">
+        <v>26482.069378111268</v>
+      </c>
       <c r="E483" s="4">
-        <v>44866</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C484" s="3">
-        <v>69023</v>
-      </c>
-      <c r="D484" s="3"/>
+        <v>12711.39525591745</v>
+      </c>
+      <c r="D484" s="3">
+        <v>12711.395255917352</v>
+      </c>
       <c r="E484" s="4">
-        <v>44896</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C485" s="3">
-        <v>69023</v>
-      </c>
-      <c r="D485" s="3"/>
+        <v>4018.5517036805713</v>
+      </c>
+      <c r="D485" s="3">
+        <v>4018.5517036805718</v>
+      </c>
       <c r="E485" s="4">
-        <v>44927</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
@@ -8710,7 +8713,7 @@
       </c>
       <c r="D486" s="3"/>
       <c r="E486" s="4">
-        <v>44958</v>
+        <v>44805</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
@@ -8725,7 +8728,7 @@
       </c>
       <c r="D487" s="3"/>
       <c r="E487" s="4">
-        <v>44986</v>
+        <v>44835</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
@@ -8740,7 +8743,7 @@
       </c>
       <c r="D488" s="3"/>
       <c r="E488" s="4">
-        <v>45017</v>
+        <v>44866</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
@@ -8755,7 +8758,7 @@
       </c>
       <c r="D489" s="3"/>
       <c r="E489" s="4">
-        <v>45047</v>
+        <v>44896</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
@@ -8770,7 +8773,7 @@
       </c>
       <c r="D490" s="3"/>
       <c r="E490" s="4">
-        <v>45078</v>
+        <v>44927</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
@@ -8785,7 +8788,7 @@
       </c>
       <c r="D491" s="3"/>
       <c r="E491" s="4">
-        <v>45108</v>
+        <v>44958</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
@@ -8800,7 +8803,7 @@
       </c>
       <c r="D492" s="3"/>
       <c r="E492" s="4">
-        <v>45139</v>
+        <v>44986</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
@@ -8815,7 +8818,7 @@
       </c>
       <c r="D493" s="3"/>
       <c r="E493" s="4">
-        <v>45170</v>
+        <v>45017</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
@@ -8830,7 +8833,7 @@
       </c>
       <c r="D494" s="3"/>
       <c r="E494" s="4">
-        <v>45200</v>
+        <v>45047</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
@@ -8845,7 +8848,7 @@
       </c>
       <c r="D495" s="3"/>
       <c r="E495" s="4">
-        <v>45231</v>
+        <v>45078</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
@@ -8860,7 +8863,7 @@
       </c>
       <c r="D496" s="3"/>
       <c r="E496" s="4">
-        <v>45261</v>
+        <v>45108</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
@@ -8875,7 +8878,7 @@
       </c>
       <c r="D497" s="3"/>
       <c r="E497" s="4">
-        <v>45292</v>
+        <v>45139</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
@@ -8890,7 +8893,7 @@
       </c>
       <c r="D498" s="3"/>
       <c r="E498" s="4">
-        <v>45323</v>
+        <v>45170</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
@@ -8905,7 +8908,7 @@
       </c>
       <c r="D499" s="3"/>
       <c r="E499" s="4">
-        <v>45352</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
@@ -8920,7 +8923,7 @@
       </c>
       <c r="D500" s="3"/>
       <c r="E500" s="4">
-        <v>45383</v>
+        <v>45231</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
@@ -8935,7 +8938,7 @@
       </c>
       <c r="D501" s="3"/>
       <c r="E501" s="4">
-        <v>45413</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
@@ -8950,7 +8953,7 @@
       </c>
       <c r="D502" s="3"/>
       <c r="E502" s="4">
-        <v>45444</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -8965,7 +8968,7 @@
       </c>
       <c r="D503" s="3"/>
       <c r="E503" s="4">
-        <v>45474</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
@@ -8980,7 +8983,7 @@
       </c>
       <c r="D504" s="3"/>
       <c r="E504" s="4">
-        <v>45505</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
@@ -8995,7 +8998,7 @@
       </c>
       <c r="D505" s="3"/>
       <c r="E505" s="4">
-        <v>45536</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -9010,7 +9013,7 @@
       </c>
       <c r="D506" s="3"/>
       <c r="E506" s="4">
-        <v>45566</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
@@ -9025,7 +9028,7 @@
       </c>
       <c r="D507" s="3"/>
       <c r="E507" s="4">
-        <v>45597</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
@@ -9040,7 +9043,7 @@
       </c>
       <c r="D508" s="3"/>
       <c r="E508" s="4">
-        <v>45627</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
@@ -9055,7 +9058,7 @@
       </c>
       <c r="D509" s="3"/>
       <c r="E509" s="4">
-        <v>45658</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
@@ -9070,7 +9073,7 @@
       </c>
       <c r="D510" s="3"/>
       <c r="E510" s="4">
-        <v>45689</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
@@ -9085,7 +9088,7 @@
       </c>
       <c r="D511" s="3"/>
       <c r="E511" s="4">
-        <v>45717</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
@@ -9100,7 +9103,7 @@
       </c>
       <c r="D512" s="3"/>
       <c r="E512" s="4">
-        <v>45748</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
@@ -9111,11 +9114,11 @@
         <v>28</v>
       </c>
       <c r="C513" s="3">
-        <v>0</v>
+        <v>69023</v>
       </c>
       <c r="D513" s="3"/>
       <c r="E513" s="4">
-        <v>45778</v>
+        <v>45627</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
@@ -9126,11 +9129,11 @@
         <v>28</v>
       </c>
       <c r="C514" s="3">
-        <v>0</v>
+        <v>69023</v>
       </c>
       <c r="D514" s="3"/>
       <c r="E514" s="4">
-        <v>45809</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
@@ -9141,11 +9144,11 @@
         <v>28</v>
       </c>
       <c r="C515" s="3">
-        <v>38988.409999999996</v>
+        <v>69023</v>
       </c>
       <c r="D515" s="3"/>
       <c r="E515" s="4">
-        <v>45839</v>
+        <v>45689</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
@@ -9156,11 +9159,11 @@
         <v>28</v>
       </c>
       <c r="C516" s="3">
-        <v>0</v>
+        <v>69023</v>
       </c>
       <c r="D516" s="3"/>
       <c r="E516" s="4">
-        <v>45870</v>
+        <v>45717</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
@@ -9171,11 +9174,11 @@
         <v>28</v>
       </c>
       <c r="C517" s="3">
-        <v>0</v>
+        <v>69023</v>
       </c>
       <c r="D517" s="3"/>
       <c r="E517" s="4">
-        <v>45901</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
@@ -9190,7 +9193,7 @@
       </c>
       <c r="D518" s="3"/>
       <c r="E518" s="4">
-        <v>45931</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
@@ -9205,7 +9208,7 @@
       </c>
       <c r="D519" s="3"/>
       <c r="E519" s="4">
-        <v>45962</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
@@ -9216,11 +9219,11 @@
         <v>28</v>
       </c>
       <c r="C520" s="3">
-        <v>0</v>
+        <v>38988.409999999996</v>
       </c>
       <c r="D520" s="3"/>
       <c r="E520" s="4">
-        <v>45992</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
@@ -9235,7 +9238,7 @@
       </c>
       <c r="D521" s="3"/>
       <c r="E521" s="4">
-        <v>46023</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
@@ -9250,7 +9253,7 @@
       </c>
       <c r="D522" s="3"/>
       <c r="E522" s="4">
-        <v>46054</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
@@ -9265,7 +9268,7 @@
       </c>
       <c r="D523" s="3"/>
       <c r="E523" s="4">
-        <v>46082</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
@@ -9280,7 +9283,7 @@
       </c>
       <c r="D524" s="3"/>
       <c r="E524" s="4">
-        <v>46113</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
@@ -9291,96 +9294,86 @@
         <v>28</v>
       </c>
       <c r="C525" s="3">
-        <v>1821264</v>
+        <v>0</v>
       </c>
       <c r="D525" s="3"/>
       <c r="E525" s="4">
-        <v>46143</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C526" s="3">
-        <v>118649.512</v>
-      </c>
-      <c r="D526" s="3">
-        <v>118649.512</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D526" s="3"/>
       <c r="E526" s="4">
-        <v>44621</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C527" s="3">
-        <v>41389.364999999998</v>
-      </c>
-      <c r="D527" s="3">
-        <v>41389.364999999998</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D527" s="3"/>
       <c r="E527" s="4">
-        <v>44652</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C528" s="3">
-        <v>33111.491999999998</v>
-      </c>
-      <c r="D528" s="3">
-        <v>33111.491999999998</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D528" s="3"/>
       <c r="E528" s="4">
-        <v>44682</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C529" s="3">
-        <v>35870.783000000003</v>
-      </c>
-      <c r="D529" s="3">
-        <v>35870.783000000003</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D529" s="3"/>
       <c r="E529" s="4">
-        <v>44713</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C530" s="3">
-        <v>46907.946000000004</v>
-      </c>
-      <c r="D530" s="3">
-        <v>46907.946000000004</v>
-      </c>
+        <v>1821264</v>
+      </c>
+      <c r="D530" s="3"/>
       <c r="E530" s="4">
-        <v>44743</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
@@ -9391,13 +9384,13 @@
         <v>28</v>
       </c>
       <c r="C531" s="3">
-        <v>27592.91</v>
+        <v>118649.512</v>
       </c>
       <c r="D531" s="3">
-        <v>27592.91</v>
+        <v>118649.512</v>
       </c>
       <c r="E531" s="4">
-        <v>44774</v>
+        <v>44621</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
@@ -9408,13 +9401,13 @@
         <v>28</v>
       </c>
       <c r="C532" s="3">
-        <v>38906.002999999997</v>
+        <v>41389.364999999998</v>
       </c>
       <c r="D532" s="3">
-        <v>38906.002999999997</v>
+        <v>41389.364999999998</v>
       </c>
       <c r="E532" s="4">
-        <v>44805</v>
+        <v>44652</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
@@ -9425,13 +9418,13 @@
         <v>28</v>
       </c>
       <c r="C533" s="3">
-        <v>77536.076000000001</v>
+        <v>33111.491999999998</v>
       </c>
       <c r="D533" s="3">
-        <v>77536.076000000001</v>
+        <v>33111.491999999998</v>
       </c>
       <c r="E533" s="4">
-        <v>44835</v>
+        <v>44682</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -9442,13 +9435,13 @@
         <v>28</v>
       </c>
       <c r="C534" s="3">
-        <v>84986.161999999997</v>
+        <v>35870.783000000003</v>
       </c>
       <c r="D534" s="3">
-        <v>84986.161999999997</v>
+        <v>35870.783000000003</v>
       </c>
       <c r="E534" s="4">
-        <v>44866</v>
+        <v>44713</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
@@ -9459,13 +9452,13 @@
         <v>28</v>
       </c>
       <c r="C535" s="3">
-        <v>97140.87</v>
+        <v>46907.946000000004</v>
       </c>
       <c r="D535" s="3">
-        <v>97140.87</v>
+        <v>46907.946000000004</v>
       </c>
       <c r="E535" s="4">
-        <v>44896</v>
+        <v>44743</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
@@ -9476,13 +9469,13 @@
         <v>28</v>
       </c>
       <c r="C536" s="3">
-        <v>134653.4</v>
+        <v>27592.91</v>
       </c>
       <c r="D536" s="3">
-        <v>134653.4</v>
+        <v>27592.91</v>
       </c>
       <c r="E536" s="4">
-        <v>44927</v>
+        <v>44774</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
@@ -9493,13 +9486,13 @@
         <v>28</v>
       </c>
       <c r="C537" s="3">
-        <v>144034.99</v>
+        <v>38906.002999999997</v>
       </c>
       <c r="D537" s="3">
-        <v>144034.99</v>
+        <v>38906.002999999997</v>
       </c>
       <c r="E537" s="4">
-        <v>44958</v>
+        <v>44805</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
@@ -9510,13 +9503,13 @@
         <v>28</v>
       </c>
       <c r="C538" s="3">
-        <v>181009.49</v>
+        <v>77536.076000000001</v>
       </c>
       <c r="D538" s="3">
-        <v>181009.49</v>
+        <v>77536.076000000001</v>
       </c>
       <c r="E538" s="4">
-        <v>44986</v>
+        <v>44835</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
@@ -9527,13 +9520,13 @@
         <v>28</v>
       </c>
       <c r="C539" s="3">
-        <v>126108.61121657665</v>
+        <v>84986.161999999997</v>
       </c>
       <c r="D539" s="3">
-        <v>122788.44828959998</v>
+        <v>84986.161999999997</v>
       </c>
       <c r="E539" s="4">
-        <v>45017</v>
+        <v>44866</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
@@ -9544,13 +9537,13 @@
         <v>28</v>
       </c>
       <c r="C540" s="3">
-        <v>108060.77429213714</v>
+        <v>97140.87</v>
       </c>
       <c r="D540" s="3">
-        <v>107060.48974463998</v>
+        <v>97140.87</v>
       </c>
       <c r="E540" s="4">
-        <v>45047</v>
+        <v>44896</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
@@ -9561,13 +9554,13 @@
         <v>28</v>
       </c>
       <c r="C541" s="3">
-        <v>103736.89783644832</v>
+        <v>134653.4</v>
       </c>
       <c r="D541" s="3">
-        <v>102369.69509087999</v>
+        <v>134653.4</v>
       </c>
       <c r="E541" s="4">
-        <v>45078</v>
+        <v>44927</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
@@ -9578,13 +9571,13 @@
         <v>28</v>
       </c>
       <c r="C542" s="3">
-        <v>127453.76846242594</v>
+        <v>144034.99</v>
       </c>
       <c r="D542" s="3">
-        <v>124719.95197055998</v>
+        <v>144034.99</v>
       </c>
       <c r="E542" s="4">
-        <v>45108</v>
+        <v>44958</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
@@ -9595,13 +9588,13 @@
         <v>28</v>
       </c>
       <c r="C543" s="3">
-        <v>128371.71516401674</v>
+        <v>181009.49</v>
       </c>
       <c r="D543" s="3">
-        <v>125547.73926240001</v>
+        <v>181009.49</v>
       </c>
       <c r="E543" s="4">
-        <v>45139</v>
+        <v>44986</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
@@ -9612,13 +9605,13 @@
         <v>28</v>
       </c>
       <c r="C544" s="3">
-        <v>126702.7345474715</v>
+        <v>126108.61121657665</v>
       </c>
       <c r="D544" s="3">
-        <v>123616.23558144001</v>
+        <v>122788.44828959998</v>
       </c>
       <c r="E544" s="4">
-        <v>45170</v>
+        <v>45017</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
@@ -9629,13 +9622,13 @@
         <v>28</v>
       </c>
       <c r="C545" s="3">
-        <v>122469.50334718848</v>
+        <v>108060.77429213714</v>
       </c>
       <c r="D545" s="3">
-        <v>119201.37002495999</v>
+        <v>107060.48974463998</v>
       </c>
       <c r="E545" s="4">
-        <v>45200</v>
+        <v>45047</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
@@ -9646,13 +9639,13 @@
         <v>28</v>
       </c>
       <c r="C546" s="3">
-        <v>136351.8822857202</v>
+        <v>103736.89783644832</v>
       </c>
       <c r="D546" s="3">
-        <v>132445.96669439998</v>
+        <v>102369.69509087999</v>
       </c>
       <c r="E546" s="4">
-        <v>45231</v>
+        <v>45078</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
@@ -9663,13 +9656,13 @@
         <v>28</v>
       </c>
       <c r="C547" s="3">
-        <v>181700.25508377992</v>
+        <v>127453.76846242594</v>
       </c>
       <c r="D547" s="3">
-        <v>176318.69316191997</v>
+        <v>124719.95197055998</v>
       </c>
       <c r="E547" s="4">
-        <v>45261</v>
+        <v>45108</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
@@ -9680,13 +9673,13 @@
         <v>28</v>
       </c>
       <c r="C548" s="3">
-        <v>210966.46738108408</v>
+        <v>128371.71516401674</v>
       </c>
       <c r="D548" s="3">
-        <v>204187.53198719997</v>
+        <v>125547.73926240001</v>
       </c>
       <c r="E548" s="4">
-        <v>45292</v>
+        <v>45139</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
@@ -9697,13 +9690,13 @@
         <v>28</v>
       </c>
       <c r="C549" s="3">
-        <v>206311.08591475722</v>
+        <v>126702.7345474715</v>
       </c>
       <c r="D549" s="3">
-        <v>199220.80823615997</v>
+        <v>123616.23558144001</v>
       </c>
       <c r="E549" s="4">
-        <v>45323</v>
+        <v>45170</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
@@ -9714,13 +9707,13 @@
         <v>28</v>
       </c>
       <c r="C550" s="3">
-        <v>106514.37928003953</v>
+        <v>122469.50334718848</v>
       </c>
       <c r="D550" s="3">
-        <v>102645.62418815999</v>
+        <v>119201.37002495999</v>
       </c>
       <c r="E550" s="4">
-        <v>45352</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
@@ -9731,98 +9724,98 @@
         <v>28</v>
       </c>
       <c r="C551" s="3">
-        <v>59685.735913831784</v>
+        <v>136351.8822857202</v>
       </c>
       <c r="D551" s="3">
-        <v>57379.42208999861</v>
+        <v>132445.96669439998</v>
       </c>
       <c r="E551" s="4">
-        <v>45383</v>
+        <v>45231</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C552" s="3">
-        <v>33562.230417420651</v>
+        <v>181700.25508377992</v>
       </c>
       <c r="D552" s="3">
-        <v>33543.402508702398</v>
+        <v>176318.69316191997</v>
       </c>
       <c r="E552" s="4">
-        <v>45139</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C553" s="3">
-        <v>11630.763264592404</v>
+        <v>210966.46738108408</v>
       </c>
       <c r="D553" s="3">
-        <v>11596.167719302701</v>
+        <v>204187.53198719997</v>
       </c>
       <c r="E553" s="4">
-        <v>45170</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C554" s="3">
-        <v>51295.182339413339</v>
+        <v>206311.08591475722</v>
       </c>
       <c r="D554" s="3">
-        <v>51020.723661475065</v>
+        <v>199220.80823615997</v>
       </c>
       <c r="E554" s="4">
-        <v>45200</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C555" s="3">
-        <v>62911.355705869886</v>
+        <v>106514.37928003953</v>
       </c>
       <c r="D555" s="3">
-        <v>62448.698263129692</v>
+        <v>102645.62418815999</v>
       </c>
       <c r="E555" s="4">
-        <v>45231</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C556" s="3">
-        <v>74844.872082093367</v>
+        <v>59685.735913831784</v>
       </c>
       <c r="D556" s="3">
-        <v>74220.114109500981</v>
+        <v>57379.42208999861</v>
       </c>
       <c r="E556" s="4">
-        <v>45261</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
@@ -9833,13 +9826,13 @@
         <v>28</v>
       </c>
       <c r="C557" s="3">
-        <v>62392.907094820497</v>
+        <v>33562.230417420651</v>
       </c>
       <c r="D557" s="3">
-        <v>61711.734980167465</v>
+        <v>33543.402508702398</v>
       </c>
       <c r="E557" s="4">
-        <v>45292</v>
+        <v>45139</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -9850,13 +9843,13 @@
         <v>28</v>
       </c>
       <c r="C558" s="3">
-        <v>41443.802425811758</v>
+        <v>11630.763264592404</v>
       </c>
       <c r="D558" s="3">
-        <v>40896.71955015479</v>
+        <v>11596.167719302701</v>
       </c>
       <c r="E558" s="4">
-        <v>45323</v>
+        <v>45170</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
@@ -9867,13 +9860,13 @@
         <v>28</v>
       </c>
       <c r="C559" s="3">
-        <v>50248.450154161663</v>
+        <v>51295.182339413339</v>
       </c>
       <c r="D559" s="3">
-        <v>49484.776855388613</v>
+        <v>51020.723661475065</v>
       </c>
       <c r="E559" s="4">
-        <v>45352</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
@@ -9884,13 +9877,13 @@
         <v>28</v>
       </c>
       <c r="C560" s="3">
-        <v>19609.602990791438</v>
+        <v>62911.355705869886</v>
       </c>
       <c r="D560" s="3">
-        <v>19265.095400911854</v>
+        <v>62448.698263129692</v>
       </c>
       <c r="E560" s="4">
-        <v>45383</v>
+        <v>45231</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
@@ -9901,13 +9894,13 @@
         <v>28</v>
       </c>
       <c r="C561" s="3">
-        <v>53861.898356575533</v>
+        <v>74844.872082093367</v>
       </c>
       <c r="D561" s="3">
-        <v>52699.3449939774</v>
+        <v>74220.114109500981</v>
       </c>
       <c r="E561" s="4">
-        <v>45413</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
@@ -9918,13 +9911,13 @@
         <v>28</v>
       </c>
       <c r="C562" s="3">
-        <v>58634.619720868533</v>
+        <v>62392.907094820497</v>
       </c>
       <c r="D562" s="3">
-        <v>57033.187248730632</v>
+        <v>61711.734980167465</v>
       </c>
       <c r="E562" s="4">
-        <v>45444</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
@@ -9935,98 +9928,98 @@
         <v>28</v>
       </c>
       <c r="C563" s="3">
-        <v>41927.913518720656</v>
+        <v>41443.802425811758</v>
       </c>
       <c r="D563" s="3">
-        <v>40406.282020558407</v>
+        <v>40896.71955015479</v>
       </c>
       <c r="E563" s="4">
-        <v>45474</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C564" s="3">
-        <v>194565.88700000002</v>
+        <v>50248.450154161663</v>
       </c>
       <c r="D564" s="3">
-        <v>194565.88700000002</v>
+        <v>49484.776855388613</v>
       </c>
       <c r="E564" s="4">
-        <v>45017</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C565" s="3">
-        <v>194565.88700000002</v>
+        <v>19609.602990791438</v>
       </c>
       <c r="D565" s="3">
-        <v>194565.88700000002</v>
+        <v>19265.095400911854</v>
       </c>
       <c r="E565" s="4">
-        <v>45047</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C566" s="3">
-        <v>200065.89</v>
+        <v>53861.898356575533</v>
       </c>
       <c r="D566" s="3">
-        <v>200065.89</v>
+        <v>52699.3449939774</v>
       </c>
       <c r="E566" s="4">
-        <v>45078</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C567" s="3">
-        <v>200065.89</v>
+        <v>58634.619720868533</v>
       </c>
       <c r="D567" s="3">
-        <v>200065.89</v>
+        <v>57033.187248730632</v>
       </c>
       <c r="E567" s="4">
-        <v>45108</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C568" s="3">
-        <v>200065.89</v>
+        <v>41927.913518720656</v>
       </c>
       <c r="D568" s="3">
-        <v>200065.89</v>
+        <v>40406.282020558407</v>
       </c>
       <c r="E568" s="4">
-        <v>45139</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -10037,13 +10030,13 @@
         <v>28</v>
       </c>
       <c r="C569" s="3">
-        <v>200065.89</v>
+        <v>194565.88700000002</v>
       </c>
       <c r="D569" s="3">
-        <v>200065.89</v>
+        <v>194565.88700000002</v>
       </c>
       <c r="E569" s="4">
-        <v>45170</v>
+        <v>45017</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
@@ -10054,13 +10047,13 @@
         <v>28</v>
       </c>
       <c r="C570" s="3">
-        <v>200065.89</v>
+        <v>194565.88700000002</v>
       </c>
       <c r="D570" s="3">
-        <v>200065.89</v>
+        <v>194565.88700000002</v>
       </c>
       <c r="E570" s="4">
-        <v>45200</v>
+        <v>45047</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
@@ -10077,7 +10070,7 @@
         <v>200065.89</v>
       </c>
       <c r="E571" s="4">
-        <v>45231</v>
+        <v>45078</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
@@ -10094,7 +10087,7 @@
         <v>200065.89</v>
       </c>
       <c r="E572" s="4">
-        <v>45261</v>
+        <v>45108</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
@@ -10111,7 +10104,7 @@
         <v>200065.89</v>
       </c>
       <c r="E573" s="4">
-        <v>45292</v>
+        <v>45139</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
@@ -10122,13 +10115,13 @@
         <v>28</v>
       </c>
       <c r="C574" s="3">
-        <v>72753.84</v>
+        <v>200065.89</v>
       </c>
       <c r="D574" s="3">
-        <v>72753.84</v>
+        <v>200065.89</v>
       </c>
       <c r="E574" s="4">
-        <v>45323</v>
+        <v>45170</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
@@ -10139,13 +10132,13 @@
         <v>28</v>
       </c>
       <c r="C575" s="3">
-        <v>150468.19</v>
+        <v>200065.89</v>
       </c>
       <c r="D575" s="3">
-        <v>150468.19</v>
+        <v>200065.89</v>
       </c>
       <c r="E575" s="4">
-        <v>45352</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -10156,13 +10149,13 @@
         <v>28</v>
       </c>
       <c r="C576" s="3">
-        <v>150468.19</v>
+        <v>200065.89</v>
       </c>
       <c r="D576" s="3">
-        <v>150468.19</v>
+        <v>200065.89</v>
       </c>
       <c r="E576" s="4">
-        <v>45383</v>
+        <v>45231</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
@@ -10173,13 +10166,13 @@
         <v>28</v>
       </c>
       <c r="C577" s="3">
-        <v>150468.19</v>
+        <v>200065.89</v>
       </c>
       <c r="D577" s="3">
-        <v>150468.19</v>
+        <v>200065.89</v>
       </c>
       <c r="E577" s="4">
-        <v>45413</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
@@ -10190,13 +10183,13 @@
         <v>28</v>
       </c>
       <c r="C578" s="3">
-        <v>66053.240000000005</v>
+        <v>200065.89</v>
       </c>
       <c r="D578" s="3">
-        <v>66053.240000000005</v>
+        <v>200065.89</v>
       </c>
       <c r="E578" s="4">
-        <v>45444</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
@@ -10207,13 +10200,13 @@
         <v>28</v>
       </c>
       <c r="C579" s="3">
-        <v>67791.179999999993</v>
+        <v>72753.84</v>
       </c>
       <c r="D579" s="3">
-        <v>67791.179999999993</v>
+        <v>72753.84</v>
       </c>
       <c r="E579" s="4">
-        <v>45474</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
@@ -10224,98 +10217,98 @@
         <v>28</v>
       </c>
       <c r="C580" s="3">
-        <v>67791.179999999993</v>
+        <v>150468.19</v>
       </c>
       <c r="D580" s="3">
-        <v>67791.179999999993</v>
+        <v>150468.19</v>
       </c>
       <c r="E580" s="4">
-        <v>45505</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C581" s="3">
-        <v>99237.831999999995</v>
+        <v>150468.19</v>
       </c>
       <c r="D581" s="3">
-        <v>99237.831999999995</v>
+        <v>150468.19</v>
       </c>
       <c r="E581" s="4">
-        <v>44470</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C582" s="3">
-        <v>66158.554999999993</v>
+        <v>150468.19</v>
       </c>
       <c r="D582" s="3">
-        <v>66158.554999999993</v>
+        <v>150468.19</v>
       </c>
       <c r="E582" s="4">
-        <v>44501</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C583" s="3">
-        <v>43257.516000000003</v>
+        <v>66053.240000000005</v>
       </c>
       <c r="D583" s="3">
-        <v>43257.516000000003</v>
+        <v>66053.240000000005</v>
       </c>
       <c r="E583" s="4">
-        <v>44531</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C584" s="3">
-        <v>33079.277000000002</v>
+        <v>67791.179999999993</v>
       </c>
       <c r="D584" s="3">
-        <v>33079.277000000002</v>
+        <v>67791.179999999993</v>
       </c>
       <c r="E584" s="4">
-        <v>44562</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C585" s="3">
-        <v>40712.957000000002</v>
+        <v>67791.179999999993</v>
       </c>
       <c r="D585" s="3">
-        <v>40712.957000000002</v>
+        <v>67791.179999999993</v>
       </c>
       <c r="E585" s="4">
-        <v>44593</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
@@ -10326,13 +10319,13 @@
         <v>28</v>
       </c>
       <c r="C586" s="3">
-        <v>33079.277000000002</v>
+        <v>99237.831999999995</v>
       </c>
       <c r="D586" s="3">
-        <v>33079.277000000002</v>
+        <v>99237.831999999995</v>
       </c>
       <c r="E586" s="4">
-        <v>44621</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
@@ -10343,13 +10336,13 @@
         <v>28</v>
       </c>
       <c r="C587" s="3">
-        <v>48346.635999999999</v>
+        <v>66158.554999999993</v>
       </c>
       <c r="D587" s="3">
-        <v>48346.635999999999</v>
+        <v>66158.554999999993</v>
       </c>
       <c r="E587" s="4">
-        <v>44652</v>
+        <v>44501</v>
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
@@ -10360,13 +10353,13 @@
         <v>28</v>
       </c>
       <c r="C588" s="3">
-        <v>86515.032999999996</v>
+        <v>43257.516000000003</v>
       </c>
       <c r="D588" s="3">
-        <v>86515.032999999996</v>
+        <v>43257.516000000003</v>
       </c>
       <c r="E588" s="4">
-        <v>44682</v>
+        <v>44531</v>
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
@@ -10377,13 +10370,13 @@
         <v>28</v>
       </c>
       <c r="C589" s="3">
-        <v>58524.875</v>
+        <v>33079.277000000002</v>
       </c>
       <c r="D589" s="3">
-        <v>58524.875</v>
+        <v>33079.277000000002</v>
       </c>
       <c r="E589" s="4">
-        <v>44713</v>
+        <v>44562</v>
       </c>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
@@ -10394,13 +10387,13 @@
         <v>28</v>
       </c>
       <c r="C590" s="3">
-        <v>71247.673999999999</v>
+        <v>40712.957000000002</v>
       </c>
       <c r="D590" s="3">
-        <v>71247.673999999999</v>
+        <v>40712.957000000002</v>
       </c>
       <c r="E590" s="4">
-        <v>44743</v>
+        <v>44593</v>
       </c>
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
@@ -10411,13 +10404,13 @@
         <v>28</v>
       </c>
       <c r="C591" s="3">
-        <v>50891.196000000004</v>
+        <v>33079.277000000002</v>
       </c>
       <c r="D591" s="3">
-        <v>50891.196000000004</v>
+        <v>33079.277000000002</v>
       </c>
       <c r="E591" s="4">
-        <v>44774</v>
+        <v>44621</v>
       </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
@@ -10428,13 +10421,13 @@
         <v>28</v>
       </c>
       <c r="C592" s="3">
-        <v>90331.873000000007</v>
+        <v>48346.635999999999</v>
       </c>
       <c r="D592" s="3">
-        <v>90331.873000000007</v>
+        <v>48346.635999999999</v>
       </c>
       <c r="E592" s="4">
-        <v>44805</v>
+        <v>44652</v>
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
@@ -10445,13 +10438,13 @@
         <v>28</v>
       </c>
       <c r="C593" s="3">
-        <v>94148.712</v>
+        <v>86515.032999999996</v>
       </c>
       <c r="D593" s="3">
-        <v>94148.712</v>
+        <v>86515.032999999996</v>
       </c>
       <c r="E593" s="4">
-        <v>44835</v>
+        <v>44682</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
@@ -10462,13 +10455,13 @@
         <v>28</v>
       </c>
       <c r="C594" s="3">
-        <v>75318.97</v>
+        <v>58524.875</v>
       </c>
       <c r="D594" s="3">
-        <v>75318.97</v>
+        <v>58524.875</v>
       </c>
       <c r="E594" s="4">
-        <v>44866</v>
+        <v>44713</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -10479,13 +10472,13 @@
         <v>28</v>
       </c>
       <c r="C595" s="3">
-        <v>154709.24</v>
+        <v>71247.673999999999</v>
       </c>
       <c r="D595" s="3">
-        <v>154709.24</v>
+        <v>71247.673999999999</v>
       </c>
       <c r="E595" s="4">
-        <v>44896</v>
+        <v>44743</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
@@ -10496,13 +10489,13 @@
         <v>28</v>
       </c>
       <c r="C596" s="3">
-        <v>108739.76281380528</v>
+        <v>50891.196000000004</v>
       </c>
       <c r="D596" s="3">
-        <v>108398.25</v>
+        <v>50891.196000000004</v>
       </c>
       <c r="E596" s="4">
-        <v>44927</v>
+        <v>44774</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
@@ -10513,13 +10506,13 @@
         <v>28</v>
       </c>
       <c r="C597" s="3">
-        <v>130710.51053817889</v>
+        <v>90331.873000000007</v>
       </c>
       <c r="D597" s="3">
-        <v>130027.01</v>
+        <v>90331.873000000007</v>
       </c>
       <c r="E597" s="4">
-        <v>44958</v>
+        <v>44805</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
@@ -10530,13 +10523,13 @@
         <v>28</v>
       </c>
       <c r="C598" s="3">
-        <v>120692.52894461731</v>
+        <v>94148.712</v>
       </c>
       <c r="D598" s="3">
-        <v>119848.77</v>
+        <v>94148.712</v>
       </c>
       <c r="E598" s="4">
-        <v>44986</v>
+        <v>44835</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -10547,13 +10540,13 @@
         <v>28</v>
       </c>
       <c r="C599" s="3">
-        <v>120692.52894461731</v>
+        <v>75318.97</v>
       </c>
       <c r="D599" s="3">
-        <v>119848.77</v>
+        <v>75318.97</v>
       </c>
       <c r="E599" s="4">
-        <v>45017</v>
+        <v>44866</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
@@ -10564,13 +10557,13 @@
         <v>28</v>
       </c>
       <c r="C600" s="3">
-        <v>126362.03522286958</v>
+        <v>154709.24</v>
       </c>
       <c r="D600" s="3">
-        <v>125192.34166800001</v>
+        <v>154709.24</v>
       </c>
       <c r="E600" s="4">
-        <v>45047</v>
+        <v>44896</v>
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
@@ -10581,13 +10574,13 @@
         <v>28</v>
       </c>
       <c r="C601" s="3">
-        <v>165026.80094276034</v>
+        <v>108739.76281380528</v>
       </c>
       <c r="D601" s="3">
-        <v>162851.82656000002</v>
+        <v>108398.25</v>
       </c>
       <c r="E601" s="4">
-        <v>45078</v>
+        <v>44927</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
@@ -10598,13 +10591,13 @@
         <v>28</v>
       </c>
       <c r="C602" s="3">
-        <v>158100.40602735957</v>
+        <v>130710.51053817889</v>
       </c>
       <c r="D602" s="3">
-        <v>154709.23523200001</v>
+        <v>130027.01</v>
       </c>
       <c r="E602" s="4">
-        <v>45108</v>
+        <v>44958</v>
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
@@ -10615,13 +10608,13 @@
         <v>28</v>
       </c>
       <c r="C603" s="3">
-        <v>145440.35132198705</v>
+        <v>120692.52894461731</v>
       </c>
       <c r="D603" s="3">
-        <v>142240.892261</v>
+        <v>119848.77</v>
       </c>
       <c r="E603" s="4">
-        <v>45139</v>
+        <v>44986</v>
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
@@ -10632,13 +10625,13 @@
         <v>28</v>
       </c>
       <c r="C604" s="3">
-        <v>178132.77671143232</v>
+        <v>120692.52894461731</v>
       </c>
       <c r="D604" s="3">
-        <v>173793.43365699999</v>
+        <v>119848.77</v>
       </c>
       <c r="E604" s="4">
-        <v>45170</v>
+        <v>45017</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
@@ -10649,13 +10642,13 @@
         <v>28</v>
       </c>
       <c r="C605" s="3">
-        <v>165225.26154596073</v>
+        <v>126362.03522286958</v>
       </c>
       <c r="D605" s="3">
-        <v>160816.17872800003</v>
+        <v>125192.34166800001</v>
       </c>
       <c r="E605" s="4">
-        <v>45200</v>
+        <v>45047</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
@@ -10666,98 +10659,98 @@
         <v>28</v>
       </c>
       <c r="C606" s="3">
-        <v>104260.09881201708</v>
+        <v>165026.80094276034</v>
       </c>
       <c r="D606" s="3">
-        <v>101273.47964200001</v>
+        <v>162851.82656000002</v>
       </c>
       <c r="E606" s="4">
-        <v>45231</v>
+        <v>45078</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C607" s="3">
-        <v>32224.206999999999</v>
+        <v>158100.40602735957</v>
       </c>
       <c r="D607" s="3">
-        <v>32224.206999999999</v>
+        <v>154709.23523200001</v>
       </c>
       <c r="E607" s="4">
-        <v>44682</v>
+        <v>45108</v>
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C608" s="3">
-        <v>36252.233</v>
+        <v>145440.35132198705</v>
       </c>
       <c r="D608" s="3">
-        <v>36252.233</v>
+        <v>142240.892261</v>
       </c>
       <c r="E608" s="4">
-        <v>44713</v>
+        <v>45139</v>
       </c>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C609" s="3">
-        <v>92644.596000000005</v>
+        <v>178132.77671143232</v>
       </c>
       <c r="D609" s="3">
-        <v>92644.596000000005</v>
+        <v>173793.43365699999</v>
       </c>
       <c r="E609" s="4">
-        <v>44743</v>
+        <v>45170</v>
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C610" s="3">
-        <v>84991.346999999994</v>
+        <v>165225.26154596073</v>
       </c>
       <c r="D610" s="3">
-        <v>84991.346999999994</v>
+        <v>160816.17872800003</v>
       </c>
       <c r="E610" s="4">
-        <v>44774</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C611" s="3">
-        <v>33835.417999999998</v>
+        <v>104260.09881201708</v>
       </c>
       <c r="D611" s="3">
-        <v>33835.417999999998</v>
+        <v>101273.47964200001</v>
       </c>
       <c r="E611" s="4">
-        <v>44805</v>
+        <v>45231</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
@@ -10768,13 +10761,13 @@
         <v>28</v>
       </c>
       <c r="C612" s="3">
-        <v>109965.10799999999</v>
+        <v>32224.206999999999</v>
       </c>
       <c r="D612" s="3">
-        <v>109965.10799999999</v>
+        <v>32224.206999999999</v>
       </c>
       <c r="E612" s="4">
-        <v>44835</v>
+        <v>44682</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
@@ -10785,13 +10778,13 @@
         <v>28</v>
       </c>
       <c r="C613" s="3">
-        <v>174816.32500000001</v>
+        <v>36252.233</v>
       </c>
       <c r="D613" s="3">
-        <v>174816.32500000001</v>
+        <v>36252.233</v>
       </c>
       <c r="E613" s="4">
-        <v>44866</v>
+        <v>44713</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
@@ -10802,13 +10795,13 @@
         <v>28</v>
       </c>
       <c r="C614" s="3">
-        <v>125674.41</v>
+        <v>92644.596000000005</v>
       </c>
       <c r="D614" s="3">
-        <v>125674.41</v>
+        <v>92644.596000000005</v>
       </c>
       <c r="E614" s="4">
-        <v>44896</v>
+        <v>44743</v>
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
@@ -10819,13 +10812,13 @@
         <v>28</v>
       </c>
       <c r="C615" s="3">
-        <v>186094.8</v>
+        <v>84991.346999999994</v>
       </c>
       <c r="D615" s="3">
-        <v>186094.8</v>
+        <v>84991.346999999994</v>
       </c>
       <c r="E615" s="4">
-        <v>44927</v>
+        <v>44774</v>
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
@@ -10836,13 +10829,13 @@
         <v>28</v>
       </c>
       <c r="C616" s="3">
-        <v>178844.35</v>
+        <v>33835.417999999998</v>
       </c>
       <c r="D616" s="3">
-        <v>178844.35</v>
+        <v>33835.417999999998</v>
       </c>
       <c r="E616" s="4">
-        <v>44958</v>
+        <v>44805</v>
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
@@ -10853,13 +10846,13 @@
         <v>28</v>
       </c>
       <c r="C617" s="3">
-        <v>165551.87</v>
+        <v>109965.10799999999</v>
       </c>
       <c r="D617" s="3">
-        <v>165551.87</v>
+        <v>109965.10799999999</v>
       </c>
       <c r="E617" s="4">
-        <v>44986</v>
+        <v>44835</v>
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
@@ -10870,13 +10863,13 @@
         <v>28</v>
       </c>
       <c r="C618" s="3">
-        <v>197398.3631409852</v>
+        <v>174816.32500000001</v>
       </c>
       <c r="D618" s="3">
-        <v>193345.2440448</v>
+        <v>174816.32500000001</v>
       </c>
       <c r="E618" s="4">
-        <v>45017</v>
+        <v>44866</v>
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
@@ -10887,13 +10880,13 @@
         <v>28</v>
       </c>
       <c r="C619" s="3">
-        <v>227676.98552024309</v>
+        <v>125674.41</v>
       </c>
       <c r="D619" s="3">
-        <v>225569.45138560008</v>
+        <v>125674.41</v>
       </c>
       <c r="E619" s="4">
-        <v>45047</v>
+        <v>44896</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
@@ -10904,13 +10897,13 @@
         <v>28</v>
       </c>
       <c r="C620" s="3">
-        <v>242460.24974388635</v>
+        <v>186094.8</v>
       </c>
       <c r="D620" s="3">
-        <v>239264.73950544011</v>
+        <v>186094.8</v>
       </c>
       <c r="E620" s="4">
-        <v>45078</v>
+        <v>44927</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
@@ -10921,13 +10914,13 @@
         <v>28</v>
       </c>
       <c r="C621" s="3">
-        <v>265090.93052942725</v>
+        <v>178844.35</v>
       </c>
       <c r="D621" s="3">
-        <v>259404.86909344009</v>
+        <v>178844.35</v>
       </c>
       <c r="E621" s="4">
-        <v>45108</v>
+        <v>44958</v>
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
@@ -10938,13 +10931,13 @@
         <v>28</v>
       </c>
       <c r="C622" s="3">
-        <v>254119.42697087646</v>
+        <v>165551.87</v>
       </c>
       <c r="D622" s="3">
-        <v>248529.19911592008</v>
+        <v>165551.87</v>
       </c>
       <c r="E622" s="4">
-        <v>45139</v>
+        <v>44986</v>
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
@@ -10955,13 +10948,13 @@
         <v>28</v>
       </c>
       <c r="C623" s="3">
-        <v>251018.83493052915</v>
+        <v>197398.3631409852</v>
       </c>
       <c r="D623" s="3">
-        <v>244903.97579008</v>
+        <v>193345.2440448</v>
       </c>
       <c r="E623" s="4">
-        <v>45170</v>
+        <v>45017</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
@@ -10972,13 +10965,13 @@
         <v>28</v>
       </c>
       <c r="C624" s="3">
-        <v>228029.2531500464</v>
+        <v>227676.98552024309</v>
       </c>
       <c r="D624" s="3">
-        <v>221944.22805976009</v>
+        <v>225569.45138560008</v>
       </c>
       <c r="E624" s="4">
-        <v>45200</v>
+        <v>45047</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
@@ -10989,13 +10982,13 @@
         <v>28</v>
       </c>
       <c r="C625" s="3">
-        <v>207755.42937511552</v>
+        <v>242460.24974388635</v>
       </c>
       <c r="D625" s="3">
-        <v>201804.09847176008</v>
+        <v>239264.73950544011</v>
       </c>
       <c r="E625" s="4">
-        <v>45231</v>
+        <v>45078</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
@@ -11006,13 +10999,13 @@
         <v>28</v>
       </c>
       <c r="C626" s="3">
-        <v>192604.93719886002</v>
+        <v>265090.93052942725</v>
       </c>
       <c r="D626" s="3">
-        <v>186900.40257664007</v>
+        <v>259404.86909344009</v>
       </c>
       <c r="E626" s="4">
-        <v>45261</v>
+        <v>45108</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
@@ -11023,13 +11016,13 @@
         <v>28</v>
       </c>
       <c r="C627" s="3">
-        <v>194353.93932716036</v>
+        <v>254119.42697087646</v>
       </c>
       <c r="D627" s="3">
-        <v>188108.81035192008</v>
+        <v>248529.19911592008</v>
       </c>
       <c r="E627" s="4">
-        <v>45292</v>
+        <v>45139</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
@@ -11040,13 +11033,13 @@
         <v>28</v>
       </c>
       <c r="C628" s="3">
-        <v>145164.14734065809</v>
+        <v>251018.83493052915</v>
       </c>
       <c r="D628" s="3">
-        <v>140175.30193248001</v>
+        <v>244903.97579008</v>
       </c>
       <c r="E628" s="4">
-        <v>45323</v>
+        <v>45170</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
@@ -11057,13 +11050,13 @@
         <v>28</v>
       </c>
       <c r="C629" s="3">
-        <v>131247.09668956493</v>
+        <v>228029.2531500464</v>
       </c>
       <c r="D629" s="3">
-        <v>126480.01381264004</v>
+        <v>221944.22805976009</v>
       </c>
       <c r="E629" s="4">
-        <v>45352</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
@@ -11074,13 +11067,13 @@
         <v>28</v>
       </c>
       <c r="C630" s="3">
-        <v>142038.58515593995</v>
+        <v>207755.42937511552</v>
       </c>
       <c r="D630" s="3">
-        <v>136550.07860664005</v>
+        <v>201804.09847176008</v>
       </c>
       <c r="E630" s="4">
-        <v>45383</v>
+        <v>45231</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
@@ -11091,13 +11084,13 @@
         <v>28</v>
       </c>
       <c r="C631" s="3">
-        <v>50906.215554355993</v>
+        <v>192604.93719886002</v>
       </c>
       <c r="D631" s="3">
-        <v>48739.113704302843</v>
+        <v>186900.40257664007</v>
       </c>
       <c r="E631" s="4">
-        <v>45413</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
@@ -11108,13 +11101,13 @@
         <v>28</v>
       </c>
       <c r="C632" s="3">
-        <v>47397.288384959851</v>
+        <v>194353.93932716036</v>
       </c>
       <c r="D632" s="3">
-        <v>45113.89037092495</v>
+        <v>188108.81035192008</v>
       </c>
       <c r="E632" s="4">
-        <v>45444</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
@@ -11125,13 +11118,13 @@
         <v>28</v>
       </c>
       <c r="C633" s="3">
-        <v>46984.655675507878</v>
+        <v>145164.14734065809</v>
       </c>
       <c r="D633" s="3">
-        <v>44308.285185729852</v>
+        <v>140175.30193248001</v>
       </c>
       <c r="E633" s="4">
-        <v>45474</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
@@ -11142,13 +11135,13 @@
         <v>28</v>
       </c>
       <c r="C634" s="3">
-        <v>43386.9891464498</v>
+        <v>131247.09668956493</v>
       </c>
       <c r="D634" s="3">
-        <v>40634.725541240259</v>
+        <v>126480.01381264004</v>
       </c>
       <c r="E634" s="4">
-        <v>45505</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
@@ -11159,13 +11152,13 @@
         <v>28</v>
       </c>
       <c r="C635" s="3">
-        <v>16465.193822671186</v>
+        <v>142038.58515593995</v>
       </c>
       <c r="D635" s="3">
-        <v>15322.610622410581</v>
+        <v>136550.07860664005</v>
       </c>
       <c r="E635" s="4">
-        <v>45536</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
@@ -11176,92 +11169,98 @@
         <v>28</v>
       </c>
       <c r="C636" s="3">
-        <v>217.73795044825414</v>
+        <v>50906.215554355993</v>
       </c>
       <c r="D636" s="3">
-        <v>201.40129629877208</v>
+        <v>48739.113704302843</v>
       </c>
       <c r="E636" s="4">
-        <v>45566</v>
+        <v>45413</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C637" s="3">
-        <v>31705.257707988181</v>
+        <v>47397.288384959851</v>
       </c>
       <c r="D637" s="3">
-        <v>26580.415227886144</v>
+        <v>45113.89037092495</v>
       </c>
       <c r="E637" s="4">
-        <v>46143</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C638" s="3">
-        <v>83527.94</v>
+        <v>46984.655675507878</v>
       </c>
       <c r="D638" s="3">
-        <v>85805.588690683333</v>
+        <v>44308.285185729852</v>
       </c>
       <c r="E638" s="4">
-        <v>46174</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C639" s="3"/>
+      <c r="C639" s="3">
+        <v>43386.9891464498</v>
+      </c>
       <c r="D639" s="3">
-        <v>86669.875192860127</v>
+        <v>40634.725541240259</v>
       </c>
       <c r="E639" s="4">
-        <v>46204</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C640" s="3"/>
+      <c r="C640" s="3">
+        <v>16465.193822671186</v>
+      </c>
       <c r="D640" s="3">
-        <v>79235.248633312178</v>
+        <v>15322.610622410581</v>
       </c>
       <c r="E640" s="4">
-        <v>46235</v>
+        <v>45536</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C641" s="3"/>
+      <c r="C641" s="3">
+        <v>217.73795044825414</v>
+      </c>
       <c r="D641" s="3">
-        <v>57423.298166838591</v>
+        <v>201.40129629877208</v>
       </c>
       <c r="E641" s="4">
-        <v>46266</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
@@ -11271,12 +11270,14 @@
       <c r="B642" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C642" s="3"/>
+      <c r="C642" s="3">
+        <v>31705.257707988181</v>
+      </c>
       <c r="D642" s="3">
-        <v>61429.574783129654</v>
+        <v>26580.415227886144</v>
       </c>
       <c r="E642" s="4">
-        <v>46296</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
@@ -11286,12 +11287,14 @@
       <c r="B643" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C643" s="3"/>
+      <c r="C643" s="3">
+        <v>83527.94</v>
+      </c>
       <c r="D643" s="3">
-        <v>108614.61048611326</v>
+        <v>85805.588690683333</v>
       </c>
       <c r="E643" s="4">
-        <v>46327</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
@@ -11303,10 +11306,10 @@
       </c>
       <c r="C644" s="3"/>
       <c r="D644" s="3">
-        <v>96150.63879098554</v>
+        <v>86669.875192860127</v>
       </c>
       <c r="E644" s="4">
-        <v>46357</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
@@ -11318,10 +11321,10 @@
       </c>
       <c r="C645" s="3"/>
       <c r="D645" s="3">
-        <v>93479.78771345815</v>
+        <v>79235.248633312178</v>
       </c>
       <c r="E645" s="4">
-        <v>46388</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
@@ -11333,10 +11336,10 @@
       </c>
       <c r="C646" s="3"/>
       <c r="D646" s="3">
-        <v>107724.32679360424</v>
+        <v>57423.298166838591</v>
       </c>
       <c r="E646" s="4">
-        <v>46419</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -11348,10 +11351,10 @@
       </c>
       <c r="C647" s="3"/>
       <c r="D647" s="3">
-        <v>132652.27018385968</v>
+        <v>61429.574783129654</v>
       </c>
       <c r="E647" s="4">
-        <v>46447</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
@@ -11363,10 +11366,10 @@
       </c>
       <c r="C648" s="3"/>
       <c r="D648" s="3">
-        <v>71222.695400729935</v>
+        <v>108614.61048611326</v>
       </c>
       <c r="E648" s="4">
-        <v>46478</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -11378,10 +11381,10 @@
       </c>
       <c r="C649" s="3"/>
       <c r="D649" s="3">
-        <v>124639.71695127757</v>
+        <v>96150.63879098554</v>
       </c>
       <c r="E649" s="4">
-        <v>46508</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -11393,10 +11396,10 @@
       </c>
       <c r="C650" s="3"/>
       <c r="D650" s="3">
-        <v>180282.44773309791</v>
+        <v>93479.78771345815</v>
       </c>
       <c r="E650" s="4">
-        <v>46539</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
@@ -11408,10 +11411,10 @@
       </c>
       <c r="C651" s="3"/>
       <c r="D651" s="3">
-        <v>185179.00804189791</v>
+        <v>107724.32679360424</v>
       </c>
       <c r="E651" s="4">
-        <v>46569</v>
+        <v>46419</v>
       </c>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
@@ -11423,10 +11426,10 @@
       </c>
       <c r="C652" s="3"/>
       <c r="D652" s="3">
-        <v>224351.49051229988</v>
+        <v>132652.27018385968</v>
       </c>
       <c r="E652" s="4">
-        <v>46600</v>
+        <v>46447</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
@@ -11438,10 +11441,10 @@
       </c>
       <c r="C653" s="3"/>
       <c r="D653" s="3">
-        <v>171379.61080800637</v>
+        <v>71222.695400729935</v>
       </c>
       <c r="E653" s="4">
-        <v>46631</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
@@ -11453,10 +11456,10 @@
       </c>
       <c r="C654" s="3"/>
       <c r="D654" s="3">
-        <v>176721.31296306133</v>
+        <v>124639.71695127757</v>
       </c>
       <c r="E654" s="4">
-        <v>46661</v>
+        <v>46508</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
@@ -11468,10 +11471,10 @@
       </c>
       <c r="C655" s="3"/>
       <c r="D655" s="3">
-        <v>250614.85944131887</v>
+        <v>180282.44773309791</v>
       </c>
       <c r="E655" s="4">
-        <v>46692</v>
+        <v>46539</v>
       </c>
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
@@ -11483,10 +11486,10 @@
       </c>
       <c r="C656" s="3"/>
       <c r="D656" s="3">
-        <v>160251.06465164261</v>
+        <v>185179.00804189791</v>
       </c>
       <c r="E656" s="4">
-        <v>46722</v>
+        <v>46569</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -11498,10 +11501,10 @@
       </c>
       <c r="C657" s="3"/>
       <c r="D657" s="3">
-        <v>286671.34898793825</v>
+        <v>224351.49051229988</v>
       </c>
       <c r="E657" s="4">
-        <v>46753</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
@@ -11513,10 +11516,10 @@
       </c>
       <c r="C658" s="3"/>
       <c r="D658" s="3">
-        <v>299580.46252932085</v>
+        <v>171379.61080800637</v>
       </c>
       <c r="E658" s="4">
-        <v>46784</v>
+        <v>46631</v>
       </c>
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
@@ -11528,10 +11531,10 @@
       </c>
       <c r="C659" s="3"/>
       <c r="D659" s="3">
-        <v>310709.00868568494</v>
+        <v>176721.31296306133</v>
       </c>
       <c r="E659" s="4">
-        <v>46813</v>
+        <v>46661</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
@@ -11543,10 +11546,10 @@
       </c>
       <c r="C660" s="3"/>
       <c r="D660" s="3">
-        <v>238150.88774619077</v>
+        <v>250614.85944131887</v>
       </c>
       <c r="E660" s="4">
-        <v>46844</v>
+        <v>46692</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -11558,10 +11561,10 @@
       </c>
       <c r="C661" s="3"/>
       <c r="D661" s="3">
-        <v>284445.63975666557</v>
+        <v>160251.06465164261</v>
       </c>
       <c r="E661" s="4">
-        <v>46874</v>
+        <v>46722</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
@@ -11573,10 +11576,10 @@
       </c>
       <c r="C662" s="3"/>
       <c r="D662" s="3">
-        <v>231473.7600523727</v>
+        <v>286671.34898793825</v>
       </c>
       <c r="E662" s="4">
-        <v>46905</v>
+        <v>46753</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
@@ -11588,10 +11591,10 @@
       </c>
       <c r="C663" s="3"/>
       <c r="D663" s="3">
-        <v>226132.05789731778</v>
+        <v>299580.46252932085</v>
       </c>
       <c r="E663" s="4">
-        <v>46935</v>
+        <v>46784</v>
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
@@ -11603,10 +11606,10 @@
       </c>
       <c r="C664" s="3"/>
       <c r="D664" s="3">
-        <v>89918.652943421475</v>
+        <v>310709.00868568494</v>
       </c>
       <c r="E664" s="4">
-        <v>46966</v>
+        <v>46813</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -11618,10 +11621,10 @@
       </c>
       <c r="C665" s="3"/>
       <c r="D665" s="3">
-        <v>7122.2695400728508</v>
+        <v>238150.88774619077</v>
       </c>
       <c r="E665" s="4">
-        <v>46997</v>
+        <v>46844</v>
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
@@ -11633,85 +11636,85 @@
       </c>
       <c r="C666" s="3"/>
       <c r="D666" s="3">
-        <v>445.14184625479044</v>
+        <v>284445.63975666557</v>
       </c>
       <c r="E666" s="4">
-        <v>47027</v>
+        <v>46874</v>
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C667" s="3">
-        <v>42885.197485220473</v>
-      </c>
-      <c r="D667" s="3"/>
+      <c r="C667" s="3"/>
+      <c r="D667" s="3">
+        <v>231473.7600523727</v>
+      </c>
       <c r="E667" s="4">
-        <v>45931</v>
+        <v>46905</v>
       </c>
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C668" s="3">
-        <v>60954.31</v>
-      </c>
-      <c r="D668" s="3"/>
+      <c r="C668" s="3"/>
+      <c r="D668" s="3">
+        <v>226132.05789731778</v>
+      </c>
       <c r="E668" s="4">
-        <v>45962</v>
+        <v>46935</v>
       </c>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C669" s="3">
-        <v>47204.33</v>
-      </c>
-      <c r="D669" s="3"/>
+      <c r="C669" s="3"/>
+      <c r="D669" s="3">
+        <v>89918.652943421475</v>
+      </c>
       <c r="E669" s="4">
-        <v>45992</v>
+        <v>46966</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C670" s="3">
-        <v>24668.959999999999</v>
-      </c>
-      <c r="D670" s="3"/>
+      <c r="C670" s="3"/>
+      <c r="D670" s="3">
+        <v>7122.2695400728508</v>
+      </c>
       <c r="E670" s="4">
-        <v>46023</v>
+        <v>46997</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C671" s="3">
-        <v>40298.53</v>
-      </c>
-      <c r="D671" s="3"/>
+      <c r="C671" s="3"/>
+      <c r="D671" s="3">
+        <v>445.14184625479044</v>
+      </c>
       <c r="E671" s="4">
-        <v>46054</v>
+        <v>47027</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -11722,11 +11725,11 @@
         <v>28</v>
       </c>
       <c r="C672" s="3">
-        <v>65823.179999999993</v>
+        <v>42885.197485220473</v>
       </c>
       <c r="D672" s="3"/>
       <c r="E672" s="4">
-        <v>46082</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
@@ -11737,11 +11740,11 @@
         <v>28</v>
       </c>
       <c r="C673" s="3">
-        <v>55154.35</v>
+        <v>60954.31</v>
       </c>
       <c r="D673" s="3"/>
       <c r="E673" s="4">
-        <v>46113</v>
+        <v>45962</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
@@ -11752,11 +11755,11 @@
         <v>28</v>
       </c>
       <c r="C674" s="3">
-        <v>69303.728343001363</v>
+        <v>47204.33</v>
       </c>
       <c r="D674" s="3"/>
       <c r="E674" s="4">
-        <v>46143</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
@@ -11767,11 +11770,11 @@
         <v>28</v>
       </c>
       <c r="C675" s="3">
-        <v>38459.14917177835</v>
+        <v>24668.959999999999</v>
       </c>
       <c r="D675" s="3"/>
       <c r="E675" s="4">
-        <v>46174</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
@@ -11781,12 +11784,12 @@
       <c r="B676" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C676" s="3"/>
-      <c r="D676" s="3">
-        <v>81295.287309138046</v>
-      </c>
+      <c r="C676" s="3">
+        <v>40298.53</v>
+      </c>
+      <c r="D676" s="3"/>
       <c r="E676" s="4">
-        <v>46204</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
@@ -11796,12 +11799,12 @@
       <c r="B677" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C677" s="3"/>
-      <c r="D677" s="3">
-        <v>86042.457370985532</v>
-      </c>
+      <c r="C677" s="3">
+        <v>65823.179999999993</v>
+      </c>
+      <c r="D677" s="3"/>
       <c r="E677" s="4">
-        <v>46235</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
@@ -11811,12 +11814,12 @@
       <c r="B678" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C678" s="3"/>
-      <c r="D678" s="3">
-        <v>95932.394999834461</v>
-      </c>
+      <c r="C678" s="3">
+        <v>55154.35</v>
+      </c>
+      <c r="D678" s="3"/>
       <c r="E678" s="4">
-        <v>46266</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
@@ -11826,12 +11829,12 @@
       <c r="B679" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C679" s="3"/>
-      <c r="D679" s="3">
-        <v>117096.86152557113</v>
-      </c>
+      <c r="C679" s="3">
+        <v>69303.728343001363</v>
+      </c>
+      <c r="D679" s="3"/>
       <c r="E679" s="4">
-        <v>46296</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
@@ -11841,12 +11844,12 @@
       <c r="B680" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C680" s="3"/>
-      <c r="D680" s="3">
-        <v>116305.66651526322</v>
-      </c>
+      <c r="C680" s="3">
+        <v>38459.14917177835</v>
+      </c>
+      <c r="D680" s="3"/>
       <c r="E680" s="4">
-        <v>46327</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
@@ -11858,10 +11861,10 @@
       </c>
       <c r="C681" s="3"/>
       <c r="D681" s="3">
-        <v>79712.897288522247</v>
+        <v>81295.287309138046</v>
       </c>
       <c r="E681" s="4">
-        <v>46357</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
@@ -11873,10 +11876,10 @@
       </c>
       <c r="C682" s="3"/>
       <c r="D682" s="3">
-        <v>118283.65404103301</v>
+        <v>86042.457370985532</v>
       </c>
       <c r="E682" s="4">
-        <v>46388</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
@@ -11888,10 +11891,10 @@
       </c>
       <c r="C683" s="3"/>
       <c r="D683" s="3">
-        <v>124811.01287607328</v>
+        <v>95932.394999834461</v>
       </c>
       <c r="E683" s="4">
-        <v>46419</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
@@ -11903,10 +11906,10 @@
       </c>
       <c r="C684" s="3"/>
       <c r="D684" s="3">
-        <v>136085.54177296103</v>
+        <v>117096.86152557113</v>
       </c>
       <c r="E684" s="4">
-        <v>46447</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
@@ -11918,10 +11921,10 @@
       </c>
       <c r="C685" s="3"/>
       <c r="D685" s="3">
-        <v>135887.74302038405</v>
+        <v>116305.66651526322</v>
       </c>
       <c r="E685" s="4">
-        <v>46478</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
@@ -11933,10 +11936,10 @@
       </c>
       <c r="C686" s="3"/>
       <c r="D686" s="3">
-        <v>120657.23907195672</v>
+        <v>79712.897288522247</v>
       </c>
       <c r="E686" s="4">
-        <v>46508</v>
+        <v>46357</v>
       </c>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
@@ -11948,10 +11951,10 @@
       </c>
       <c r="C687" s="3"/>
       <c r="D687" s="3">
-        <v>82086.48231944599</v>
+        <v>118283.65404103301</v>
       </c>
       <c r="E687" s="4">
-        <v>46539</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
@@ -11963,10 +11966,10 @@
       </c>
       <c r="C688" s="3"/>
       <c r="D688" s="3">
-        <v>85646.85986583159</v>
+        <v>124811.01287607328</v>
       </c>
       <c r="E688" s="4">
-        <v>46569</v>
+        <v>46419</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
@@ -11978,10 +11981,10 @@
       </c>
       <c r="C689" s="3"/>
       <c r="D689" s="3">
-        <v>115712.27025753228</v>
+        <v>136085.54177296103</v>
       </c>
       <c r="E689" s="4">
-        <v>46600</v>
+        <v>46447</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
@@ -11993,10 +11996,10 @@
       </c>
       <c r="C690" s="3"/>
       <c r="D690" s="3">
-        <v>98305.98003075819</v>
+        <v>135887.74302038405</v>
       </c>
       <c r="E690" s="4">
-        <v>46631</v>
+        <v>46478</v>
       </c>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
@@ -12008,9 +12011,84 @@
       </c>
       <c r="C691" s="3"/>
       <c r="D691" s="3">
+        <v>120657.23907195672</v>
+      </c>
+      <c r="E691" s="4">
+        <v>46508</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A692" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C692" s="3"/>
+      <c r="D692" s="3">
+        <v>82086.48231944599</v>
+      </c>
+      <c r="E692" s="4">
+        <v>46539</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A693" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C693" s="3"/>
+      <c r="D693" s="3">
+        <v>85646.85986583159</v>
+      </c>
+      <c r="E693" s="4">
+        <v>46569</v>
+      </c>
+    </row>
+    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A694" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C694" s="3"/>
+      <c r="D694" s="3">
+        <v>115712.27025753228</v>
+      </c>
+      <c r="E694" s="4">
+        <v>46600</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A695" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C695" s="3"/>
+      <c r="D695" s="3">
+        <v>98305.98003075819</v>
+      </c>
+      <c r="E695" s="4">
+        <v>46631</v>
+      </c>
+    </row>
+    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A696" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C696" s="3"/>
+      <c r="D696" s="3">
         <v>0</v>
       </c>
-      <c r="E691" s="4">
+      <c r="E696" s="4">
         <v>46661</v>
       </c>
     </row>

--- a/RECEITAS TAXA ADM.xlsx
+++ b/RECEITAS TAXA ADM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HomePC\.gemini\antigravity-ide\scratch\analise-dre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B32862-419D-4651-9D9C-89F2596BC922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CBC075-07DC-462D-9D5B-D3A4474D6FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Banco de Dados" sheetId="26" r:id="rId1"/>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Lior</t>
-  </si>
-  <si>
-    <t>Amíz</t>
   </si>
   <si>
     <t>Poty</t>
@@ -124,6 +121,9 @@
   <si>
     <t xml:space="preserve"> R$                        -  </t>
   </si>
+  <si>
+    <t>Amiz</t>
+  </si>
 </sst>
 </file>
 
@@ -139,7 +139,7 @@
     <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="mm/yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,6 +183,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Gravity"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -197,12 +203,25 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -431,7 +450,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -444,6 +463,9 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="223">
@@ -862,10 +884,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -882,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3">
         <v>120763.23062467722</v>
@@ -899,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3">
         <v>96629.992197816246</v>
@@ -916,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3">
         <v>80899.092604098594</v>
@@ -933,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3">
         <v>80944.501257276948</v>
@@ -950,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3">
         <v>81140.443737492635</v>
@@ -967,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3">
         <v>81334.277689865863</v>
@@ -984,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3">
         <v>79646.204333237984</v>
@@ -1001,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3">
         <v>186336.30034455773</v>
@@ -1018,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3">
         <v>240728.88663240641</v>
@@ -1035,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3">
         <v>220790.53183020689</v>
@@ -1052,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3">
         <v>196033.96670579311</v>
@@ -1069,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3">
         <v>208671.66365624877</v>
@@ -1086,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3">
         <v>202950.98715852812</v>
@@ -1103,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3">
         <v>221278.37136071009</v>
@@ -1120,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3">
         <v>365921.30992483516</v>
@@ -1137,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3">
         <v>449557.40884935879</v>
@@ -1154,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3">
         <v>411661.13793514267</v>
@@ -1171,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3">
         <v>987706.93951372593</v>
@@ -1188,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3">
         <v>382231.54073795641</v>
@@ -1205,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="3">
         <v>295576.59389772697</v>
@@ -1222,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="3">
         <v>214057.93408147432</v>
@@ -1239,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" s="3">
         <v>358507.7003997569</v>
@@ -1256,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="3">
         <v>367865.51221016981</v>
@@ -1273,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3">
         <v>330526.9020675178</v>
@@ -1290,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="3">
         <v>351717.7121872846</v>
@@ -1307,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="3">
         <v>316251.92556483019</v>
@@ -1324,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="3">
         <v>240459.05900293961</v>
@@ -1341,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="3">
         <v>314082.42503469996</v>
@@ -1358,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" s="3">
         <v>330313.62750834902</v>
@@ -1375,7 +1397,7 @@
         <v>0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="3">
         <v>598546.62234422565</v>
@@ -1392,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" s="3">
         <v>559142.20127239637</v>
@@ -1409,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33" s="3">
         <v>214115.41300491616</v>
@@ -1426,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" s="3">
         <v>162596.681908397</v>
@@ -1443,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" s="3">
         <v>216466.47548598636</v>
@@ -1460,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C36" s="3">
         <v>162590.13531371392</v>
@@ -1477,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C37" s="3">
         <v>120699.86351087503</v>
@@ -1494,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C38" s="3">
         <v>58244.656252510846</v>
@@ -1511,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C39" s="3">
         <v>69444.523439874873</v>
@@ -1528,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3">
@@ -1543,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3">
@@ -1558,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3">
@@ -1573,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3">
@@ -1588,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
@@ -1603,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3">
@@ -1618,7 +1640,7 @@
         <v>4</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="3">
         <v>40749.620000000003</v>
@@ -1635,7 +1657,7 @@
         <v>4</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C47" s="3">
         <v>60954.13</v>
@@ -1652,7 +1674,7 @@
         <v>4</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C48" s="3">
         <v>111023.41</v>
@@ -1669,7 +1691,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C49" s="3">
         <v>97187.23</v>
@@ -1686,7 +1708,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C50" s="3">
         <v>50771.049361899015</v>
@@ -1703,7 +1725,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C51" s="3">
         <v>93646.550595068853</v>
@@ -1720,7 +1742,7 @@
         <v>4</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C52" s="3">
         <v>98510.990429371508</v>
@@ -1737,7 +1759,7 @@
         <v>4</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C53" s="3">
         <v>50161.356874610348</v>
@@ -1754,7 +1776,7 @@
         <v>4</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C54" s="3">
         <v>85841.406808130792</v>
@@ -1771,7 +1793,7 @@
         <v>4</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C55" s="3">
         <v>72249.130525338114</v>
@@ -1788,7 +1810,7 @@
         <v>4</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C56" s="3">
         <v>67776.115293153445</v>
@@ -1805,7 +1827,7 @@
         <v>4</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C57" s="3">
         <v>73144.362763179932</v>
@@ -1822,7 +1844,7 @@
         <v>4</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C58" s="3">
         <v>72502.483791719656</v>
@@ -1839,7 +1861,7 @@
         <v>4</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C59" s="3">
         <v>50400.31138324074</v>
@@ -1856,7 +1878,7 @@
         <v>4</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C60" s="3">
         <v>48776.904303525807</v>
@@ -1873,7 +1895,7 @@
         <v>4</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C61" s="3">
         <v>59789.221203257563</v>
@@ -1890,7 +1912,7 @@
         <v>4</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C62" s="3">
         <v>84284.729193399893</v>
@@ -1907,7 +1929,7 @@
         <v>4</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C63" s="3">
         <v>98808.613056843169</v>
@@ -1924,7 +1946,7 @@
         <v>4</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C64" s="3">
         <v>92687.410232070601</v>
@@ -1941,7 +1963,7 @@
         <v>4</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C65" s="3">
         <v>58011.374013866298</v>
@@ -1958,7 +1980,7 @@
         <v>4</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C66" s="3">
         <v>84815.956202169182</v>
@@ -1975,7 +1997,7 @@
         <v>4</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C67" s="3">
         <v>113783.14840621036</v>
@@ -1992,7 +2014,7 @@
         <v>4</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C68" s="3">
         <v>123073.90428047325</v>
@@ -2009,7 +2031,7 @@
         <v>4</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C69" s="3">
         <v>196425.76576552889</v>
@@ -2026,7 +2048,7 @@
         <v>4</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C70" s="3">
         <v>166529.4505946727</v>
@@ -2043,7 +2065,7 @@
         <v>4</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C71" s="3">
         <v>243242.46629476454</v>
@@ -2060,7 +2082,7 @@
         <v>4</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3">
@@ -2075,7 +2097,7 @@
         <v>4</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3">
@@ -2090,7 +2112,7 @@
         <v>4</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3">
@@ -2105,7 +2127,7 @@
         <v>4</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3">
@@ -2120,7 +2142,7 @@
         <v>4</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3">
@@ -2135,7 +2157,7 @@
         <v>4</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3">
@@ -2150,7 +2172,7 @@
         <v>4</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3">
@@ -2165,7 +2187,7 @@
         <v>4</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3">
@@ -2180,7 +2202,7 @@
         <v>4</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3">
@@ -2195,7 +2217,7 @@
         <v>4</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3">
@@ -2210,7 +2232,7 @@
         <v>4</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3">
@@ -2225,7 +2247,7 @@
         <v>4</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3">
@@ -2240,7 +2262,7 @@
         <v>4</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3">
@@ -2255,7 +2277,7 @@
         <v>4</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3">
@@ -2270,7 +2292,7 @@
         <v>4</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3">
@@ -2285,7 +2307,7 @@
         <v>5</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C87" s="3">
         <v>55364.543627177394</v>
@@ -2302,7 +2324,7 @@
         <v>5</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C88" s="3">
         <v>59325.14910753585</v>
@@ -2319,7 +2341,7 @@
         <v>5</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C89" s="3">
         <v>47127.893048533762</v>
@@ -2336,7 +2358,7 @@
         <v>5</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C90" s="3">
         <v>26536.030366786017</v>
@@ -2353,7 +2375,7 @@
         <v>5</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C91" s="3">
         <v>41006.720319505897</v>
@@ -2370,7 +2392,7 @@
         <v>5</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C92" s="3">
         <v>30345.78</v>
@@ -2387,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C93" s="3">
         <v>44895.373321182968</v>
@@ -2404,7 +2426,7 @@
         <v>5</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C94" s="3">
         <v>78824.552501933038</v>
@@ -2421,7 +2443,7 @@
         <v>5</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C95" s="3">
         <v>110205.8489416425</v>
@@ -2438,7 +2460,7 @@
         <v>5</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C96" s="3">
         <v>71681.001433393278</v>
@@ -2455,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C97" s="3">
         <v>111414.73031018535</v>
@@ -2472,7 +2494,7 @@
         <v>5</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C98" s="3">
         <v>111613.77499261958</v>
@@ -2489,7 +2511,7 @@
         <v>5</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C99" s="3">
         <v>109251.49616127201</v>
@@ -2506,7 +2528,7 @@
         <v>5</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C100" s="3">
         <v>93566.569943108363</v>
@@ -2523,7 +2545,7 @@
         <v>5</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C101" s="3">
         <v>98366.517968100728</v>
@@ -2540,7 +2562,7 @@
         <v>5</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C102" s="3">
         <v>60146.214373939903</v>
@@ -2557,7 +2579,7 @@
         <v>5</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C103" s="3">
         <v>101252.75609622919</v>
@@ -2574,7 +2596,7 @@
         <v>5</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C104" s="3">
         <v>67744.223308494082</v>
@@ -2591,7 +2613,7 @@
         <v>5</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C105" s="3">
         <v>92550.315615851665</v>
@@ -2608,7 +2630,7 @@
         <v>5</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C106" s="3">
         <v>136887.70602622326</v>
@@ -2625,7 +2647,7 @@
         <v>5</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C107" s="3">
         <v>60757.705797713716</v>
@@ -2642,7 +2664,7 @@
         <v>5</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C108" s="3">
         <v>168685.89070289861</v>
@@ -2659,7 +2681,7 @@
         <v>5</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C109" s="3"/>
       <c r="D109" s="3">
@@ -2674,7 +2696,7 @@
         <v>5</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C110" s="3"/>
       <c r="D110" s="3">
@@ -2689,7 +2711,7 @@
         <v>5</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C111" s="3"/>
       <c r="D111" s="3">
@@ -2704,7 +2726,7 @@
         <v>5</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C112" s="3"/>
       <c r="D112" s="3">
@@ -2719,7 +2741,7 @@
         <v>5</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C113" s="3"/>
       <c r="D113" s="3">
@@ -2734,7 +2756,7 @@
         <v>5</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="3">
@@ -2749,7 +2771,7 @@
         <v>5</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="3">
@@ -2764,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="3">
@@ -2779,7 +2801,7 @@
         <v>6</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C117" s="3">
         <v>44403.900969864721</v>
@@ -2796,7 +2818,7 @@
         <v>6</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C118" s="3">
         <v>38627.573892845357</v>
@@ -2813,7 +2835,7 @@
         <v>6</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C119" s="3">
         <v>36383.375761094394</v>
@@ -2830,7 +2852,7 @@
         <v>6</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C120" s="3">
         <v>51058.763332425915</v>
@@ -2847,7 +2869,7 @@
         <v>6</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C121" s="3">
         <v>67284.162206742432</v>
@@ -2864,7 +2886,7 @@
         <v>6</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C122" s="3">
         <v>71309.804082344403</v>
@@ -2881,7 +2903,7 @@
         <v>6</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C123" s="3">
         <v>34522.29</v>
@@ -2898,7 +2920,7 @@
         <v>6</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C124" s="3">
         <v>30073.833679998235</v>
@@ -2915,7 +2937,7 @@
         <v>6</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C125" s="3">
         <v>53881.225504532864</v>
@@ -2932,7 +2954,7 @@
         <v>6</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C126" s="3">
         <v>62717.952724417846</v>
@@ -2949,7 +2971,7 @@
         <v>6</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C127" s="3">
         <v>66316.475050475958</v>
@@ -2966,7 +2988,7 @@
         <v>6</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C128" s="3">
         <v>97753.589025929337</v>
@@ -2983,7 +3005,7 @@
         <v>6</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C129" s="3">
         <v>85255.29</v>
@@ -3000,7 +3022,7 @@
         <v>6</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C130" s="3">
         <v>93368.096110828104</v>
@@ -3017,7 +3039,7 @@
         <v>6</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C131" s="3">
         <v>85636.836317100271</v>
@@ -3034,7 +3056,7 @@
         <v>6</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C132" s="3">
         <v>97110.011452788603</v>
@@ -3051,7 +3073,7 @@
         <v>6</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C133" s="3">
         <v>106213.95394453121</v>
@@ -3068,7 +3090,7 @@
         <v>6</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C134" s="3">
         <v>88456.863670235034</v>
@@ -3085,7 +3107,7 @@
         <v>6</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C135" s="3">
         <v>58136.045919668628</v>
@@ -3102,7 +3124,7 @@
         <v>6</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C136" s="3">
         <v>84936.0001894983</v>
@@ -3119,7 +3141,7 @@
         <v>6</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C137" s="3">
         <v>49365.726483164355</v>
@@ -3136,7 +3158,7 @@
         <v>6</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C138" s="3">
         <v>76474.339846546762</v>
@@ -3153,7 +3175,7 @@
         <v>6</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C139" s="3">
         <v>61644.935269497568</v>
@@ -3170,7 +3192,7 @@
         <v>6</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C140" s="3">
         <v>76701.971606113948</v>
@@ -3187,7 +3209,7 @@
         <v>6</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C141" s="3">
         <v>123284.84077270329</v>
@@ -3204,7 +3226,7 @@
         <v>6</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C142" s="3"/>
       <c r="D142" s="3">
@@ -3219,7 +3241,7 @@
         <v>6</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="3">
@@ -3234,7 +3256,7 @@
         <v>6</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="3">
@@ -3249,7 +3271,7 @@
         <v>6</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3">
@@ -3264,7 +3286,7 @@
         <v>6</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3">
@@ -3275,11 +3297,11 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="2" t="s">
-        <v>7</v>
+      <c r="A147" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C147" s="3">
         <v>38437.810000000005</v>
@@ -3292,11 +3314,11 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="2" t="s">
-        <v>7</v>
+      <c r="A148" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C148" s="3">
         <v>81848.038745955084</v>
@@ -3309,11 +3331,11 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="2" t="s">
-        <v>7</v>
+      <c r="A149" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C149" s="3">
         <v>66335.94371685377</v>
@@ -3326,11 +3348,11 @@
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="2" t="s">
-        <v>7</v>
+      <c r="A150" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C150" s="3">
         <v>53208.476400291285</v>
@@ -3343,11 +3365,11 @@
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="2" t="s">
-        <v>7</v>
+      <c r="A151" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C151" s="3">
         <v>41726.833172243612</v>
@@ -3360,11 +3382,11 @@
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="2" t="s">
-        <v>7</v>
+      <c r="A152" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C152" s="3">
         <v>68494.97287740765</v>
@@ -3377,11 +3399,11 @@
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="2" t="s">
-        <v>7</v>
+      <c r="A153" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C153" s="3">
         <v>73417.82673764514</v>
@@ -3394,11 +3416,11 @@
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="2" t="s">
-        <v>7</v>
+      <c r="A154" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C154" s="3">
         <v>34736.984928419057</v>
@@ -3411,11 +3433,11 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="2" t="s">
-        <v>7</v>
+      <c r="A155" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C155" s="3">
         <v>108767.73848052265</v>
@@ -3428,11 +3450,11 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="2" t="s">
-        <v>7</v>
+      <c r="A156" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C156" s="3">
         <v>135366.87229650162</v>
@@ -3445,11 +3467,11 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="2" t="s">
-        <v>7</v>
+      <c r="A157" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C157" s="3">
         <v>148091.85598497401</v>
@@ -3462,11 +3484,11 @@
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="2" t="s">
-        <v>7</v>
+      <c r="A158" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C158" s="3">
         <v>165517.24817777344</v>
@@ -3479,11 +3501,11 @@
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="2" t="s">
-        <v>7</v>
+      <c r="A159" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C159" s="3">
         <v>165000.04067564558</v>
@@ -3496,11 +3518,11 @@
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="2" t="s">
-        <v>7</v>
+      <c r="A160" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C160" s="3">
         <v>140464.69692654372</v>
@@ -3513,11 +3535,11 @@
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="2" t="s">
-        <v>7</v>
+      <c r="A161" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C161" s="3">
         <v>158630.17953563761</v>
@@ -3530,11 +3552,11 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="2" t="s">
-        <v>7</v>
+      <c r="A162" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C162" s="3">
         <v>87079.260112158954</v>
@@ -3547,11 +3569,11 @@
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="2" t="s">
-        <v>7</v>
+      <c r="A163" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C163" s="3">
         <v>108526.58138933522</v>
@@ -3564,11 +3586,11 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="2" t="s">
-        <v>7</v>
+      <c r="A164" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C164" s="3">
         <v>114277.97261012362</v>
@@ -3581,11 +3603,11 @@
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="2" t="s">
-        <v>7</v>
+      <c r="A165" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C165" s="3">
         <v>117414.45105467853</v>
@@ -3598,11 +3620,11 @@
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="2" t="s">
-        <v>7</v>
+      <c r="A166" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C166" s="3">
         <v>115515.12911392585</v>
@@ -3615,11 +3637,11 @@
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="2" t="s">
-        <v>7</v>
+      <c r="A167" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C167" s="3"/>
       <c r="D167" s="3">
@@ -3630,11 +3652,11 @@
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="2" t="s">
-        <v>7</v>
+      <c r="A168" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C168" s="3"/>
       <c r="D168" s="3">
@@ -3645,11 +3667,11 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="2" t="s">
-        <v>7</v>
+      <c r="A169" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C169" s="3"/>
       <c r="D169" s="3">
@@ -3660,11 +3682,11 @@
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="2" t="s">
-        <v>7</v>
+      <c r="A170" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C170" s="3"/>
       <c r="D170" s="3">
@@ -3675,11 +3697,11 @@
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="2" t="s">
-        <v>7</v>
+      <c r="A171" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C171" s="3"/>
       <c r="D171" s="3">
@@ -3690,11 +3712,11 @@
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="2" t="s">
-        <v>7</v>
+      <c r="A172" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C172" s="3"/>
       <c r="D172" s="3">
@@ -3705,11 +3727,11 @@
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="2" t="s">
-        <v>7</v>
+      <c r="A173" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C173" s="3"/>
       <c r="D173" s="3">
@@ -3720,11 +3742,11 @@
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="2" t="s">
-        <v>7</v>
+      <c r="A174" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C174" s="3"/>
       <c r="D174" s="3">
@@ -3735,11 +3757,11 @@
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="2" t="s">
-        <v>7</v>
+      <c r="A175" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C175" s="3"/>
       <c r="D175" s="3">
@@ -3750,11 +3772,11 @@
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="2" t="s">
-        <v>7</v>
+      <c r="A176" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C176" s="3"/>
       <c r="D176" s="3">
@@ -3765,11 +3787,11 @@
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" s="2" t="s">
-        <v>7</v>
+      <c r="A177" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C177" s="3"/>
       <c r="D177" s="3">
@@ -3780,11 +3802,11 @@
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" s="2" t="s">
-        <v>7</v>
+      <c r="A178" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C178" s="3"/>
       <c r="D178" s="3">
@@ -3795,11 +3817,11 @@
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" s="2" t="s">
-        <v>7</v>
+      <c r="A179" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C179" s="3"/>
       <c r="D179" s="3">
@@ -3810,11 +3832,11 @@
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="2" t="s">
-        <v>7</v>
+      <c r="A180" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3">
@@ -3825,11 +3847,11 @@
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" s="2" t="s">
-        <v>7</v>
+      <c r="A181" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3">
@@ -3840,11 +3862,11 @@
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" s="2" t="s">
-        <v>7</v>
+      <c r="A182" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3">
@@ -3855,11 +3877,11 @@
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" s="2" t="s">
-        <v>7</v>
+      <c r="A183" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3">
@@ -3870,11 +3892,11 @@
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" s="2" t="s">
-        <v>7</v>
+      <c r="A184" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3">
@@ -3885,11 +3907,11 @@
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" s="2" t="s">
-        <v>7</v>
+      <c r="A185" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="3">
@@ -3900,11 +3922,11 @@
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="2" t="s">
-        <v>7</v>
+      <c r="A186" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="3">
@@ -3915,11 +3937,11 @@
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
-        <v>7</v>
+      <c r="A187" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C187" s="3"/>
       <c r="D187" s="3">
@@ -3930,11 +3952,11 @@
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="2" t="s">
-        <v>7</v>
+      <c r="A188" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C188" s="3"/>
       <c r="D188" s="3">
@@ -3945,11 +3967,11 @@
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="2" t="s">
-        <v>7</v>
+      <c r="A189" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3">
@@ -3960,11 +3982,11 @@
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="2" t="s">
-        <v>7</v>
+      <c r="A190" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3">
@@ -3976,10 +3998,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C191" s="3">
         <v>77343.144774736065</v>
@@ -3993,10 +4015,10 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C192" s="3">
         <v>91570.169748360873</v>
@@ -4010,10 +4032,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C193" s="3">
         <v>59494.791943538476</v>
@@ -4027,10 +4049,10 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C194" s="3">
         <v>80184.374131623335</v>
@@ -4044,10 +4066,10 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C195" s="3">
         <v>95096.18862148175</v>
@@ -4061,10 +4083,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C196" s="3">
         <v>43321.344149635501</v>
@@ -4078,10 +4100,10 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C197" s="3">
         <v>65453.892089607776</v>
@@ -4095,10 +4117,10 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C198" s="3">
         <v>108099.756568835</v>
@@ -4112,10 +4134,10 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C199" s="3">
         <v>121504.80950188497</v>
@@ -4129,10 +4151,10 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C200" s="3">
         <v>135331.51487498061</v>
@@ -4146,10 +4168,10 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C201" s="3">
         <v>119109.58633725322</v>
@@ -4163,10 +4185,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C202" s="3">
         <v>110354.88418673747</v>
@@ -4180,10 +4202,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C203" s="3">
         <v>50950.206447340315</v>
@@ -4197,10 +4219,10 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C204" s="3">
         <v>110492.020884339</v>
@@ -4214,10 +4236,10 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C205" s="3">
         <v>117800.93543546701</v>
@@ -4231,10 +4253,10 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C206" s="3">
         <v>164259.0396185813</v>
@@ -4248,10 +4270,10 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C207" s="3">
         <v>94037.67041908903</v>
@@ -4265,10 +4287,10 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C208" s="3">
         <v>262286.84366803966</v>
@@ -4282,10 +4304,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C209" s="3">
         <v>66922.189689956373</v>
@@ -4299,10 +4321,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C210" s="3">
         <v>175931.31929927343</v>
@@ -4316,10 +4338,10 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C211" s="3">
         <v>240147.8057931792</v>
@@ -4333,10 +4355,10 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C212" s="3">
         <v>258409.23290236853</v>
@@ -4350,10 +4372,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C213" s="3">
         <v>238758.95920021785</v>
@@ -4367,10 +4389,10 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C214" s="3">
         <v>317044.67645300226</v>
@@ -4384,10 +4406,10 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C215" s="3"/>
       <c r="D215" s="3">
@@ -4399,10 +4421,10 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C216" s="3"/>
       <c r="D216" s="3">
@@ -4414,10 +4436,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C217" s="3"/>
       <c r="D217" s="3">
@@ -4429,10 +4451,10 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C218" s="3"/>
       <c r="D218" s="3">
@@ -4444,10 +4466,10 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C219" s="3"/>
       <c r="D219" s="3">
@@ -4459,10 +4481,10 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C220" s="3"/>
       <c r="D220" s="3">
@@ -4474,10 +4496,10 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C221" s="3"/>
       <c r="D221" s="3">
@@ -4489,10 +4511,10 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C222" s="3"/>
       <c r="D222" s="3">
@@ -4504,10 +4526,10 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C223" s="3"/>
       <c r="D223" s="3">
@@ -4519,10 +4541,10 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C224" s="3"/>
       <c r="D224" s="3">
@@ -4534,10 +4556,10 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C225" s="3"/>
       <c r="D225" s="3">
@@ -4549,10 +4571,10 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C226" s="3"/>
       <c r="D226" s="3">
@@ -4564,10 +4586,10 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C227" s="3"/>
       <c r="D227" s="3">
@@ -4579,10 +4601,10 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C228" s="3"/>
       <c r="D228" s="3">
@@ -4594,10 +4616,10 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C229" s="3"/>
       <c r="D229" s="3">
@@ -4609,10 +4631,10 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C230" s="3"/>
       <c r="D230" s="3">
@@ -4624,10 +4646,10 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C231" s="3"/>
       <c r="D231" s="3">
@@ -4639,10 +4661,10 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C232" s="3">
         <v>6991.6728709922854</v>
@@ -4656,10 +4678,10 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C233" s="3">
         <v>13902.460407732571</v>
@@ -4673,10 +4695,10 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C234" s="3">
         <v>12732.00454517746</v>
@@ -4690,10 +4712,10 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C235" s="3">
         <v>7806.6358191176505</v>
@@ -4707,10 +4729,10 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C236" s="3">
         <v>14343.39019754808</v>
@@ -4724,10 +4746,10 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C237" s="3">
         <v>7506.76</v>
@@ -4741,10 +4763,10 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C238" s="3">
         <v>4700.0600000000004</v>
@@ -4758,10 +4780,10 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C239" s="3">
         <v>29751.825463214176</v>
@@ -4775,10 +4797,10 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C240" s="3">
         <v>4694.6495356464429</v>
@@ -4792,10 +4814,10 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C241" s="3">
         <v>3336.6670950583211</v>
@@ -4809,10 +4831,10 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C242" s="3">
         <v>1762.53</v>
@@ -4826,10 +4848,10 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C243" s="3">
         <v>65261.14</v>
@@ -4843,10 +4865,10 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C244" s="3">
         <v>76993.48</v>
@@ -4860,10 +4882,10 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C245" s="3">
         <v>89459.09</v>
@@ -4877,10 +4899,10 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C246" s="3">
         <v>147746.59</v>
@@ -4894,10 +4916,10 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C247" s="3">
         <v>129512.84</v>
@@ -4911,10 +4933,10 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C248" s="3">
         <v>148727.01999999999</v>
@@ -4928,10 +4950,10 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C249" s="3">
         <v>161939.65</v>
@@ -4945,10 +4967,10 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C250" s="3">
         <v>227086.8</v>
@@ -4962,10 +4984,10 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C251" s="3">
         <v>260326.74</v>
@@ -4979,10 +5001,10 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C252" s="3">
         <v>300590.25</v>
@@ -4996,10 +5018,10 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C253" s="3">
         <v>318921.73</v>
@@ -5013,10 +5035,10 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C254" s="3">
         <v>351008.9</v>
@@ -5030,10 +5052,10 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C255" s="3">
         <v>375939.69</v>
@@ -5047,10 +5069,10 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C256" s="3">
         <v>383019.2</v>
@@ -5064,10 +5086,10 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C257" s="3">
         <v>424085.36</v>
@@ -5081,10 +5103,10 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C258" s="3">
         <v>328868.13</v>
@@ -5098,10 +5120,10 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C259" s="3">
         <v>340252.41</v>
@@ -5115,10 +5137,10 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C260" s="3">
         <v>256434.06</v>
@@ -5132,10 +5154,10 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C261" s="3">
         <v>260310.09</v>
@@ -5149,10 +5171,10 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C262" s="3">
         <v>278158.43</v>
@@ -5166,10 +5188,10 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C263" s="3">
         <v>198853.41</v>
@@ -5183,13 +5205,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B264" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C264" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D264" s="3">
         <v>169808.69468307818</v>
@@ -5200,13 +5222,13 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B265" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C265" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C265" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D265" s="3">
         <v>224047.11135465943</v>
@@ -5217,13 +5239,13 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B266" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C266" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C266" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D266" s="3">
         <v>256507.95557092282</v>
@@ -5234,13 +5256,13 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B267" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C267" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C267" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D267" s="3">
         <v>241350.51618362853</v>
@@ -5251,13 +5273,13 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B268" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C268" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C268" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D268" s="3">
         <v>249851.59082992279</v>
@@ -5268,13 +5290,13 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B269" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C269" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C269" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D269" s="3">
         <v>259759.90071645114</v>
@@ -5285,13 +5307,13 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B270" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C270" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C270" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D270" s="3">
         <v>264381.13121420774</v>
@@ -5302,10 +5324,10 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C271" s="3">
         <v>221068.84</v>
@@ -5319,10 +5341,10 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C272" s="3">
         <v>318039.02</v>
@@ -5336,10 +5358,10 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C273" s="3">
         <v>627728.86</v>
@@ -5353,10 +5375,10 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C274" s="3">
         <v>394888.77</v>
@@ -5370,10 +5392,10 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C275" s="3">
         <v>531945.79</v>
@@ -5387,10 +5409,10 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C276" s="3">
         <v>598553.74</v>
@@ -5402,10 +5424,10 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C277" s="3">
         <v>432253.01</v>
@@ -5417,10 +5439,10 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C278" s="3">
         <v>231392.12</v>
@@ -5432,13 +5454,13 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B279" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C279" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C279" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D279" s="3"/>
       <c r="E279" s="4">
@@ -5447,10 +5469,10 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C280" s="3">
         <v>20028.330000000002</v>
@@ -5462,10 +5484,10 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C281" s="3">
         <v>168138.81</v>
@@ -5477,10 +5499,10 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C282" s="3">
         <v>98070.38</v>
@@ -5492,10 +5514,10 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C283" s="3">
         <v>84094.83</v>
@@ -5507,10 +5529,10 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C284" s="3">
         <v>57748.03</v>
@@ -5522,10 +5544,10 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C285" s="3">
         <v>46336.35</v>
@@ -5537,10 +5559,10 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C286" s="3">
         <v>94742.51</v>
@@ -5552,10 +5574,10 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C287" s="3">
         <v>25212.524959232152</v>
@@ -5569,10 +5591,10 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C288" s="3">
         <v>67204.745290938736</v>
@@ -5586,10 +5608,10 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C289" s="3">
         <v>81518.247506175598</v>
@@ -5603,10 +5625,10 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C290" s="3">
         <v>54457.985144909791</v>
@@ -5620,10 +5642,10 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C291" s="3">
         <v>45839.064371133427</v>
@@ -5637,10 +5659,10 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C292" s="3">
         <v>30767.521918081562</v>
@@ -5654,10 +5676,10 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C293" s="3">
         <v>59033.491767121071</v>
@@ -5671,10 +5693,10 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C294" s="3">
         <v>43563.452441023081</v>
@@ -5688,10 +5710,10 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C295" s="3">
         <v>41696.11818349018</v>
@@ -5705,10 +5727,10 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C296" s="3">
         <v>24016.950594697322</v>
@@ -5722,10 +5744,10 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C297" s="3">
         <v>22279.218700217491</v>
@@ -5739,10 +5761,10 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C298" s="3">
         <v>37793.894683640276</v>
@@ -5756,10 +5778,10 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C299" s="3"/>
       <c r="D299" s="3">
@@ -5771,10 +5793,10 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C300" s="3"/>
       <c r="D300" s="3">
@@ -5786,10 +5808,10 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C301" s="3"/>
       <c r="D301" s="3">
@@ -5801,10 +5823,10 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C302" s="3"/>
       <c r="D302" s="3">
@@ -5816,10 +5838,10 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C303" s="3"/>
       <c r="D303" s="3">
@@ -5831,10 +5853,10 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C304" s="3"/>
       <c r="D304" s="3">
@@ -5846,10 +5868,10 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C305" s="3"/>
       <c r="D305" s="3">
@@ -5861,10 +5883,10 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C306" s="3"/>
       <c r="D306" s="3">
@@ -5876,10 +5898,10 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C307" s="3"/>
       <c r="D307" s="3">
@@ -5891,10 +5913,10 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C308" s="3"/>
       <c r="D308" s="3">
@@ -5906,10 +5928,10 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C309" s="3">
         <v>130557.75855251723</v>
@@ -5923,10 +5945,10 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C310" s="3">
         <v>145517.47756593174</v>
@@ -5940,10 +5962,10 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C311" s="3">
         <v>213848.5456893518</v>
@@ -5957,10 +5979,10 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C312" s="3">
         <v>154879.189241727</v>
@@ -5974,10 +5996,10 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C313" s="3"/>
       <c r="D313" s="3">
@@ -5989,10 +6011,10 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C314" s="3"/>
       <c r="D314" s="3">
@@ -6004,10 +6026,10 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C315" s="3"/>
       <c r="D315" s="3">
@@ -6019,10 +6041,10 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C316" s="3"/>
       <c r="D316" s="3">
@@ -6034,10 +6056,10 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C317" s="3"/>
       <c r="D317" s="3">
@@ -6049,10 +6071,10 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C318" s="3"/>
       <c r="D318" s="3">
@@ -6064,10 +6086,10 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C319" s="3"/>
       <c r="D319" s="3">
@@ -6079,10 +6101,10 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C320" s="3"/>
       <c r="D320" s="3">
@@ -6094,10 +6116,10 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C321" s="3"/>
       <c r="D321" s="3">
@@ -6109,10 +6131,10 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C322" s="3"/>
       <c r="D322" s="3">
@@ -6124,10 +6146,10 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C323" s="3"/>
       <c r="D323" s="3">
@@ -6139,10 +6161,10 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C324" s="3"/>
       <c r="D324" s="3">
@@ -6154,10 +6176,10 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C325" s="3"/>
       <c r="D325" s="3">
@@ -6169,10 +6191,10 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C326" s="3"/>
       <c r="D326" s="3">
@@ -6184,10 +6206,10 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C327" s="3"/>
       <c r="D327" s="3">
@@ -6199,10 +6221,10 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C328" s="3"/>
       <c r="D328" s="3">
@@ -6214,10 +6236,10 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C329" s="3"/>
       <c r="D329" s="3">
@@ -6229,10 +6251,10 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C330" s="3"/>
       <c r="D330" s="3">
@@ -6244,10 +6266,10 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C331" s="3"/>
       <c r="D331" s="3">
@@ -6259,10 +6281,10 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C332" s="3"/>
       <c r="D332" s="3">
@@ -6274,10 +6296,10 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C333" s="3"/>
       <c r="D333" s="3">
@@ -6289,10 +6311,10 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C334" s="3"/>
       <c r="D334" s="3">
@@ -6304,10 +6326,10 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C335" s="3"/>
       <c r="D335" s="3">
@@ -6319,10 +6341,10 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C336" s="3"/>
       <c r="D336" s="3">
@@ -6334,10 +6356,10 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C337" s="3"/>
       <c r="D337" s="3">
@@ -6349,10 +6371,10 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C338" s="3"/>
       <c r="D338" s="3">
@@ -6364,10 +6386,10 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C339" s="3"/>
       <c r="D339" s="3">
@@ -6379,10 +6401,10 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C340" s="3"/>
       <c r="D340" s="3">
@@ -6394,10 +6416,10 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C341" s="3"/>
       <c r="D341" s="3">
@@ -6409,10 +6431,10 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C342" s="3"/>
       <c r="D342" s="3">
@@ -6424,10 +6446,10 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C343" s="3"/>
       <c r="D343" s="3">
@@ -6439,10 +6461,10 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C344" s="3"/>
       <c r="D344" s="3">
@@ -6454,10 +6476,10 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C345" s="3"/>
       <c r="D345" s="3">
@@ -6469,10 +6491,10 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C346" s="3"/>
       <c r="D346" s="3">
@@ -6484,10 +6506,10 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C347" s="3"/>
       <c r="D347" s="3">
@@ -6499,10 +6521,10 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C348" s="3"/>
       <c r="D348" s="3">
@@ -6514,10 +6536,10 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C349" s="3"/>
       <c r="D349" s="3">
@@ -6529,10 +6551,10 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C350" s="3"/>
       <c r="D350" s="3">
@@ -6544,10 +6566,10 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C351" s="3"/>
       <c r="D351" s="3">
@@ -6559,10 +6581,10 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C352" s="3"/>
       <c r="D352" s="3">
@@ -6574,10 +6596,10 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C353" s="3"/>
       <c r="D353" s="3">
@@ -6589,10 +6611,10 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C354" s="3">
         <v>30130.775000000001</v>
@@ -6604,10 +6626,10 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C355" s="3">
         <v>38558.961000000003</v>
@@ -6619,10 +6641,10 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C356" s="3">
         <v>77485.978000000003</v>
@@ -6634,10 +6656,10 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C357" s="3">
         <v>24178.572</v>
@@ -6649,10 +6671,10 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C358" s="3">
         <v>62108.562000000013</v>
@@ -6664,10 +6686,10 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C359" s="3">
         <v>37123.801999999996</v>
@@ -6679,10 +6701,10 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C360" s="3">
         <v>20666.242000000002</v>
@@ -6694,10 +6716,10 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C361" s="3">
         <v>70332.395000000004</v>
@@ -6709,10 +6731,10 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C362" s="3">
         <v>46771.264999999999</v>
@@ -6724,10 +6746,10 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C363" s="3">
         <v>43923.928000000014</v>
@@ -6739,10 +6761,10 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C364" s="3">
         <v>46834.330999999998</v>
@@ -6754,10 +6776,10 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C365" s="3">
         <v>78670.63900000001</v>
@@ -6769,10 +6791,10 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C366" s="3">
         <v>103769.64199999999</v>
@@ -6784,10 +6806,10 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C367" s="3">
         <v>87782.781000000017</v>
@@ -6799,10 +6821,10 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C368" s="3">
         <v>76568.732999999993</v>
@@ -6814,10 +6836,10 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C369" s="3">
         <v>107837.569</v>
@@ -6829,10 +6851,10 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C370" s="3">
         <v>88596.103000000003</v>
@@ -6844,10 +6866,10 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C371" s="3">
         <v>150026.516</v>
@@ -6859,10 +6881,10 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C372" s="3">
         <v>179151.39599999995</v>
@@ -6874,10 +6896,10 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C373" s="3">
         <v>152045.40000000002</v>
@@ -6889,10 +6911,10 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C374" s="3">
         <v>167363.64200000002</v>
@@ -6904,10 +6926,10 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C375" s="3">
         <v>177970.74705999997</v>
@@ -6919,10 +6941,10 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C376" s="3">
         <v>210039.28201000002</v>
@@ -6934,10 +6956,10 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C377" s="3">
         <v>106528.88401999998</v>
@@ -6949,10 +6971,10 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C378" s="3">
         <v>140690.58727999998</v>
@@ -6964,10 +6986,10 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C379" s="3">
         <v>191261.03599</v>
@@ -6979,10 +7001,10 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C380" s="3">
         <v>70253.478990000003</v>
@@ -6994,10 +7016,10 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C381" s="3">
         <v>166515.68897000002</v>
@@ -7009,10 +7031,10 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C382" s="3">
         <v>86831.99768</v>
@@ -7024,10 +7046,10 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C383" s="3">
         <v>73873.089990000008</v>
@@ -7039,10 +7061,10 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C384" s="3">
         <v>203586.33702000004</v>
@@ -7054,10 +7076,10 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C385" s="3">
         <v>0</v>
@@ -7069,10 +7091,10 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C386" s="3">
         <v>0</v>
@@ -7084,10 +7106,10 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C387" s="3">
         <v>0</v>
@@ -7099,10 +7121,10 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C388" s="3">
         <v>24793.759999999998</v>
@@ -7116,10 +7138,10 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C389" s="3">
         <v>15771.623288620114</v>
@@ -7133,10 +7155,10 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C390" s="3">
         <v>26475.609246023771</v>
@@ -7150,10 +7172,10 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C391" s="3"/>
       <c r="D391" s="3">
@@ -7165,10 +7187,10 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C392" s="3"/>
       <c r="D392" s="3">
@@ -7180,10 +7202,10 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C393" s="3"/>
       <c r="D393" s="3">
@@ -7195,10 +7217,10 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C394" s="3"/>
       <c r="D394" s="3">
@@ -7210,10 +7232,10 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C395" s="3"/>
       <c r="D395" s="3">
@@ -7225,10 +7247,10 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C396" s="3"/>
       <c r="D396" s="3">
@@ -7240,10 +7262,10 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C397" s="3"/>
       <c r="D397" s="3">
@@ -7255,10 +7277,10 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C398" s="3"/>
       <c r="D398" s="3">
@@ -7270,10 +7292,10 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C399" s="3"/>
       <c r="D399" s="3">
@@ -7285,10 +7307,10 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C400" s="3"/>
       <c r="D400" s="3">
@@ -7300,10 +7322,10 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C401" s="3"/>
       <c r="D401" s="3">
@@ -7315,10 +7337,10 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C402" s="3"/>
       <c r="D402" s="3">
@@ -7330,10 +7352,10 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C403" s="3">
         <v>26851.820000000007</v>
@@ -7347,10 +7369,10 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C404" s="3">
         <v>166811.38069934564</v>
@@ -7364,10 +7386,10 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C405" s="3">
         <v>154809.84939034589</v>
@@ -7381,10 +7403,10 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C406" s="3">
         <v>255368.67</v>
@@ -7398,10 +7420,10 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C407" s="3">
         <v>162881.49229537524</v>
@@ -7415,10 +7437,10 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C408" s="3">
         <v>101930.18455784231</v>
@@ -7432,10 +7454,10 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C409" s="3">
         <v>171765.37459269757</v>
@@ -7449,10 +7471,10 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C410" s="3">
         <v>200119.48519500322</v>
@@ -7466,10 +7488,10 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C411" s="3">
         <v>122618.12646991033</v>
@@ -7483,10 +7505,10 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C412" s="3">
         <v>109173.12817728696</v>
@@ -7500,10 +7522,10 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C413" s="3">
         <v>64939.473290446986</v>
@@ -7517,10 +7539,10 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C414" s="3">
         <v>98395.325175217033</v>
@@ -7534,10 +7556,10 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C415" s="3">
         <v>103451.0419977219</v>
@@ -7551,10 +7573,10 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C416" s="3">
         <v>122918.29</v>
@@ -7568,10 +7590,10 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C417" s="3">
         <v>136650.91</v>
@@ -7585,10 +7607,10 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C418" s="3">
         <v>136165.79502335232</v>
@@ -7602,10 +7624,10 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C419" s="3">
         <v>199823.24395059652</v>
@@ -7619,10 +7641,10 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C420" s="3">
         <v>167059.63684127861</v>
@@ -7636,10 +7658,10 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C421" s="3">
         <v>160446.04582894297</v>
@@ -7653,10 +7675,10 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C422" s="3">
         <v>198879.01733365844</v>
@@ -7670,10 +7692,10 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C423" s="3">
         <v>200379.34</v>
@@ -7687,10 +7709,10 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C424" s="3">
         <v>214970.12258073571</v>
@@ -7704,10 +7726,10 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C425" s="3">
         <v>96943.01</v>
@@ -7721,10 +7743,10 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C426" s="3">
         <v>123079.08</v>
@@ -7738,10 +7760,10 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C427" s="3">
         <v>179863.01220826618</v>
@@ -7755,10 +7777,10 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C428" s="3">
         <v>164075.29806907824</v>
@@ -7772,10 +7794,10 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C429" s="3">
         <v>181931.9978069053</v>
@@ -7789,10 +7811,10 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C430" s="3">
         <v>163601.48263622401</v>
@@ -7806,10 +7828,10 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C431" s="3">
         <v>121181.49074320766</v>
@@ -7823,10 +7845,10 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C432" s="3">
         <v>156205.71780410968</v>
@@ -7840,10 +7862,10 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C433" s="3"/>
       <c r="D433" s="3">
@@ -7855,10 +7877,10 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C434" s="3"/>
       <c r="D434" s="3">
@@ -7870,10 +7892,10 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C435" s="3"/>
       <c r="D435" s="3">
@@ -7885,10 +7907,10 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C436" s="3"/>
       <c r="D436" s="3">
@@ -7900,10 +7922,10 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C437" s="3"/>
       <c r="D437" s="3">
@@ -7915,10 +7937,10 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C438" s="3"/>
       <c r="D438" s="3">
@@ -7930,10 +7952,10 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C439" s="3"/>
       <c r="D439" s="3">
@@ -7945,10 +7967,10 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C440" s="3"/>
       <c r="D440" s="3">
@@ -7960,10 +7982,10 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C441" s="3"/>
       <c r="D441" s="3">
@@ -7975,10 +7997,10 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C442" s="3"/>
       <c r="D442" s="3">
@@ -7990,10 +8012,10 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C443" s="3"/>
       <c r="D443" s="3">
@@ -8005,10 +8027,10 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C444" s="3"/>
       <c r="D444" s="3">
@@ -8020,10 +8042,10 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C445" s="3"/>
       <c r="D445" s="3">
@@ -8035,10 +8057,10 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C446" s="3"/>
       <c r="D446" s="3">
@@ -8050,10 +8072,10 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C447" s="3">
         <v>92993.94544996148</v>
@@ -8065,10 +8087,10 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C448" s="3">
         <v>119807.97601575598</v>
@@ -8082,10 +8104,10 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C449" s="3">
         <v>167984.15201723264</v>
@@ -8099,10 +8121,10 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C450" s="3">
         <v>215703.30706053553</v>
@@ -8116,10 +8138,10 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C451" s="3">
         <v>178228.674851786</v>
@@ -8133,10 +8155,10 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C452" s="3">
         <v>99010.759076728253</v>
@@ -8150,10 +8172,10 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C453" s="3">
         <v>125437.20844000007</v>
@@ -8167,10 +8189,10 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C454" s="3"/>
       <c r="D454" s="3">
@@ -8182,10 +8204,10 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C455" s="3"/>
       <c r="D455" s="3">
@@ -8197,10 +8219,10 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C456" s="3"/>
       <c r="D456" s="3">
@@ -8212,10 +8234,10 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C457" s="3"/>
       <c r="D457" s="3">
@@ -8227,10 +8249,10 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C458" s="3">
         <v>19584.319258181378</v>
@@ -8244,10 +8266,10 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C459" s="3">
         <v>33157.46608977556</v>
@@ -8261,10 +8283,10 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C460" s="3">
         <v>51487.02341419139</v>
@@ -8278,10 +8300,10 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C461" s="3">
         <v>29982.972168923607</v>
@@ -8295,10 +8317,10 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C462" s="3">
         <v>44957.664924564924</v>
@@ -8312,10 +8334,10 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C463" s="3">
         <v>21535.88354184922</v>
@@ -8329,10 +8351,10 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C464" s="3">
         <v>22093.922811214816</v>
@@ -8346,10 +8368,10 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C465" s="3">
         <v>46306.77660016506</v>
@@ -8363,10 +8385,10 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C466" s="3">
         <v>47898.044578191897</v>
@@ -8380,10 +8402,10 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C467" s="3">
         <v>40326.864942313507</v>
@@ -8397,10 +8419,10 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C468" s="3">
         <v>57802.291959106376</v>
@@ -8414,10 +8436,10 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C469" s="3">
         <v>88534.714708509302</v>
@@ -8431,10 +8453,10 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C470" s="3">
         <v>47272.172344710641</v>
@@ -8448,10 +8470,10 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C471" s="3">
         <v>107496.49013155067</v>
@@ -8465,10 +8487,10 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C472" s="3">
         <v>72088.000288274052</v>
@@ -8482,10 +8504,10 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C473" s="3">
         <v>59843.837644577608</v>
@@ -8499,10 +8521,10 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C474" s="3">
         <v>92206.68100426592</v>
@@ -8516,10 +8538,10 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C475" s="3">
         <v>67829.975967821461</v>
@@ -8533,10 +8555,10 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C476" s="3">
         <v>104933.01920021485</v>
@@ -8550,10 +8572,10 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C477" s="3">
         <v>103936.34990262899</v>
@@ -8567,10 +8589,10 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C478" s="3">
         <v>100847.41125942138</v>
@@ -8584,10 +8606,10 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C479" s="3">
         <v>79529.460583435008</v>
@@ -8601,10 +8623,10 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C480" s="3">
         <v>77436.813221762583</v>
@@ -8618,10 +8640,10 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C481" s="3">
         <v>91938.98020487951</v>
@@ -8635,10 +8657,10 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C482" s="3">
         <v>79385.948344763252</v>
@@ -8652,10 +8674,10 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C483" s="3">
         <v>26482.069378111279</v>
@@ -8669,10 +8691,10 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C484" s="3">
         <v>12711.39525591745</v>
@@ -8686,10 +8708,10 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C485" s="3">
         <v>4018.5517036805713</v>
@@ -8703,10 +8725,10 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C486" s="3">
         <v>69023</v>
@@ -8718,10 +8740,10 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C487" s="3">
         <v>69023</v>
@@ -8733,10 +8755,10 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C488" s="3">
         <v>69023</v>
@@ -8748,10 +8770,10 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C489" s="3">
         <v>69023</v>
@@ -8763,10 +8785,10 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C490" s="3">
         <v>69023</v>
@@ -8778,10 +8800,10 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C491" s="3">
         <v>69023</v>
@@ -8793,10 +8815,10 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C492" s="3">
         <v>69023</v>
@@ -8808,10 +8830,10 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C493" s="3">
         <v>69023</v>
@@ -8823,10 +8845,10 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C494" s="3">
         <v>69023</v>
@@ -8838,10 +8860,10 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C495" s="3">
         <v>69023</v>
@@ -8853,10 +8875,10 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C496" s="3">
         <v>69023</v>
@@ -8868,10 +8890,10 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C497" s="3">
         <v>69023</v>
@@ -8883,10 +8905,10 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C498" s="3">
         <v>69023</v>
@@ -8898,10 +8920,10 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C499" s="3">
         <v>69023</v>
@@ -8913,10 +8935,10 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C500" s="3">
         <v>69023</v>
@@ -8928,10 +8950,10 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C501" s="3">
         <v>69023</v>
@@ -8943,10 +8965,10 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C502" s="3">
         <v>69023</v>
@@ -8958,10 +8980,10 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C503" s="3">
         <v>69023</v>
@@ -8973,10 +8995,10 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C504" s="3">
         <v>69023</v>
@@ -8988,10 +9010,10 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C505" s="3">
         <v>69023</v>
@@ -9003,10 +9025,10 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C506" s="3">
         <v>69023</v>
@@ -9018,10 +9040,10 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C507" s="3">
         <v>69023</v>
@@ -9033,10 +9055,10 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C508" s="3">
         <v>69023</v>
@@ -9048,10 +9070,10 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C509" s="3">
         <v>69023</v>
@@ -9063,10 +9085,10 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C510" s="3">
         <v>69023</v>
@@ -9078,10 +9100,10 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C511" s="3">
         <v>69023</v>
@@ -9093,10 +9115,10 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C512" s="3">
         <v>69023</v>
@@ -9108,10 +9130,10 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C513" s="3">
         <v>69023</v>
@@ -9123,10 +9145,10 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C514" s="3">
         <v>69023</v>
@@ -9138,10 +9160,10 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C515" s="3">
         <v>69023</v>
@@ -9153,10 +9175,10 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C516" s="3">
         <v>69023</v>
@@ -9168,10 +9190,10 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C517" s="3">
         <v>69023</v>
@@ -9183,10 +9205,10 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C518" s="3">
         <v>0</v>
@@ -9198,10 +9220,10 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C519" s="3">
         <v>0</v>
@@ -9213,10 +9235,10 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C520" s="3">
         <v>38988.409999999996</v>
@@ -9228,10 +9250,10 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C521" s="3">
         <v>0</v>
@@ -9243,10 +9265,10 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C522" s="3">
         <v>0</v>
@@ -9258,10 +9280,10 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C523" s="3">
         <v>0</v>
@@ -9273,10 +9295,10 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C524" s="3">
         <v>0</v>
@@ -9288,10 +9310,10 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C525" s="3">
         <v>0</v>
@@ -9303,10 +9325,10 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C526" s="3">
         <v>0</v>
@@ -9318,10 +9340,10 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C527" s="3">
         <v>0</v>
@@ -9333,10 +9355,10 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C528" s="3">
         <v>0</v>
@@ -9348,10 +9370,10 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C529" s="3">
         <v>0</v>
@@ -9363,10 +9385,10 @@
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C530" s="3">
         <v>1821264</v>
@@ -9378,10 +9400,10 @@
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C531" s="3">
         <v>118649.512</v>
@@ -9395,10 +9417,10 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C532" s="3">
         <v>41389.364999999998</v>
@@ -9412,10 +9434,10 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C533" s="3">
         <v>33111.491999999998</v>
@@ -9429,10 +9451,10 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C534" s="3">
         <v>35870.783000000003</v>
@@ -9446,10 +9468,10 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C535" s="3">
         <v>46907.946000000004</v>
@@ -9463,10 +9485,10 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C536" s="3">
         <v>27592.91</v>
@@ -9480,10 +9502,10 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C537" s="3">
         <v>38906.002999999997</v>
@@ -9497,10 +9519,10 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C538" s="3">
         <v>77536.076000000001</v>
@@ -9514,10 +9536,10 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C539" s="3">
         <v>84986.161999999997</v>
@@ -9531,10 +9553,10 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C540" s="3">
         <v>97140.87</v>
@@ -9548,10 +9570,10 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C541" s="3">
         <v>134653.4</v>
@@ -9565,10 +9587,10 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C542" s="3">
         <v>144034.99</v>
@@ -9582,10 +9604,10 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C543" s="3">
         <v>181009.49</v>
@@ -9599,10 +9621,10 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C544" s="3">
         <v>126108.61121657665</v>
@@ -9616,10 +9638,10 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C545" s="3">
         <v>108060.77429213714</v>
@@ -9633,10 +9655,10 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C546" s="3">
         <v>103736.89783644832</v>
@@ -9650,10 +9672,10 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C547" s="3">
         <v>127453.76846242594</v>
@@ -9667,10 +9689,10 @@
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C548" s="3">
         <v>128371.71516401674</v>
@@ -9684,10 +9706,10 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C549" s="3">
         <v>126702.7345474715</v>
@@ -9701,10 +9723,10 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C550" s="3">
         <v>122469.50334718848</v>
@@ -9718,10 +9740,10 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C551" s="3">
         <v>136351.8822857202</v>
@@ -9735,10 +9757,10 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C552" s="3">
         <v>181700.25508377992</v>
@@ -9752,10 +9774,10 @@
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C553" s="3">
         <v>210966.46738108408</v>
@@ -9769,10 +9791,10 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C554" s="3">
         <v>206311.08591475722</v>
@@ -9786,10 +9808,10 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C555" s="3">
         <v>106514.37928003953</v>
@@ -9803,10 +9825,10 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C556" s="3">
         <v>59685.735913831784</v>
@@ -9820,10 +9842,10 @@
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C557" s="3">
         <v>33562.230417420651</v>
@@ -9837,10 +9859,10 @@
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C558" s="3">
         <v>11630.763264592404</v>
@@ -9854,10 +9876,10 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C559" s="3">
         <v>51295.182339413339</v>
@@ -9871,10 +9893,10 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C560" s="3">
         <v>62911.355705869886</v>
@@ -9888,10 +9910,10 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C561" s="3">
         <v>74844.872082093367</v>
@@ -9905,10 +9927,10 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C562" s="3">
         <v>62392.907094820497</v>
@@ -9922,10 +9944,10 @@
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C563" s="3">
         <v>41443.802425811758</v>
@@ -9939,10 +9961,10 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C564" s="3">
         <v>50248.450154161663</v>
@@ -9956,10 +9978,10 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C565" s="3">
         <v>19609.602990791438</v>
@@ -9973,10 +9995,10 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C566" s="3">
         <v>53861.898356575533</v>
@@ -9990,10 +10012,10 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C567" s="3">
         <v>58634.619720868533</v>
@@ -10007,10 +10029,10 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C568" s="3">
         <v>41927.913518720656</v>
@@ -10024,10 +10046,10 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C569" s="3">
         <v>194565.88700000002</v>
@@ -10041,10 +10063,10 @@
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C570" s="3">
         <v>194565.88700000002</v>
@@ -10058,10 +10080,10 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C571" s="3">
         <v>200065.89</v>
@@ -10075,10 +10097,10 @@
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C572" s="3">
         <v>200065.89</v>
@@ -10092,10 +10114,10 @@
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C573" s="3">
         <v>200065.89</v>
@@ -10109,10 +10131,10 @@
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C574" s="3">
         <v>200065.89</v>
@@ -10126,10 +10148,10 @@
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C575" s="3">
         <v>200065.89</v>
@@ -10143,10 +10165,10 @@
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C576" s="3">
         <v>200065.89</v>
@@ -10160,10 +10182,10 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C577" s="3">
         <v>200065.89</v>
@@ -10177,10 +10199,10 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C578" s="3">
         <v>200065.89</v>
@@ -10194,10 +10216,10 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C579" s="3">
         <v>72753.84</v>
@@ -10211,10 +10233,10 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C580" s="3">
         <v>150468.19</v>
@@ -10228,10 +10250,10 @@
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C581" s="3">
         <v>150468.19</v>
@@ -10245,10 +10267,10 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C582" s="3">
         <v>150468.19</v>
@@ -10262,10 +10284,10 @@
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C583" s="3">
         <v>66053.240000000005</v>
@@ -10279,10 +10301,10 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C584" s="3">
         <v>67791.179999999993</v>
@@ -10296,10 +10318,10 @@
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C585" s="3">
         <v>67791.179999999993</v>
@@ -10313,10 +10335,10 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C586" s="3">
         <v>99237.831999999995</v>
@@ -10330,10 +10352,10 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C587" s="3">
         <v>66158.554999999993</v>
@@ -10347,10 +10369,10 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C588" s="3">
         <v>43257.516000000003</v>
@@ -10364,10 +10386,10 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C589" s="3">
         <v>33079.277000000002</v>
@@ -10381,10 +10403,10 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C590" s="3">
         <v>40712.957000000002</v>
@@ -10398,10 +10420,10 @@
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C591" s="3">
         <v>33079.277000000002</v>
@@ -10415,10 +10437,10 @@
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C592" s="3">
         <v>48346.635999999999</v>
@@ -10432,10 +10454,10 @@
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C593" s="3">
         <v>86515.032999999996</v>
@@ -10449,10 +10471,10 @@
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C594" s="3">
         <v>58524.875</v>
@@ -10466,10 +10488,10 @@
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C595" s="3">
         <v>71247.673999999999</v>
@@ -10483,10 +10505,10 @@
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C596" s="3">
         <v>50891.196000000004</v>
@@ -10500,10 +10522,10 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C597" s="3">
         <v>90331.873000000007</v>
@@ -10517,10 +10539,10 @@
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C598" s="3">
         <v>94148.712</v>
@@ -10534,10 +10556,10 @@
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C599" s="3">
         <v>75318.97</v>
@@ -10551,10 +10573,10 @@
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C600" s="3">
         <v>154709.24</v>
@@ -10568,10 +10590,10 @@
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C601" s="3">
         <v>108739.76281380528</v>
@@ -10585,10 +10607,10 @@
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C602" s="3">
         <v>130710.51053817889</v>
@@ -10602,10 +10624,10 @@
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C603" s="3">
         <v>120692.52894461731</v>
@@ -10619,10 +10641,10 @@
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C604" s="3">
         <v>120692.52894461731</v>
@@ -10636,10 +10658,10 @@
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C605" s="3">
         <v>126362.03522286958</v>
@@ -10653,10 +10675,10 @@
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C606" s="3">
         <v>165026.80094276034</v>
@@ -10670,10 +10692,10 @@
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C607" s="3">
         <v>158100.40602735957</v>
@@ -10687,10 +10709,10 @@
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C608" s="3">
         <v>145440.35132198705</v>
@@ -10704,10 +10726,10 @@
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C609" s="3">
         <v>178132.77671143232</v>
@@ -10721,10 +10743,10 @@
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C610" s="3">
         <v>165225.26154596073</v>
@@ -10738,10 +10760,10 @@
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C611" s="3">
         <v>104260.09881201708</v>
@@ -10755,10 +10777,10 @@
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C612" s="3">
         <v>32224.206999999999</v>
@@ -10772,10 +10794,10 @@
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C613" s="3">
         <v>36252.233</v>
@@ -10789,10 +10811,10 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C614" s="3">
         <v>92644.596000000005</v>
@@ -10806,10 +10828,10 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C615" s="3">
         <v>84991.346999999994</v>
@@ -10823,10 +10845,10 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C616" s="3">
         <v>33835.417999999998</v>
@@ -10840,10 +10862,10 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C617" s="3">
         <v>109965.10799999999</v>
@@ -10857,10 +10879,10 @@
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C618" s="3">
         <v>174816.32500000001</v>
@@ -10874,10 +10896,10 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C619" s="3">
         <v>125674.41</v>
@@ -10891,10 +10913,10 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C620" s="3">
         <v>186094.8</v>
@@ -10908,10 +10930,10 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C621" s="3">
         <v>178844.35</v>
@@ -10925,10 +10947,10 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C622" s="3">
         <v>165551.87</v>
@@ -10942,10 +10964,10 @@
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C623" s="3">
         <v>197398.3631409852</v>
@@ -10959,10 +10981,10 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C624" s="3">
         <v>227676.98552024309</v>
@@ -10976,10 +10998,10 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C625" s="3">
         <v>242460.24974388635</v>
@@ -10993,10 +11015,10 @@
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C626" s="3">
         <v>265090.93052942725</v>
@@ -11010,10 +11032,10 @@
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C627" s="3">
         <v>254119.42697087646</v>
@@ -11027,10 +11049,10 @@
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C628" s="3">
         <v>251018.83493052915</v>
@@ -11044,10 +11066,10 @@
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C629" s="3">
         <v>228029.2531500464</v>
@@ -11061,10 +11083,10 @@
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C630" s="3">
         <v>207755.42937511552</v>
@@ -11078,10 +11100,10 @@
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C631" s="3">
         <v>192604.93719886002</v>
@@ -11095,10 +11117,10 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C632" s="3">
         <v>194353.93932716036</v>
@@ -11112,10 +11134,10 @@
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C633" s="3">
         <v>145164.14734065809</v>
@@ -11129,10 +11151,10 @@
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C634" s="3">
         <v>131247.09668956493</v>
@@ -11146,10 +11168,10 @@
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C635" s="3">
         <v>142038.58515593995</v>
@@ -11163,10 +11185,10 @@
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C636" s="3">
         <v>50906.215554355993</v>
@@ -11180,10 +11202,10 @@
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C637" s="3">
         <v>47397.288384959851</v>
@@ -11197,10 +11219,10 @@
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C638" s="3">
         <v>46984.655675507878</v>
@@ -11214,10 +11236,10 @@
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C639" s="3">
         <v>43386.9891464498</v>
@@ -11231,10 +11253,10 @@
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C640" s="3">
         <v>16465.193822671186</v>
@@ -11248,10 +11270,10 @@
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C641" s="3">
         <v>217.73795044825414</v>
@@ -11265,10 +11287,10 @@
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C642" s="3">
         <v>31705.257707988181</v>
@@ -11282,10 +11304,10 @@
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C643" s="3">
         <v>83527.94</v>
@@ -11299,10 +11321,10 @@
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C644" s="3"/>
       <c r="D644" s="3">
@@ -11314,10 +11336,10 @@
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C645" s="3"/>
       <c r="D645" s="3">
@@ -11329,10 +11351,10 @@
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C646" s="3"/>
       <c r="D646" s="3">
@@ -11344,10 +11366,10 @@
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C647" s="3"/>
       <c r="D647" s="3">
@@ -11359,10 +11381,10 @@
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C648" s="3"/>
       <c r="D648" s="3">
@@ -11374,10 +11396,10 @@
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C649" s="3"/>
       <c r="D649" s="3">
@@ -11389,10 +11411,10 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C650" s="3"/>
       <c r="D650" s="3">
@@ -11404,10 +11426,10 @@
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C651" s="3"/>
       <c r="D651" s="3">
@@ -11419,10 +11441,10 @@
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C652" s="3"/>
       <c r="D652" s="3">
@@ -11434,10 +11456,10 @@
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C653" s="3"/>
       <c r="D653" s="3">
@@ -11449,10 +11471,10 @@
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C654" s="3"/>
       <c r="D654" s="3">
@@ -11464,10 +11486,10 @@
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C655" s="3"/>
       <c r="D655" s="3">
@@ -11479,10 +11501,10 @@
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C656" s="3"/>
       <c r="D656" s="3">
@@ -11494,10 +11516,10 @@
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C657" s="3"/>
       <c r="D657" s="3">
@@ -11509,10 +11531,10 @@
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C658" s="3"/>
       <c r="D658" s="3">
@@ -11524,10 +11546,10 @@
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C659" s="3"/>
       <c r="D659" s="3">
@@ -11539,10 +11561,10 @@
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C660" s="3"/>
       <c r="D660" s="3">
@@ -11554,10 +11576,10 @@
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C661" s="3"/>
       <c r="D661" s="3">
@@ -11569,10 +11591,10 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C662" s="3"/>
       <c r="D662" s="3">
@@ -11584,10 +11606,10 @@
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C663" s="3"/>
       <c r="D663" s="3">
@@ -11599,10 +11621,10 @@
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C664" s="3"/>
       <c r="D664" s="3">
@@ -11614,10 +11636,10 @@
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C665" s="3"/>
       <c r="D665" s="3">
@@ -11629,10 +11651,10 @@
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C666" s="3"/>
       <c r="D666" s="3">
@@ -11644,10 +11666,10 @@
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C667" s="3"/>
       <c r="D667" s="3">
@@ -11659,10 +11681,10 @@
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C668" s="3"/>
       <c r="D668" s="3">
@@ -11674,10 +11696,10 @@
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C669" s="3"/>
       <c r="D669" s="3">
@@ -11689,10 +11711,10 @@
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C670" s="3"/>
       <c r="D670" s="3">
@@ -11704,10 +11726,10 @@
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C671" s="3"/>
       <c r="D671" s="3">
@@ -11719,10 +11741,10 @@
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C672" s="3">
         <v>42885.197485220473</v>
@@ -11734,10 +11756,10 @@
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C673" s="3">
         <v>60954.31</v>
@@ -11749,10 +11771,10 @@
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C674" s="3">
         <v>47204.33</v>
@@ -11764,10 +11786,10 @@
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C675" s="3">
         <v>24668.959999999999</v>
@@ -11779,10 +11801,10 @@
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C676" s="3">
         <v>40298.53</v>
@@ -11794,10 +11816,10 @@
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C677" s="3">
         <v>65823.179999999993</v>
@@ -11809,10 +11831,10 @@
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C678" s="3">
         <v>55154.35</v>
@@ -11824,10 +11846,10 @@
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C679" s="3">
         <v>69303.728343001363</v>
@@ -11839,10 +11861,10 @@
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C680" s="3">
         <v>38459.14917177835</v>
@@ -11854,10 +11876,10 @@
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C681" s="3"/>
       <c r="D681" s="3">
@@ -11869,10 +11891,10 @@
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C682" s="3"/>
       <c r="D682" s="3">
@@ -11884,10 +11906,10 @@
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C683" s="3"/>
       <c r="D683" s="3">
@@ -11899,10 +11921,10 @@
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C684" s="3"/>
       <c r="D684" s="3">
@@ -11914,10 +11936,10 @@
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C685" s="3"/>
       <c r="D685" s="3">
@@ -11929,10 +11951,10 @@
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C686" s="3"/>
       <c r="D686" s="3">
@@ -11944,10 +11966,10 @@
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C687" s="3"/>
       <c r="D687" s="3">
@@ -11959,10 +11981,10 @@
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C688" s="3"/>
       <c r="D688" s="3">
@@ -11974,10 +11996,10 @@
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C689" s="3"/>
       <c r="D689" s="3">
@@ -11989,10 +12011,10 @@
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C690" s="3"/>
       <c r="D690" s="3">
@@ -12004,10 +12026,10 @@
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C691" s="3"/>
       <c r="D691" s="3">
@@ -12019,10 +12041,10 @@
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C692" s="3"/>
       <c r="D692" s="3">
@@ -12034,10 +12056,10 @@
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C693" s="3"/>
       <c r="D693" s="3">
@@ -12049,10 +12071,10 @@
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C694" s="3"/>
       <c r="D694" s="3">
@@ -12064,10 +12086,10 @@
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C695" s="3"/>
       <c r="D695" s="3">
@@ -12079,10 +12101,10 @@
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C696" s="3"/>
       <c r="D696" s="3">
